--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A829B5C2-27E4-4438-97AD-536DFD91552E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB79382-A264-43B9-A758-916E8373434A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" firstSheet="30" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -4298,19 +4298,6 @@
     <t>effort_SAR</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Fishing effort&lt;/h4&gt;
-&lt;p&gt;
-Spatial distribution of average annual fishing effort (mW fishing hours) in the years 2021–2024, by gear type. Fishing effort data are only shown for vessels &gt; 12 m with vessel monitoring systems (VMS)‡; this will bias the distributions, particularly in coastal areas. In the legend, “n” gives the number of c-squares attributed to that level.
-&lt;/p&gt; 
-&lt;p&gt;
-‡ Details on countries submitting VMS and logbook data can be found at &lt;a href="https://data.ices.dk/vms/inventory" target="_blank"&gt;ICES VMS and Logbook DataBase&lt;/a&gt;
-&lt;/p&gt; 
-&lt;h4&gt;Swept Area Ratio&lt;/h4&gt;
-&lt;p&gt;
-Average annual (2021–2024) surface (left panel) and subsurface (right panel) disturbance by mobile
-bottom-contacting fishing gear (bottom otter trawls, bottom seines, dredges, and beam trawls) in the ecoregion, expressed as average swept-area ratios (SAR).&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>&lt;ul&gt;
   &lt;li&gt;
     The majority of the fisheries in the Azores ecoregion are targeted by Azorean vessels. Only a small proportion of catch is taken by surface longliners from mainland Portugal and Spain targeting swordfish and blue shark. The fisheries are classified as small scale because around 60% of the vessels are under nine metres in length and target many different species. The most important targets are tuna and tuna-like species (in weight), deep-water demersal species (in value), and small pelagic species. The most important fishing methods are handline and bottom longline, followed by pole and line (bait boats). Surface longline is also used but mainly by non-regional vessels that operate outside a 100 nautical mile area. The Azores Exclusive Economic Zone (EEZ) is recognized as a no take area for nets (including a trawl ban) excluding a few small coastal gillnets and purse seiners for small pelagics.
@@ -4519,6 +4506,19 @@
  The fisheries overview document (pdf) is accessible at
   &lt;a href="https://doi.org/10.17895/ices.advice.27880092" target="_blank"&gt;ICES Library&lt;/a&gt;.
 &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Fishing effort&lt;/h4&gt;
+&lt;p&gt;
+Spatial distribution of average annual fishing effort (mW fishing hours) in the years 2021–2024, by gear type. Fishing effort data are only shown for vessels &gt; 12 m with vessel monitoring systems (VMS)‡; this will bias the distributions, particularly in coastal areas. In the legend, “n” gives the number of c-squares attributed to that level. The data is aggregated to ensure vessel anonymity.
+&lt;/p&gt; 
+&lt;p&gt;
+‡ Details on countries submitting VMS and logbook data can be found at &lt;a href="https://data.ices.dk/vms/inventory" target="_blank"&gt;ICES VMS and Logbook DataBase&lt;/a&gt;
+&lt;/p&gt; 
+&lt;h4&gt;Swept Area Ratio&lt;/h4&gt;
+&lt;p&gt;
+Average annual (2021–2024) surface (left panel) and subsurface (right panel) disturbance by mobile
+bottom-contacting fishing gear (bottom otter trawls, bottom seines, dredges, and beam trawls) in the ecoregion, expressed as average swept-area ratios (SAR). In the legend, “n” gives the number of c-squares attributed to that level. The data is aggregated to ensure vessel anonymity.&lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -4953,16 +4953,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C292"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.6640625" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>49</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>41</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>23</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>31</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>27</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>37</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>47</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
         <v>66</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>69</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>72</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>75</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>78</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>81</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>84</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>87</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>90</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>93</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>96</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>99</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>102</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>105</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>108</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>111</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>114</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>117</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>120</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>123</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>126</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>129</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>132</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>135</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>138</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>141</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>144</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>147</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>150</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>153</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>156</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>159</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>162</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>165</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>168</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>171</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>174</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>177</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>180</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>183</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>186</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>189</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
         <v>192</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>195</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>198</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>201</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>204</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>207</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>210</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>213</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>216</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>219</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>222</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>225</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>228</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>231</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>234</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>237</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>240</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>243</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>246</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>249</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>252</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>255</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>258</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>261</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>264</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>267</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>270</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>273</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>276</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>279</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>282</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>285</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>288</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>291</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>294</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>297</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>300</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>303</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>306</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>309</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
         <v>312</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>315</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>318</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>321</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
         <v>324</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>327</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>330</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>333</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>336</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>339</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>342</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>345</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
         <v>348</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>351</v>
       </c>
@@ -6238,7 +6238,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>354</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>357</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>360</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>363</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>366</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
         <v>369</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>372</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>375</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="10" t="s">
         <v>378</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>381</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>384</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>387</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>390</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>393</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>396</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>399</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>402</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>405</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>408</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>411</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="10" t="s">
         <v>414</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>417</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>420</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>423</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
         <v>426</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>429</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="10" t="s">
         <v>432</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
         <v>435</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="10" t="s">
         <v>438</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>441</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>444</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>447</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
         <v>450</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>453</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
         <v>456</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>459</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
         <v>462</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
         <v>465</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="10" t="s">
         <v>468</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
         <v>471</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="10" t="s">
         <v>474</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
         <v>477</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="10" t="s">
         <v>480</v>
       </c>
@@ -6711,7 +6711,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
         <v>483</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="10" t="s">
         <v>486</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
         <v>489</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="10" t="s">
         <v>492</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
         <v>495</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="10" t="s">
         <v>498</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
         <v>501</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="10" t="s">
         <v>504</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
         <v>507</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="10" t="s">
         <v>510</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
         <v>513</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
         <v>516</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>519</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>522</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>525</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="10" t="s">
         <v>528</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>531</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="10" t="s">
         <v>534</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
         <v>537</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="10" t="s">
         <v>540</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
         <v>543</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
         <v>546</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>549</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
         <v>552</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>555</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
         <v>558</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>561</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
         <v>564</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>567</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
         <v>570</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>573</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
         <v>576</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>579</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="10" t="s">
         <v>582</v>
       </c>
@@ -7085,7 +7085,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
         <v>585</v>
       </c>
@@ -7096,7 +7096,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="10" t="s">
         <v>588</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
         <v>591</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="10" t="s">
         <v>594</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
         <v>597</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
         <v>600</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>603</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
         <v>606</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>609</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
         <v>612</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>615</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="10" t="s">
         <v>618</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
         <v>621</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
         <v>624</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>627</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
         <v>630</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
         <v>633</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="10" t="s">
         <v>636</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>639</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="10" t="s">
         <v>642</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>645</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
         <v>648</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>651</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
         <v>654</v>
       </c>
@@ -7349,7 +7349,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>657</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
         <v>660</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>663</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
         <v>666</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>669</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
         <v>672</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>675</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>678</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>681</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>684</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>687</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>690</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>693</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>696</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>699</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
         <v>702</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>705</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>708</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>711</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>714</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>717</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
         <v>720</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
         <v>723</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="10" t="s">
         <v>726</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="10" t="s">
         <v>729</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="10" t="s">
         <v>732</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="10" t="s">
         <v>735</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
         <v>738</v>
       </c>
@@ -7657,7 +7657,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
         <v>741</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
         <v>744</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
         <v>747</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
         <v>750</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
         <v>753</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
         <v>756</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
         <v>759</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
         <v>762</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
         <v>765</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="10" t="s">
         <v>768</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="10" t="s">
         <v>771</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="10" t="s">
         <v>774</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="10" t="s">
         <v>777</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="10" t="s">
         <v>780</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="10" t="s">
         <v>783</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" s="10" t="s">
         <v>786</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="10" t="s">
         <v>789</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="10" t="s">
         <v>792</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
         <v>795</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="10" t="s">
         <v>798</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="10" t="s">
         <v>801</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="10" t="s">
         <v>804</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="10" t="s">
         <v>807</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="10" t="s">
         <v>810</v>
       </c>
@@ -7921,7 +7921,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="10" t="s">
         <v>813</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="10" t="s">
         <v>816</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="10" t="s">
         <v>819</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="10" t="s">
         <v>822</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="10" t="s">
         <v>825</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="10" t="s">
         <v>828</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="10" t="s">
         <v>831</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="10" t="s">
         <v>834</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="10" t="s">
         <v>837</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="10" t="s">
         <v>840</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="10" t="s">
         <v>843</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="10" t="s">
         <v>846</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="10" t="s">
         <v>849</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="10" t="s">
         <v>852</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="10" t="s">
         <v>855</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="10" t="s">
         <v>858</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="10" t="s">
         <v>861</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="10" t="s">
         <v>864</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="10" t="s">
         <v>867</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="10" t="s">
         <v>870</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="10" t="s">
         <v>873</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="10" t="s">
         <v>876</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="10" t="s">
         <v>879</v>
       </c>
@@ -8191,13 +8191,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8205,15 +8205,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8240,13 +8240,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="198.36328125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8254,15 +8254,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8286,13 +8286,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="229.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="229.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8300,15 +8300,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8332,13 +8332,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8370,13 +8370,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8408,13 +8408,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8446,13 +8446,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8484,12 +8484,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+    <col min="2" max="2" width="125.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -8521,13 +8521,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8559,13 +8559,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8597,13 +8597,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="152.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="152.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8611,15 +8611,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8643,13 +8643,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8684,13 +8684,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8722,13 +8722,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8760,13 +8760,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8799,13 +8799,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8851,13 +8851,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8902,13 +8902,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8953,13 +8953,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9007,13 +9007,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9058,13 +9058,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9109,13 +9109,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="253.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="253.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9123,15 +9123,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9155,13 +9155,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9206,13 +9206,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9257,13 +9257,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9308,13 +9308,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9359,13 +9359,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9413,13 +9413,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9427,12 +9427,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9443,13 +9443,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9457,12 +9457,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9473,13 +9473,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9487,12 +9487,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9503,13 +9503,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9517,12 +9517,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9533,13 +9533,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9547,12 +9547,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9563,13 +9563,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="223.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="223.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9577,15 +9577,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9609,13 +9609,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9623,12 +9623,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9639,13 +9639,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9653,12 +9653,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9669,13 +9669,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9683,12 +9683,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9699,13 +9699,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9713,12 +9713,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9729,13 +9729,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9743,12 +9743,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9759,13 +9759,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9773,12 +9773,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9792,12 +9792,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9824,13 +9824,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="159.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="159.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9854,13 +9854,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="181.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9868,15 +9868,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9900,13 +9900,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="222.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="222.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9914,15 +9914,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9930,7 +9930,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9946,13 +9946,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="137.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="137.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9960,15 +9960,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9984,13 +9984,13 @@
         <v>899</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10001,13 +10001,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="135.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="135.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10047,13 +10047,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="114.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="114.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A829B5C2-27E4-4438-97AD-536DFD91552E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A487D9-2DDD-4C63-B91B-4023BC05F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="932">
   <si>
     <t>section</t>
   </si>
@@ -4519,6 +4519,9 @@
  The fisheries overview document (pdf) is accessible at
   &lt;a href="https://doi.org/10.17895/ices.advice.27880092" target="_blank"&gt;ICES Library&lt;/a&gt;.
 &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Metier / fleet grouping</t>
   </si>
 </sst>
 </file>
@@ -4952,17 +4955,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
-  <dimension ref="A1:C292"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C293"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.6640625" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -4973,7 +4976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -4984,7 +4987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
@@ -4995,7 +4998,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -5017,7 +5020,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
@@ -5028,7 +5031,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -5039,7 +5042,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5050,7 +5053,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -5061,7 +5064,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>49</v>
       </c>
@@ -5072,7 +5075,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
@@ -5083,7 +5086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>41</v>
       </c>
@@ -5094,7 +5097,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>23</v>
       </c>
@@ -5105,7 +5108,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5116,3070 +5119,3081 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B22" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C22" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B24" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B25" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C25" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B26" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C26" s="10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B27" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C27" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B28" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B29" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B30" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C30" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B31" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C31" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B32" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C32" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B33" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C33" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B34" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C34" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B35" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C35" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B36" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C36" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B37" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C37" s="10" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B38" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C38" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B39" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C39" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B40" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C40" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B41" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C41" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B42" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C42" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B43" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C43" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B44" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="10" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B45" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C45" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="10" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B46" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C46" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C48" s="10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B49" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C49" s="10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B50" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C50" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B51" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C51" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B52" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C52" s="10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B53" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C53" s="10" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="10" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C54" s="10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C55" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B56" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C56" s="10" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="10" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C57" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B58" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C58" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C59" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="10" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B60" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C60" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B61" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C61" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B62" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C62" s="10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B63" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C63" s="10" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="10" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B64" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C64" s="10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B65" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C65" s="10" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B66" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C66" s="10" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="10" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B67" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C67" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="10" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B68" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C68" s="10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="10" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B69" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C69" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B70" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C70" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="10" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B71" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C71" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="10" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B72" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C72" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="10" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B73" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C73" s="10" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B74" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C74" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B75" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C75" s="10" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="10" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B76" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C76" s="10" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="10" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B77" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C77" s="10" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="10" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B78" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C78" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="10" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B79" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C79" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B80" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C80" s="10" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="10" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B81" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C81" s="10" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="10" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B82" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C82" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="10" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B83" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C83" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="10" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B84" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C84" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="10" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B85" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C85" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B86" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C86" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="10" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B87" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C87" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="10" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B88" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C88" s="10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="10" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B89" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C89" s="10" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="10" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B90" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C90" s="10" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="10" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B91" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="10" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B92" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C92" s="10" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B93" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C93" s="10" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B94" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C94" s="10" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B95" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C95" s="10" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="10" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B96" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C96" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B97" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C97" s="10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="10" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B98" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C98" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="10" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B99" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C99" s="10" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="10" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B100" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C100" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B101" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C101" s="10" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B102" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C102" s="10" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B103" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C103" s="10" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="10" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B104" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C104" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B105" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C105" s="10" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B106" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C106" s="10" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B107" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C107" s="10" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="10" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B108" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C108" s="10" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="10" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B109" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C109" s="10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="10" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B110" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C110" s="10" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B111" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C111" s="10" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="10" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B112" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C112" s="10" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="10" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B113" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C113" s="10" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="10" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B114" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C114" s="10" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="10" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B115" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C115" s="10" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="10" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B116" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="C115" s="10" t="s">
+      <c r="C116" s="10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="10" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B117" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C117" s="10" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="10" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B118" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C118" s="10" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="10" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B119" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C119" s="10" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B120" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C120" s="10" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="10" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B121" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C121" s="10" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="10" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B122" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C122" s="10" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B123" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C123" s="10" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="10" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B124" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C124" s="10" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="10" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B125" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C125" s="10" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="10" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B126" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C126" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B127" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C127" s="10" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="10" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B128" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C128" s="10" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B129" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C129" s="10" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B130" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C130" s="10" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="10" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B131" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C131" s="10" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="10" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B131" s="10" t="s">
+      <c r="B132" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="C131" s="10" t="s">
+      <c r="C132" s="10" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="10" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B133" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C133" s="10" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B134" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C134" s="10" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="10" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B135" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C135" s="10" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B136" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="C136" s="10" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="10" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B137" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C137" s="10" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="10" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B138" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="10" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B139" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C139" s="10" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="10" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B140" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C140" s="10" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="10" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B141" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C141" s="10" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="10" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B142" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="C141" s="10" t="s">
+      <c r="C142" s="10" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="10" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B143" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C143" s="10" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="10" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B144" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C144" s="10" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="10" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B145" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C145" s="10" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="10" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B146" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C146" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="10" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B147" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C147" s="10" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="10" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B148" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C148" s="10" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="10" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B149" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C149" s="10" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="10" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B150" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C150" s="10" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="10" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B151" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C151" s="10" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="10" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B152" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C152" s="10" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="10" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B153" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C153" s="10" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="10" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B153" s="10" t="s">
+      <c r="B154" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C154" s="10" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="10" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B155" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C155" s="10" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="10" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B156" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C156" s="10" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="10" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="B157" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C157" s="10" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="10" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B158" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C158" s="10" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="10" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B158" s="10" t="s">
+      <c r="B159" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C159" s="10" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="10" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="B160" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C160" s="10" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="10" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="B161" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C161" s="10" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="10" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="B161" s="10" t="s">
+      <c r="B162" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="C161" s="10" t="s">
+      <c r="C162" s="10" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="10" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B163" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C163" s="10" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="10" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B164" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C164" s="10" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="10" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B165" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C165" s="10" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="10" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B166" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C166" s="10" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="10" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B167" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C167" s="10" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="10" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B168" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C168" s="10" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="10" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B169" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="C168" s="10" t="s">
+      <c r="C169" s="10" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="10" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="B169" s="10" t="s">
+      <c r="B170" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C170" s="10" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="10" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B170" s="10" t="s">
+      <c r="B171" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C171" s="10" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="10" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="B171" s="10" t="s">
+      <c r="B172" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C172" s="10" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="10" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B173" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C173" s="10" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="10" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B174" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C174" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="10" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B175" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="C175" s="10" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="10" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B176" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C176" s="10" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="10" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B176" s="10" t="s">
+      <c r="B177" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C177" s="10" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="10" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B178" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C178" s="10" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="10" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="B178" s="10" t="s">
+      <c r="B179" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C179" s="10" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="10" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B180" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="C179" s="10" t="s">
+      <c r="C180" s="10" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="10" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="B180" s="10" t="s">
+      <c r="B181" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C181" s="10" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="10" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="B181" s="10" t="s">
+      <c r="B182" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C182" s="10" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="10" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="B183" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="C182" s="10" t="s">
+      <c r="C183" s="10" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" s="10" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B184" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C184" s="10" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="10" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B185" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C185" s="10" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="10" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="B185" s="10" t="s">
+      <c r="B186" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C186" s="10" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" s="10" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="B186" s="10" t="s">
+      <c r="B187" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C187" s="10" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="10" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="B187" s="10" t="s">
+      <c r="B188" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C188" s="10" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="10" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B189" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C189" s="10" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="10" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B190" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C190" s="10" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="10" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B191" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C191" s="10" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="10" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B192" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="C192" s="10" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="10" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B193" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C193" s="10" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="10" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B194" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C194" s="10" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="10" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B195" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C195" s="10" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="10" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B196" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C196" s="10" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="10" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B197" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C197" s="10" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="10" t="s">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B198" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="C197" s="10" t="s">
+      <c r="C198" s="10" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="10" t="s">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="B198" s="10" t="s">
+      <c r="B199" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C199" s="10" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="10" t="s">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="B200" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C200" s="10" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" s="10" t="s">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B201" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C201" s="10" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" s="10" t="s">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="B201" s="10" t="s">
+      <c r="B202" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C202" s="10" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" s="10" t="s">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B203" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C203" s="10" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" s="10" t="s">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B204" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="C203" s="10" t="s">
+      <c r="C204" s="10" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" s="10" t="s">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="B204" s="10" t="s">
+      <c r="B205" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C204" s="10" t="s">
+      <c r="C205" s="10" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" s="10" t="s">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B206" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C205" s="10" t="s">
+      <c r="C206" s="10" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" s="10" t="s">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="B206" s="10" t="s">
+      <c r="B207" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="C206" s="10" t="s">
+      <c r="C207" s="10" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" s="10" t="s">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="B207" s="10" t="s">
+      <c r="B208" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="C207" s="10" t="s">
+      <c r="C208" s="10" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" s="10" t="s">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="B208" s="10" t="s">
+      <c r="B209" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="C209" s="10" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" s="10" t="s">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="B209" s="10" t="s">
+      <c r="B210" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="C209" s="10" t="s">
+      <c r="C210" s="10" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" s="10" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B211" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C211" s="10" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="10" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B212" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C212" s="10" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" s="10" t="s">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="B212" s="10" t="s">
+      <c r="B213" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C213" s="10" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="10" t="s">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B214" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C214" s="10" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214" s="10" t="s">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="B214" s="10" t="s">
+      <c r="B215" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="C214" s="10" t="s">
+      <c r="C215" s="10" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215" s="10" t="s">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B216" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="C216" s="10" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A216" s="10" t="s">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B217" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="C217" s="10" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A217" s="10" t="s">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B218" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="C217" s="10" t="s">
+      <c r="C218" s="10" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A218" s="10" t="s">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B219" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="C218" s="10" t="s">
+      <c r="C219" s="10" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A219" s="10" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B220" s="10" t="s">
         <v>661</v>
       </c>
-      <c r="C219" s="10" t="s">
+      <c r="C220" s="10" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A220" s="10" t="s">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="B220" s="10" t="s">
+      <c r="B221" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="C220" s="10" t="s">
+      <c r="C221" s="10" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A221" s="10" t="s">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="B221" s="10" t="s">
+      <c r="B222" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="C222" s="10" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A222" s="10" t="s">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="B222" s="10" t="s">
+      <c r="B223" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="C222" s="10" t="s">
+      <c r="C223" s="10" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A223" s="10" t="s">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B223" s="10" t="s">
+      <c r="B224" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="C223" s="10" t="s">
+      <c r="C224" s="10" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A224" s="10" t="s">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="B224" s="10" t="s">
+      <c r="B225" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="C224" s="10" t="s">
+      <c r="C225" s="10" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A225" s="10" t="s">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="B225" s="10" t="s">
+      <c r="B226" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="C225" s="10" t="s">
+      <c r="C226" s="10" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A226" s="10" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="B226" s="10" t="s">
+      <c r="B227" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="C226" s="10" t="s">
+      <c r="C227" s="10" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" s="10" t="s">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="B227" s="10" t="s">
+      <c r="B228" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="C228" s="10" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" s="10" t="s">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="B228" s="10" t="s">
+      <c r="B229" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="C228" s="10" t="s">
+      <c r="C229" s="10" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" s="10" t="s">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="B229" s="10" t="s">
+      <c r="B230" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="C229" s="10" t="s">
+      <c r="C230" s="10" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="10" t="s">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B231" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="C230" s="10" t="s">
+      <c r="C231" s="10" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="10" t="s">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B232" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="C231" s="10" t="s">
+      <c r="C232" s="10" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" s="10" t="s">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="B232" s="10" t="s">
+      <c r="B233" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="C232" s="10" t="s">
+      <c r="C233" s="10" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233" s="10" t="s">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B234" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="C233" s="10" t="s">
+      <c r="C234" s="10" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" s="10" t="s">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="B234" s="10" t="s">
+      <c r="B235" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="C234" s="10" t="s">
+      <c r="C235" s="10" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A235" s="10" t="s">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="B235" s="10" t="s">
+      <c r="B236" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="C235" s="10" t="s">
+      <c r="C236" s="10" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A236" s="10" t="s">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="B236" s="10" t="s">
+      <c r="B237" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="C236" s="10" t="s">
+      <c r="C237" s="10" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A237" s="10" t="s">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="B237" s="10" t="s">
+      <c r="B238" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="C237" s="10" t="s">
+      <c r="C238" s="10" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A238" s="10" t="s">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="B238" s="10" t="s">
+      <c r="B239" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C238" s="10" t="s">
+      <c r="C239" s="10" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A239" s="10" t="s">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="B239" s="10" t="s">
+      <c r="B240" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="C240" s="10" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A240" s="10" t="s">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="B240" s="10" t="s">
+      <c r="B241" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="C240" s="10" t="s">
+      <c r="C241" s="10" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A241" s="10" t="s">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="B241" s="10" t="s">
+      <c r="B242" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="C241" s="10" t="s">
+      <c r="C242" s="10" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" s="10" t="s">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="B242" s="10" t="s">
+      <c r="B243" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C243" s="10" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243" s="10" t="s">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="B243" s="10" t="s">
+      <c r="B244" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="C243" s="10" t="s">
+      <c r="C244" s="10" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244" s="10" t="s">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="B244" s="10" t="s">
+      <c r="B245" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="C244" s="10" t="s">
+      <c r="C245" s="10" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245" s="10" t="s">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="B245" s="10" t="s">
+      <c r="B246" s="10" t="s">
         <v>739</v>
       </c>
-      <c r="C245" s="10" t="s">
+      <c r="C246" s="10" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="10" t="s">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B247" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="C246" s="10" t="s">
+      <c r="C247" s="10" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="10" t="s">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B247" s="10" t="s">
+      <c r="B248" s="10" t="s">
         <v>745</v>
       </c>
-      <c r="C247" s="10" t="s">
+      <c r="C248" s="10" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="10" t="s">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" s="10" t="s">
         <v>747</v>
       </c>
-      <c r="B248" s="10" t="s">
+      <c r="B249" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="C248" s="10" t="s">
+      <c r="C249" s="10" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="10" t="s">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="B249" s="10" t="s">
+      <c r="B250" s="10" t="s">
         <v>751</v>
       </c>
-      <c r="C249" s="10" t="s">
+      <c r="C250" s="10" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A250" s="10" t="s">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" s="10" t="s">
         <v>753</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B251" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="C250" s="10" t="s">
+      <c r="C251" s="10" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="10" t="s">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="B251" s="10" t="s">
+      <c r="B252" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C251" s="10" t="s">
+      <c r="C252" s="10" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="10" t="s">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" s="10" t="s">
         <v>759</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B253" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="C252" s="10" t="s">
+      <c r="C253" s="10" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253" s="10" t="s">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="B253" s="10" t="s">
+      <c r="B254" s="10" t="s">
         <v>763</v>
       </c>
-      <c r="C253" s="10" t="s">
+      <c r="C254" s="10" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="10" t="s">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" s="10" t="s">
         <v>765</v>
       </c>
-      <c r="B254" s="10" t="s">
+      <c r="B255" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="C254" s="10" t="s">
+      <c r="C255" s="10" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A255" s="10" t="s">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="B255" s="10" t="s">
+      <c r="B256" s="10" t="s">
         <v>769</v>
       </c>
-      <c r="C255" s="10" t="s">
+      <c r="C256" s="10" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A256" s="10" t="s">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" s="10" t="s">
         <v>771</v>
       </c>
-      <c r="B256" s="10" t="s">
+      <c r="B257" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C256" s="10" t="s">
+      <c r="C257" s="10" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A257" s="10" t="s">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="B257" s="10" t="s">
+      <c r="B258" s="10" t="s">
         <v>775</v>
       </c>
-      <c r="C257" s="10" t="s">
+      <c r="C258" s="10" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A258" s="10" t="s">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="B258" s="10" t="s">
+      <c r="B259" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="C258" s="10" t="s">
+      <c r="C259" s="10" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A259" s="10" t="s">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="B259" s="10" t="s">
+      <c r="B260" s="10" t="s">
         <v>781</v>
       </c>
-      <c r="C259" s="10" t="s">
+      <c r="C260" s="10" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A260" s="10" t="s">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="B260" s="10" t="s">
+      <c r="B261" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="C260" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A261" s="10" t="s">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="B262" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="C261" s="10" t="s">
+      <c r="C262" s="10" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A262" s="10" t="s">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="B262" s="10" t="s">
+      <c r="B263" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="C262" s="10" t="s">
+      <c r="C263" s="10" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A263" s="10" t="s">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="B263" s="10" t="s">
+      <c r="B264" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="C263" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A264" s="10" t="s">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="B265" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="C265" s="10" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A265" s="10" t="s">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="B265" s="10" t="s">
+      <c r="B266" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="C265" s="10" t="s">
+      <c r="C266" s="10" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266" s="10" t="s">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="B266" s="10" t="s">
+      <c r="B267" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="C266" s="10" t="s">
+      <c r="C267" s="10" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A267" s="10" t="s">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="B267" s="10" t="s">
+      <c r="B268" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="C267" s="10" t="s">
+      <c r="C268" s="10" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268" s="10" t="s">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="B268" s="10" t="s">
+      <c r="B269" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="C268" s="10" t="s">
+      <c r="C269" s="10" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269" s="10" t="s">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="B269" s="10" t="s">
+      <c r="B270" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C269" s="10" t="s">
+      <c r="C270" s="10" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" s="10" t="s">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="B270" s="10" t="s">
+      <c r="B271" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="C270" s="10" t="s">
+      <c r="C271" s="10" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" s="10" t="s">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272" s="10" t="s">
         <v>816</v>
       </c>
-      <c r="B271" s="10" t="s">
+      <c r="B272" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C271" s="10" t="s">
+      <c r="C272" s="10" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" s="10" t="s">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="B272" s="10" t="s">
+      <c r="B273" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="C272" s="10" t="s">
+      <c r="C273" s="10" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" s="10" t="s">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274" s="10" t="s">
         <v>822</v>
       </c>
-      <c r="B273" s="10" t="s">
+      <c r="B274" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="C273" s="10" t="s">
+      <c r="C274" s="10" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" s="10" t="s">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275" s="10" t="s">
         <v>825</v>
       </c>
-      <c r="B274" s="10" t="s">
+      <c r="B275" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C274" s="10" t="s">
+      <c r="C275" s="10" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" s="10" t="s">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="B275" s="10" t="s">
+      <c r="B276" s="10" t="s">
         <v>829</v>
       </c>
-      <c r="C275" s="10" t="s">
+      <c r="C276" s="10" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A276" s="10" t="s">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277" s="10" t="s">
         <v>831</v>
       </c>
-      <c r="B276" s="10" t="s">
+      <c r="B277" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C276" s="10" t="s">
+      <c r="C277" s="10" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" s="10" t="s">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="B277" s="10" t="s">
+      <c r="B278" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="C277" s="10" t="s">
+      <c r="C278" s="10" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A278" s="10" t="s">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279" s="10" t="s">
         <v>837</v>
       </c>
-      <c r="B278" s="10" t="s">
+      <c r="B279" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C278" s="10" t="s">
+      <c r="C279" s="10" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A279" s="10" t="s">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="B279" s="10" t="s">
+      <c r="B280" s="10" t="s">
         <v>841</v>
       </c>
-      <c r="C279" s="10" t="s">
+      <c r="C280" s="10" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" s="10" t="s">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281" s="10" t="s">
         <v>843</v>
       </c>
-      <c r="B280" s="10" t="s">
+      <c r="B281" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="C280" s="10" t="s">
+      <c r="C281" s="10" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A281" s="10" t="s">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B282" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="C281" s="10" t="s">
+      <c r="C282" s="10" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A282" s="10" t="s">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283" s="10" t="s">
         <v>849</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B283" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="C282" s="10" t="s">
+      <c r="C283" s="10" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A283" s="10" t="s">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B284" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="C283" s="10" t="s">
+      <c r="C284" s="10" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" s="10" t="s">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285" s="10" t="s">
         <v>855</v>
       </c>
-      <c r="B284" s="10" t="s">
+      <c r="B285" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="C284" s="10" t="s">
+      <c r="C285" s="10" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" s="10" t="s">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="B286" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="C286" s="10" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" s="10" t="s">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="B286" s="10" t="s">
+      <c r="B287" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="C286" s="10" t="s">
+      <c r="C287" s="10" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" s="10" t="s">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="B287" s="10" t="s">
+      <c r="B288" s="10" t="s">
         <v>865</v>
       </c>
-      <c r="C287" s="10" t="s">
+      <c r="C288" s="10" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" s="10" t="s">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289" s="10" t="s">
         <v>867</v>
       </c>
-      <c r="B288" s="10" t="s">
+      <c r="B289" s="10" t="s">
         <v>868</v>
       </c>
-      <c r="C288" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" s="10" t="s">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290" s="10" t="s">
         <v>870</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="B290" s="10" t="s">
         <v>871</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="C290" s="10" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" s="10" t="s">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291" s="10" t="s">
         <v>873</v>
       </c>
-      <c r="B290" s="10" t="s">
+      <c r="B291" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="C290" s="10" t="s">
+      <c r="C291" s="10" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A291" s="10" t="s">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292" s="10" t="s">
         <v>876</v>
       </c>
-      <c r="B291" s="10" t="s">
+      <c r="B292" s="10" t="s">
         <v>877</v>
       </c>
-      <c r="C291" s="10" t="s">
+      <c r="C292" s="10" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" s="10" t="s">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293" s="10" t="s">
         <v>879</v>
       </c>
-      <c r="B292" s="10" t="s">
+      <c r="B293" s="10" t="s">
         <v>880</v>
       </c>
-      <c r="C292" s="10" t="s">
+      <c r="C293" s="10" t="s">
         <v>881</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
-    <sortCondition ref="A2:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C21">
+    <sortCondition ref="A2:A21"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C37" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
+    <hyperlink ref="C38" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8191,13 +8205,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8205,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8213,7 +8227,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8221,7 +8235,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8240,13 +8254,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="198.36328125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8254,7 +8268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8262,7 +8276,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8270,7 +8284,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8286,13 +8300,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="229.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="229.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8300,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8308,7 +8322,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8316,7 +8330,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8332,13 +8346,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8346,7 +8360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8354,7 +8368,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8370,13 +8384,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8384,7 +8398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8392,7 +8406,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8408,13 +8422,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8422,7 +8436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8430,7 +8444,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8446,13 +8460,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8460,7 +8474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8468,7 +8482,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8484,12 +8498,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+    <col min="2" max="2" width="125.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8497,7 +8511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8505,7 +8519,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -8521,13 +8535,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8535,7 +8549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8543,7 +8557,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8559,13 +8573,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8573,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8581,7 +8595,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8597,13 +8611,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="152.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="152.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8611,7 +8625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8619,7 +8633,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8627,7 +8641,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8643,13 +8657,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8657,7 +8671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8665,7 +8679,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8684,13 +8698,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8698,7 +8712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8706,7 +8720,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8722,13 +8736,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8736,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8744,7 +8758,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8760,13 +8774,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8774,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8782,7 +8796,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8799,13 +8813,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8813,7 +8827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8821,7 +8835,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8829,7 +8843,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8837,7 +8851,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8851,13 +8865,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8865,7 +8879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8873,7 +8887,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8881,7 +8895,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8889,7 +8903,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8902,13 +8916,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8916,7 +8930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8924,7 +8938,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8932,7 +8946,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8940,7 +8954,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8953,13 +8967,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8967,7 +8981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8975,7 +8989,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8983,7 +8997,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8991,7 +9005,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9007,13 +9021,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9021,7 +9035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9029,7 +9043,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9037,7 +9051,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9045,7 +9059,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9058,13 +9072,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9072,7 +9086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9080,7 +9094,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9088,7 +9102,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9096,7 +9110,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9109,13 +9123,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="253.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="253.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9123,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9131,7 +9145,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9139,7 +9153,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9155,13 +9169,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9169,7 +9183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9177,7 +9191,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9185,7 +9199,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9193,7 +9207,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9206,13 +9220,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9220,7 +9234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9228,7 +9242,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9236,7 +9250,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9244,7 +9258,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9257,13 +9271,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9271,7 +9285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9279,7 +9293,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9287,7 +9301,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9295,7 +9309,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9308,13 +9322,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9322,7 +9336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9330,7 +9344,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9338,7 +9352,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9346,7 +9360,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9359,13 +9373,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="199.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9373,7 +9387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9381,7 +9395,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9389,7 +9403,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9397,7 +9411,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9413,13 +9427,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9427,7 +9441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9443,13 +9457,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9457,7 +9471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9473,13 +9487,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9487,7 +9501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9503,13 +9517,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9517,7 +9531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9533,13 +9547,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9547,7 +9561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9563,13 +9577,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="223.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="223.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9577,7 +9591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9585,7 +9599,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9593,7 +9607,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9609,13 +9623,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9623,7 +9637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9639,13 +9653,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9653,7 +9667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9669,13 +9683,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9683,7 +9697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9699,13 +9713,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9713,7 +9727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9729,13 +9743,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9743,7 +9757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9759,13 +9773,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9773,7 +9787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9792,12 +9806,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9805,7 +9819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9824,13 +9838,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="159.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="159.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9838,7 +9852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9854,13 +9868,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="181.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9868,7 +9882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9876,7 +9890,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9884,7 +9898,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9900,13 +9914,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="222.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="222.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9914,7 +9928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9922,7 +9936,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9930,7 +9944,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9946,13 +9960,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="137.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="137.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9960,7 +9974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9968,7 +9982,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9976,7 +9990,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9984,13 +9998,13 @@
         <v>899</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10001,13 +10015,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="135.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="135.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10015,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10023,7 +10037,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10031,7 +10045,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10047,13 +10061,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="114.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="114.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10061,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10069,7 +10083,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10077,7 +10091,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A487D9-2DDD-4C63-B91B-4023BC05F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523558E1-3178-4680-8AE7-AA5F361413F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="998">
   <si>
     <t>section</t>
   </si>
@@ -4522,6 +4522,204 @@
   </si>
   <si>
     <t>Metier / fleet grouping</t>
+  </si>
+  <si>
+    <t>GTR</t>
+  </si>
+  <si>
+    <t>Trammel nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=45a8983a-2a25-4959-a5aa-eb15816ddfe0</t>
+  </si>
+  <si>
+    <t>LLD</t>
+  </si>
+  <si>
+    <t>Drifting longlines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=327a2e44-ed48-44b0-900d-a07b4ac6e0fb</t>
+  </si>
+  <si>
+    <t>OTB</t>
+  </si>
+  <si>
+    <t>Bottom otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=573c31dc-b343-42c2-9697-c9a20cfc6be0</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>Purse seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=68ca65b7-3374-4fec-8bdd-8a3ccd36d7a4</t>
+  </si>
+  <si>
+    <t>PTM</t>
+  </si>
+  <si>
+    <t>Pelagic pair trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=8ce860fd-b3ea-4361-ad13-44a9f8535731</t>
+  </si>
+  <si>
+    <t>GNS</t>
+  </si>
+  <si>
+    <t>Set gillnet</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=55f84dad-e861-4d12-8582-b0fe00d99633</t>
+  </si>
+  <si>
+    <t>LLS</t>
+  </si>
+  <si>
+    <t>Set longlines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=940eecd0-d03c-444c-b388-e01d0b72ac03</t>
+  </si>
+  <si>
+    <t>FPO</t>
+  </si>
+  <si>
+    <t>Pots and traps</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=fe1fbee6-5d67-439f-aabf-ca13c48a7d62</t>
+  </si>
+  <si>
+    <t>LHP</t>
+  </si>
+  <si>
+    <t>Hand and pole lines (hand-operated)</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=3e577955-36e8-41af-aef8-3c3e57b55327</t>
+  </si>
+  <si>
+    <t>FPN</t>
+  </si>
+  <si>
+    <t>Stationary uncovered pound nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=f94b5577-2827-45d8-8636-c5d6f7ba1926</t>
+  </si>
+  <si>
+    <t>FYK</t>
+  </si>
+  <si>
+    <t>Fyke nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=0a9f8e7e-9103-4e10-9feb-cc1ebf270996</t>
+  </si>
+  <si>
+    <t>OTM</t>
+  </si>
+  <si>
+    <t>Midwater otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=4a7fcf3a-7bc2-4bcc-aa17-c5404761f48c</t>
+  </si>
+  <si>
+    <t>SDN</t>
+  </si>
+  <si>
+    <t>Anchored seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=9eded55c-2735-4d92-b9c5-97e7906b7de8</t>
+  </si>
+  <si>
+    <t>OTT</t>
+  </si>
+  <si>
+    <t>Milti-rig otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=15d29f27-abbf-468c-8964-a481ea2958f3</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>Driftnet</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=2c822a11-cd1c-4dec-b693-2b01a19871f7</t>
+  </si>
+  <si>
+    <t>GTN</t>
+  </si>
+  <si>
+    <t>Gillnets-trammel nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=6f3c7b15-f8c1-4349-93d2-46a52a965beb</t>
+  </si>
+  <si>
+    <t>LTL</t>
+  </si>
+  <si>
+    <t>Trolling lines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=8a4cbe19-220e-46c9-b59b-28719b32c3de</t>
+  </si>
+  <si>
+    <t>PTB</t>
+  </si>
+  <si>
+    <t>Bottom pair trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=2d47bbb8-5ff8-4ae5-b94d-d151fc7ef509</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>Beam trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=023236fc-b701-40b1-90d5-4d09ff60764c</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>Fly shooting seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=eb47154a-85a4-470a-afab-283eb769a5ec</t>
+  </si>
+  <si>
+    <t>DRB</t>
+  </si>
+  <si>
+    <t>Boat dredge</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=6028000e-4925-4313-90ef-1ab2461d8234</t>
+  </si>
+  <si>
+    <t>LHM</t>
+  </si>
+  <si>
+    <t>Hand and pole lines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=30d806c1-550a-4d44-9e5d-e7887407e068</t>
   </si>
 </sst>
 </file>
@@ -4624,7 +4822,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4650,6 +4848,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4955,7 +5156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
-  <dimension ref="A1:C293"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.36328125" bestFit="1" customWidth="1"/>
@@ -5021,3179 +5222,3421 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>64</v>
+      <c r="A6" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>17</v>
+      <c r="A11" s="13" t="s">
+        <v>959</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>960</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>961</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>62</v>
+      <c r="A12" s="13" t="s">
+        <v>953</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>954</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>55</v>
+      <c r="A13" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>963</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>59</v>
+      <c r="A14" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>975</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>59</v>
+      <c r="A15" s="13" t="s">
+        <v>947</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>57</v>
+      <c r="A16" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>978</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>56</v>
+      <c r="A17" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>933</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
+        <v>956</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>957</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>935</v>
+      </c>
+      <c r="B22" t="s">
+        <v>936</v>
+      </c>
+      <c r="C22" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>950</v>
+      </c>
+      <c r="B23" t="s">
+        <v>951</v>
+      </c>
+      <c r="C23" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>980</v>
+      </c>
+      <c r="B25" t="s">
+        <v>981</v>
+      </c>
+      <c r="C25" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="14" t="s">
+        <v>931</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>938</v>
+      </c>
+      <c r="B31" t="s">
+        <v>939</v>
+      </c>
+      <c r="C31" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>965</v>
+      </c>
+      <c r="B32" t="s">
+        <v>966</v>
+      </c>
+      <c r="C32" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>971</v>
+      </c>
+      <c r="B33" t="s">
+        <v>972</v>
+      </c>
+      <c r="C33" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>941</v>
+      </c>
+      <c r="B34" t="s">
+        <v>942</v>
+      </c>
+      <c r="C34" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>983</v>
+      </c>
+      <c r="B35" t="s">
+        <v>984</v>
+      </c>
+      <c r="C35" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>944</v>
+      </c>
+      <c r="B36" t="s">
+        <v>945</v>
+      </c>
+      <c r="C36" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>968</v>
+      </c>
+      <c r="B37" t="s">
+        <v>969</v>
+      </c>
+      <c r="C37" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>989</v>
+      </c>
+      <c r="B38" t="s">
+        <v>990</v>
+      </c>
+      <c r="C38" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>986</v>
+      </c>
+      <c r="B40" t="s">
+        <v>987</v>
+      </c>
+      <c r="C40" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B41" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C41" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B42" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C42" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B43" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C43" s="15" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>182</v>
+        <v>115</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>221</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>223</v>
+        <v>157</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>262</v>
+        <v>196</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>269</v>
+        <v>203</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>278</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>281</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
-        <v>282</v>
+        <v>216</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>283</v>
+        <v>217</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>284</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>287</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
-        <v>288</v>
+        <v>222</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>290</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>293</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>295</v>
+        <v>229</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>296</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>299</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
-        <v>300</v>
+        <v>234</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>302</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
-        <v>303</v>
+        <v>237</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>304</v>
+        <v>238</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>305</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
-        <v>306</v>
+        <v>240</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>307</v>
+        <v>241</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>308</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
-        <v>309</v>
+        <v>243</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>311</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
-        <v>312</v>
+        <v>246</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>313</v>
+        <v>247</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>314</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
-        <v>315</v>
+        <v>249</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
-        <v>318</v>
+        <v>252</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>319</v>
+        <v>253</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>320</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>323</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>325</v>
+        <v>259</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>326</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
-        <v>327</v>
+        <v>261</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>328</v>
+        <v>262</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>329</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
-        <v>330</v>
+        <v>264</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>331</v>
+        <v>265</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>332</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
-        <v>333</v>
+        <v>267</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>334</v>
+        <v>268</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>335</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>338</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
-        <v>339</v>
+        <v>273</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>341</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
-        <v>342</v>
+        <v>276</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>343</v>
+        <v>277</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>344</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
-        <v>345</v>
+        <v>279</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>346</v>
+        <v>280</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>350</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>353</v>
+        <v>287</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>359</v>
+        <v>293</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>361</v>
+        <v>295</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>362</v>
+        <v>296</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
-        <v>363</v>
+        <v>297</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>365</v>
+        <v>299</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
-        <v>366</v>
+        <v>300</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>367</v>
+        <v>301</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>368</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
-        <v>369</v>
+        <v>303</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>374</v>
+        <v>308</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="10" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>377</v>
+        <v>311</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>379</v>
+        <v>313</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>380</v>
+        <v>314</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
-        <v>381</v>
+        <v>315</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>382</v>
+        <v>316</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>383</v>
+        <v>317</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>385</v>
+        <v>319</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>386</v>
+        <v>320</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
-        <v>387</v>
+        <v>321</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>388</v>
+        <v>322</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>389</v>
+        <v>323</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>390</v>
+        <v>324</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>391</v>
+        <v>325</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>392</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>393</v>
+        <v>327</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>395</v>
+        <v>329</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>397</v>
+        <v>331</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>398</v>
+        <v>332</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
-        <v>399</v>
+        <v>333</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>400</v>
+        <v>334</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>401</v>
+        <v>335</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>403</v>
+        <v>337</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>407</v>
+        <v>341</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>410</v>
+        <v>344</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="10" t="s">
-        <v>411</v>
+        <v>345</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>412</v>
+        <v>346</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>418</v>
+        <v>352</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>419</v>
+        <v>353</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
-        <v>420</v>
+        <v>354</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>421</v>
+        <v>355</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>422</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>424</v>
+        <v>358</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>425</v>
+        <v>359</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="10" t="s">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>430</v>
+        <v>364</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>431</v>
+        <v>365</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>433</v>
+        <v>367</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>434</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="10" t="s">
-        <v>435</v>
+        <v>369</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>436</v>
+        <v>370</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>437</v>
+        <v>371</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>439</v>
+        <v>373</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>440</v>
+        <v>374</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>443</v>
+        <v>377</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
-        <v>444</v>
+        <v>378</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>446</v>
+        <v>380</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>448</v>
+        <v>382</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>449</v>
+        <v>383</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>452</v>
+        <v>386</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
-        <v>453</v>
+        <v>387</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>455</v>
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
-        <v>456</v>
+        <v>390</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>457</v>
+        <v>391</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>458</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>461</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
-        <v>462</v>
+        <v>396</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>463</v>
+        <v>397</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="10" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>467</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>470</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="10" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
-        <v>474</v>
+        <v>408</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>476</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="10" t="s">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>479</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>482</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="10" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>484</v>
+        <v>418</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>485</v>
+        <v>419</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
-        <v>486</v>
+        <v>420</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="10" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>494</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="10" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>497</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
-        <v>498</v>
+        <v>432</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>499</v>
+        <v>433</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>500</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="10" t="s">
-        <v>501</v>
+        <v>435</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>502</v>
+        <v>436</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>503</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
-        <v>504</v>
+        <v>438</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>505</v>
+        <v>439</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>506</v>
+        <v>440</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="10" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>508</v>
+        <v>442</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>509</v>
+        <v>443</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
-        <v>510</v>
+        <v>444</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>511</v>
+        <v>445</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>512</v>
+        <v>446</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
-        <v>513</v>
+        <v>447</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>514</v>
+        <v>448</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>515</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>518</v>
+        <v>452</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>524</v>
+        <v>458</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="10" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>526</v>
+        <v>460</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>527</v>
+        <v>461</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>530</v>
+        <v>464</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="10" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="10" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
-        <v>540</v>
+        <v>474</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>541</v>
+        <v>475</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>542</v>
+        <v>476</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
-        <v>543</v>
+        <v>477</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>544</v>
+        <v>478</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
-        <v>546</v>
+        <v>480</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>547</v>
+        <v>481</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>548</v>
+        <v>482</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
-        <v>549</v>
+        <v>483</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>550</v>
+        <v>484</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>551</v>
+        <v>485</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
-        <v>552</v>
+        <v>486</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>554</v>
+        <v>488</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>556</v>
+        <v>490</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>557</v>
+        <v>491</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
-        <v>558</v>
+        <v>492</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>559</v>
+        <v>493</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>560</v>
+        <v>494</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
-        <v>561</v>
+        <v>495</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>562</v>
+        <v>496</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>563</v>
+        <v>497</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
-        <v>564</v>
+        <v>498</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>565</v>
+        <v>499</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>566</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
-        <v>567</v>
+        <v>501</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>569</v>
+        <v>503</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>571</v>
+        <v>505</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>572</v>
+        <v>506</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>574</v>
+        <v>508</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
-        <v>576</v>
+        <v>510</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>577</v>
+        <v>511</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>578</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="10" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>580</v>
+        <v>514</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>581</v>
+        <v>515</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
-        <v>582</v>
+        <v>516</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>584</v>
+        <v>518</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="10" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>589</v>
+        <v>523</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>590</v>
+        <v>524</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="10" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>592</v>
+        <v>526</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>593</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
-        <v>594</v>
+        <v>528</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>595</v>
+        <v>529</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>596</v>
+        <v>530</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>598</v>
+        <v>532</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>599</v>
+        <v>533</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
-        <v>600</v>
+        <v>534</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>601</v>
+        <v>535</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>602</v>
+        <v>536</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>604</v>
+        <v>538</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>605</v>
+        <v>539</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
-        <v>606</v>
+        <v>540</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>607</v>
+        <v>541</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>608</v>
+        <v>542</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>610</v>
+        <v>544</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>611</v>
+        <v>545</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
-        <v>612</v>
+        <v>546</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="10" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>617</v>
+        <v>551</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>619</v>
+        <v>553</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>620</v>
+        <v>554</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
-        <v>621</v>
+        <v>555</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>622</v>
+        <v>556</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>623</v>
+        <v>557</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
-        <v>624</v>
+        <v>558</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>625</v>
+        <v>559</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>626</v>
+        <v>560</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>629</v>
+        <v>563</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
-        <v>630</v>
+        <v>564</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>631</v>
+        <v>565</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>632</v>
+        <v>566</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="10" t="s">
-        <v>633</v>
+        <v>567</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>634</v>
+        <v>568</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>635</v>
+        <v>569</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
-        <v>636</v>
+        <v>570</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>637</v>
+        <v>571</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>638</v>
+        <v>572</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="10" t="s">
-        <v>639</v>
+        <v>573</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>640</v>
+        <v>574</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>641</v>
+        <v>575</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>643</v>
+        <v>577</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>644</v>
+        <v>578</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
-        <v>645</v>
+        <v>579</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>646</v>
+        <v>580</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>647</v>
+        <v>581</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>650</v>
+        <v>584</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>652</v>
+        <v>586</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>653</v>
+        <v>587</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
-        <v>654</v>
+        <v>588</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>655</v>
+        <v>589</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>656</v>
+        <v>590</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
-        <v>657</v>
+        <v>591</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>658</v>
+        <v>592</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>659</v>
+        <v>593</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
-        <v>660</v>
+        <v>594</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>661</v>
+        <v>595</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>662</v>
+        <v>596</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>664</v>
+        <v>598</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>665</v>
+        <v>599</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>667</v>
+        <v>601</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>668</v>
+        <v>602</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>671</v>
+        <v>605</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
-        <v>672</v>
+        <v>606</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>673</v>
+        <v>607</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>674</v>
+        <v>608</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>677</v>
+        <v>611</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>680</v>
+        <v>614</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
-        <v>681</v>
+        <v>615</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>682</v>
+        <v>616</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>683</v>
+        <v>617</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>686</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>688</v>
+        <v>622</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>691</v>
+        <v>625</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>692</v>
+        <v>626</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>694</v>
+        <v>628</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>695</v>
+        <v>629</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>697</v>
+        <v>631</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>698</v>
+        <v>632</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
-        <v>699</v>
+        <v>633</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>700</v>
+        <v>634</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>701</v>
+        <v>635</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
-        <v>702</v>
+        <v>636</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>703</v>
+        <v>637</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>704</v>
+        <v>638</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>706</v>
+        <v>640</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>707</v>
+        <v>641</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
-        <v>708</v>
+        <v>642</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>709</v>
+        <v>643</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>710</v>
+        <v>644</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
-        <v>711</v>
+        <v>645</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>712</v>
+        <v>646</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>713</v>
+        <v>647</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
-        <v>714</v>
+        <v>648</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>715</v>
+        <v>649</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>716</v>
+        <v>650</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
-        <v>717</v>
+        <v>651</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>718</v>
+        <v>652</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>719</v>
+        <v>653</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>721</v>
+        <v>655</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>722</v>
+        <v>656</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="10" t="s">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>724</v>
+        <v>658</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>725</v>
+        <v>659</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="10" t="s">
-        <v>726</v>
+        <v>660</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>727</v>
+        <v>661</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>728</v>
+        <v>662</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="10" t="s">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>730</v>
+        <v>664</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>731</v>
+        <v>665</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="10" t="s">
-        <v>732</v>
+        <v>666</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>733</v>
+        <v>667</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>734</v>
+        <v>668</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
-        <v>735</v>
+        <v>669</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>736</v>
+        <v>670</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>737</v>
+        <v>671</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
-        <v>738</v>
+        <v>672</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>739</v>
+        <v>673</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>740</v>
+        <v>674</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
-        <v>741</v>
+        <v>675</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>742</v>
+        <v>676</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>743</v>
+        <v>677</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
-        <v>744</v>
+        <v>678</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>746</v>
+        <v>680</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
-        <v>747</v>
+        <v>681</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>748</v>
+        <v>682</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>749</v>
+        <v>683</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
-        <v>750</v>
+        <v>684</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>751</v>
+        <v>685</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>752</v>
+        <v>686</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
-        <v>753</v>
+        <v>687</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>754</v>
+        <v>688</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>755</v>
+        <v>689</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
-        <v>756</v>
+        <v>690</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>757</v>
+        <v>691</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>758</v>
+        <v>692</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
-        <v>759</v>
+        <v>693</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>760</v>
+        <v>694</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>761</v>
+        <v>695</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
-        <v>762</v>
+        <v>696</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>763</v>
+        <v>697</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>764</v>
+        <v>698</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="10" t="s">
-        <v>765</v>
+        <v>699</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>766</v>
+        <v>700</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>767</v>
+        <v>701</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="10" t="s">
-        <v>768</v>
+        <v>702</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>769</v>
+        <v>703</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>770</v>
+        <v>704</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="10" t="s">
-        <v>771</v>
+        <v>705</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>772</v>
+        <v>706</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>773</v>
+        <v>707</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="10" t="s">
-        <v>774</v>
+        <v>708</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>775</v>
+        <v>709</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>776</v>
+        <v>710</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="10" t="s">
-        <v>777</v>
+        <v>711</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>778</v>
+        <v>712</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>779</v>
+        <v>713</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="10" t="s">
-        <v>780</v>
+        <v>714</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>781</v>
+        <v>715</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>782</v>
+        <v>716</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" s="10" t="s">
-        <v>783</v>
+        <v>717</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>784</v>
+        <v>718</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>785</v>
+        <v>719</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="10" t="s">
-        <v>786</v>
+        <v>720</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>787</v>
+        <v>721</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>788</v>
+        <v>722</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="10" t="s">
-        <v>789</v>
+        <v>723</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>790</v>
+        <v>724</v>
       </c>
       <c r="C263" s="10" t="s">
-        <v>791</v>
+        <v>725</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
-        <v>792</v>
+        <v>726</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>793</v>
+        <v>727</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>794</v>
+        <v>728</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="10" t="s">
-        <v>795</v>
+        <v>729</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>796</v>
+        <v>730</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>797</v>
+        <v>731</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="10" t="s">
-        <v>798</v>
+        <v>732</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>799</v>
+        <v>733</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>800</v>
+        <v>734</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="10" t="s">
-        <v>801</v>
+        <v>735</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>802</v>
+        <v>736</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>803</v>
+        <v>737</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="10" t="s">
-        <v>804</v>
+        <v>738</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>805</v>
+        <v>739</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>806</v>
+        <v>740</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="10" t="s">
-        <v>807</v>
+        <v>741</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>808</v>
+        <v>742</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>809</v>
+        <v>743</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="10" t="s">
-        <v>810</v>
+        <v>744</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>811</v>
+        <v>745</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>812</v>
+        <v>746</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="10" t="s">
-        <v>813</v>
+        <v>747</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>814</v>
+        <v>748</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>815</v>
+        <v>749</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="10" t="s">
-        <v>816</v>
+        <v>750</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>817</v>
+        <v>751</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>818</v>
+        <v>752</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="10" t="s">
-        <v>819</v>
+        <v>753</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>820</v>
+        <v>754</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>821</v>
+        <v>755</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="10" t="s">
-        <v>822</v>
+        <v>756</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>823</v>
+        <v>757</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>824</v>
+        <v>758</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="10" t="s">
-        <v>825</v>
+        <v>759</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>826</v>
+        <v>760</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>827</v>
+        <v>761</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="10" t="s">
-        <v>828</v>
+        <v>762</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>829</v>
+        <v>763</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>830</v>
+        <v>764</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="10" t="s">
-        <v>831</v>
+        <v>765</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>832</v>
+        <v>766</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>833</v>
+        <v>767</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="10" t="s">
-        <v>834</v>
+        <v>768</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>835</v>
+        <v>769</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>836</v>
+        <v>770</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="10" t="s">
-        <v>837</v>
+        <v>771</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>838</v>
+        <v>772</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>839</v>
+        <v>773</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="10" t="s">
-        <v>840</v>
+        <v>774</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>841</v>
+        <v>775</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>842</v>
+        <v>776</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="10" t="s">
-        <v>843</v>
+        <v>777</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>844</v>
+        <v>778</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>845</v>
+        <v>779</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="10" t="s">
-        <v>846</v>
+        <v>780</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>847</v>
+        <v>781</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>848</v>
+        <v>782</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="10" t="s">
-        <v>849</v>
+        <v>783</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>850</v>
+        <v>784</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>851</v>
+        <v>785</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="10" t="s">
-        <v>852</v>
+        <v>786</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>853</v>
+        <v>787</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>854</v>
+        <v>788</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="10" t="s">
-        <v>855</v>
+        <v>789</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>856</v>
+        <v>790</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>857</v>
+        <v>791</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="10" t="s">
-        <v>858</v>
+        <v>792</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>859</v>
+        <v>793</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>860</v>
+        <v>794</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="10" t="s">
-        <v>861</v>
+        <v>795</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>862</v>
+        <v>796</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>863</v>
+        <v>797</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="10" t="s">
-        <v>864</v>
+        <v>798</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>865</v>
+        <v>799</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>866</v>
+        <v>800</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="10" t="s">
-        <v>867</v>
+        <v>801</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>868</v>
+        <v>802</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>869</v>
+        <v>803</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="10" t="s">
-        <v>870</v>
+        <v>804</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>871</v>
+        <v>805</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>872</v>
+        <v>806</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="10" t="s">
-        <v>873</v>
+        <v>807</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>874</v>
+        <v>808</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>875</v>
+        <v>809</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="10" t="s">
-        <v>876</v>
+        <v>810</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>877</v>
+        <v>811</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>878</v>
+        <v>812</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="B293" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C293" s="10" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="B294" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="C294" s="10" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="C295" s="10" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="B296" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="C296" s="10" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="B297" s="10" t="s">
+        <v>826</v>
+      </c>
+      <c r="C297" s="10" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298" s="10" t="s">
+        <v>828</v>
+      </c>
+      <c r="B298" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C298" s="10" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="B299" s="10" t="s">
+        <v>832</v>
+      </c>
+      <c r="C299" s="10" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300" s="10" t="s">
+        <v>834</v>
+      </c>
+      <c r="B300" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="C300" s="10" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="B301" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="C301" s="10" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="B302" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="B303" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="C303" s="10" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="B304" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="C304" s="10" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="B305" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="C305" s="10" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="B306" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="C306" s="10" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="B307" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="C307" s="10" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="C308" s="10" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B309" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="C309" s="10" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B310" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="C310" s="10" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B311" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="C311" s="10" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="B313" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="C313" s="10" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="B314" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="C314" s="10" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" s="10" t="s">
         <v>879</v>
       </c>
-      <c r="B293" s="10" t="s">
+      <c r="B315" s="10" t="s">
         <v>880</v>
       </c>
-      <c r="C293" s="10" t="s">
+      <c r="C315" s="10" t="s">
         <v>881</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C21">
-    <sortCondition ref="A2:A21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C43">
+    <sortCondition ref="A43"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C38" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
+    <hyperlink ref="C60" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB79382-A264-43B9-A758-916E8373434A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AFCFF6-EC9A-4DDE-BDB7-11F2F00078F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="826" firstSheet="30" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="997">
   <si>
     <t>section</t>
   </si>
@@ -4519,6 +4519,204 @@
 &lt;p&gt;
 Average annual (2021–2024) surface (left panel) and subsurface (right panel) disturbance by mobile
 bottom-contacting fishing gear (bottom otter trawls, bottom seines, dredges, and beam trawls) in the ecoregion, expressed as average swept-area ratios (SAR). In the legend, “n” gives the number of c-squares attributed to that level. The data is aggregated to ensure vessel anonymity.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>DRB</t>
+  </si>
+  <si>
+    <t>Boat dredge</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=6028000e-4925-4313-90ef-1ab2461d8234</t>
+  </si>
+  <si>
+    <t>FPN</t>
+  </si>
+  <si>
+    <t>Stationary uncovered pound nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=f94b5577-2827-45d8-8636-c5d6f7ba1926</t>
+  </si>
+  <si>
+    <t>FPO</t>
+  </si>
+  <si>
+    <t>Pots and traps</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=fe1fbee6-5d67-439f-aabf-ca13c48a7d62</t>
+  </si>
+  <si>
+    <t>FYK</t>
+  </si>
+  <si>
+    <t>Fyke nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=0a9f8e7e-9103-4e10-9feb-cc1ebf270996</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>Driftnet</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=2c822a11-cd1c-4dec-b693-2b01a19871f7</t>
+  </si>
+  <si>
+    <t>GNS</t>
+  </si>
+  <si>
+    <t>Set gillnet</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=55f84dad-e861-4d12-8582-b0fe00d99633</t>
+  </si>
+  <si>
+    <t>GTN</t>
+  </si>
+  <si>
+    <t>Gillnets-trammel nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=6f3c7b15-f8c1-4349-93d2-46a52a965beb</t>
+  </si>
+  <si>
+    <t>GTR</t>
+  </si>
+  <si>
+    <t>Trammel nets</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=45a8983a-2a25-4959-a5aa-eb15816ddfe0</t>
+  </si>
+  <si>
+    <t>LHM</t>
+  </si>
+  <si>
+    <t>Hand and pole lines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=30d806c1-550a-4d44-9e5d-e7887407e068</t>
+  </si>
+  <si>
+    <t>LHP</t>
+  </si>
+  <si>
+    <t>Hand and pole lines (hand-operated)</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=3e577955-36e8-41af-aef8-3c3e57b55327</t>
+  </si>
+  <si>
+    <t>LLD</t>
+  </si>
+  <si>
+    <t>Drifting longlines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=327a2e44-ed48-44b0-900d-a07b4ac6e0fb</t>
+  </si>
+  <si>
+    <t>LLS</t>
+  </si>
+  <si>
+    <t>Set longlines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=940eecd0-d03c-444c-b388-e01d0b72ac03</t>
+  </si>
+  <si>
+    <t>LTL</t>
+  </si>
+  <si>
+    <t>Trolling lines</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=8a4cbe19-220e-46c9-b59b-28719b32c3de</t>
+  </si>
+  <si>
+    <t>OTB</t>
+  </si>
+  <si>
+    <t>Bottom otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=573c31dc-b343-42c2-9697-c9a20cfc6be0</t>
+  </si>
+  <si>
+    <t>OTM</t>
+  </si>
+  <si>
+    <t>Midwater otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=4a7fcf3a-7bc2-4bcc-aa17-c5404761f48c</t>
+  </si>
+  <si>
+    <t>OTT</t>
+  </si>
+  <si>
+    <t>Milti-rig otter trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=15d29f27-abbf-468c-8964-a481ea2958f3</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>Purse seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=68ca65b7-3374-4fec-8bdd-8a3ccd36d7a4</t>
+  </si>
+  <si>
+    <t>PTB</t>
+  </si>
+  <si>
+    <t>Bottom pair trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=2d47bbb8-5ff8-4ae5-b94d-d151fc7ef509</t>
+  </si>
+  <si>
+    <t>PTM</t>
+  </si>
+  <si>
+    <t>Pelagic pair trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=8ce860fd-b3ea-4361-ad13-44a9f8535731</t>
+  </si>
+  <si>
+    <t>SDN</t>
+  </si>
+  <si>
+    <t>Anchored seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=9eded55c-2735-4d92-b9c5-97e7906b7de8</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>Fly shooting seine</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=eb47154a-85a4-470a-afab-283eb769a5ec</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>Beam trawl</t>
+  </si>
+  <si>
+    <t>https://vocab.ices.dk/?codeguid=023236fc-b701-40b1-90d5-4d09ff60764c</t>
   </si>
 </sst>
 </file>
@@ -4621,7 +4819,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4647,6 +4845,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4952,17 +5153,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
-  <dimension ref="A1:C292"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C314"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.6328125" customWidth="1"/>
-    <col min="17" max="17" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.6640625" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -4973,7 +5174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -4984,7 +5185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
@@ -4995,7 +5196,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -5006,7 +5207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -5017,3169 +5218,3411 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>931</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>934</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>935</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>937</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>940</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>941</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>943</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>944</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>947</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>949</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>952</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>953</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>955</v>
+      </c>
+      <c r="B20" t="s">
+        <v>956</v>
+      </c>
+      <c r="C20" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>958</v>
+      </c>
+      <c r="B21" t="s">
+        <v>959</v>
+      </c>
+      <c r="C21" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>961</v>
+      </c>
+      <c r="B22" t="s">
+        <v>962</v>
+      </c>
+      <c r="C22" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>964</v>
+      </c>
+      <c r="B23" t="s">
+        <v>965</v>
+      </c>
+      <c r="C23" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B24" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C24" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>967</v>
+      </c>
+      <c r="B25" t="s">
+        <v>968</v>
+      </c>
+      <c r="C25" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B26" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C26" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B27" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C27" s="15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B28" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C28" s="15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B29" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C29" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>970</v>
+      </c>
+      <c r="B30" t="s">
+        <v>971</v>
+      </c>
+      <c r="C30" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>973</v>
+      </c>
+      <c r="B31" t="s">
+        <v>974</v>
+      </c>
+      <c r="C31" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>976</v>
+      </c>
+      <c r="B32" t="s">
+        <v>977</v>
+      </c>
+      <c r="C32" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>979</v>
+      </c>
+      <c r="B33" t="s">
+        <v>980</v>
+      </c>
+      <c r="C33" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>982</v>
+      </c>
+      <c r="B34" t="s">
+        <v>983</v>
+      </c>
+      <c r="C34" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>985</v>
+      </c>
+      <c r="B35" t="s">
+        <v>986</v>
+      </c>
+      <c r="C35" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>988</v>
+      </c>
+      <c r="B36" t="s">
+        <v>989</v>
+      </c>
+      <c r="C36" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>991</v>
+      </c>
+      <c r="B37" t="s">
+        <v>992</v>
+      </c>
+      <c r="C37" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B38" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C38" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>994</v>
+      </c>
+      <c r="B39" t="s">
+        <v>995</v>
+      </c>
+      <c r="C39" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B40" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C40" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B41" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C41" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B42" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C42" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B43" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C43" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B45" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C45" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B46" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C46" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C48" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B49" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C49" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C50" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C51" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B52" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C52" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B53" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C53" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C54" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C55" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="10" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B56" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C56" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C57" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="10" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B58" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C58" s="10" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B60" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C60" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="10" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B61" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C61" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="10" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B62" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C62" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="10" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B63" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C63" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B64" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C64" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="10" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B65" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C65" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B66" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C66" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="10" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B67" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C67" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="10" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B68" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C68" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B69" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C69" s="10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="10" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B70" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C70" s="10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="10" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B71" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C71" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="10" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B72" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C72" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="10" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B73" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C73" s="10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="10" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B74" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C74" s="10" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="10" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B75" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C75" s="10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="10" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B76" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C76" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="10" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B77" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C77" s="10" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="10" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B78" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C78" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="10" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B79" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C79" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="10" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B80" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C80" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="10" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B81" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C81" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="10" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B82" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C82" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="10" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B83" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C83" s="10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="10" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B84" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C84" s="10" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="10" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B85" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C85" s="10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="10" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B86" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C86" s="10" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="10" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B87" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C87" s="10" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="10" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B88" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C88" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="10" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B89" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C89" s="10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="10" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B90" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C90" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="10" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B91" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="10" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B92" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C92" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="10" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B93" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C93" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="10" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B94" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C94" s="10" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="10" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B95" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C95" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="10" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B96" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C96" s="10" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="10" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B97" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C97" s="10" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="10" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B98" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C98" s="10" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="10" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B99" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C99" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="10" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B100" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C100" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="10" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B101" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C101" s="10" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="10" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B102" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C102" s="10" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="10" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B103" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C103" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="10" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B104" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C104" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="10" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B105" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C105" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="10" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B106" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C106" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="10" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B107" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C107" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="10" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B108" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C108" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="10" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B109" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C109" s="10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="10" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B110" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C110" s="10" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="10" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B111" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C111" s="10" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="10" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B112" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C112" s="10" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="10" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B113" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C113" s="10" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="10" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B114" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C114" s="10" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="10" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B115" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C115" s="10" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="10" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B116" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C116" s="10" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="10" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B117" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C117" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="10" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B118" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C118" s="10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="10" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B119" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C119" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="10" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B120" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C120" s="10" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="10" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B121" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C121" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="10" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B122" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C122" s="10" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="10" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B123" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C123" s="10" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="10" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B124" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C124" s="10" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="10" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B125" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C125" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="10" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B126" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C126" s="10" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="10" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B127" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C127" s="10" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="10" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B128" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C128" s="10" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="10" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B129" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C129" s="10" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="10" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B130" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C130" s="10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="10" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B131" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C131" s="10" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="10" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B132" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C132" s="10" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="10" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B133" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C133" s="10" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="10" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B134" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C134" s="10" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="10" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B135" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C135" s="10" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="10" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B136" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C136" s="10" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="10" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B137" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="C115" s="10" t="s">
+      <c r="C137" s="10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="10" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B138" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="10" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B139" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C139" s="10" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="10" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B140" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C140" s="10" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="10" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B141" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C141" s="10" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="10" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B142" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C142" s="10" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="10" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B143" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C143" s="10" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="10" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B144" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C144" s="10" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="10" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B145" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C145" s="10" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="10" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B146" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C146" s="10" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="10" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B147" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C147" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="10" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B148" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C148" s="10" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="10" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B149" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C149" s="10" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" s="10" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B150" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C150" s="10" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="10" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B151" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C151" s="10" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="10" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B152" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C152" s="10" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="10" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B131" s="10" t="s">
+      <c r="B153" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="C131" s="10" t="s">
+      <c r="C153" s="10" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" s="10" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B154" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C154" s="10" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="10" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B155" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C155" s="10" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" s="10" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B156" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C156" s="10" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="10" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B157" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="C157" s="10" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" s="10" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B158" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C158" s="10" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="10" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B159" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C159" s="10" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="10" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B160" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C160" s="10" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="10" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B161" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C161" s="10" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="10" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B162" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C162" s="10" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="10" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B163" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="C141" s="10" t="s">
+      <c r="C163" s="10" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="10" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B164" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C164" s="10" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="10" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B165" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C165" s="10" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" s="10" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B166" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C166" s="10" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" s="10" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B167" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C167" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" s="10" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B168" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C168" s="10" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" s="10" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B169" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C169" s="10" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" s="10" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B170" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C170" s="10" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="10" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B171" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C171" s="10" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="10" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B172" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C172" s="10" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151" s="10" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B173" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C173" s="10" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" s="10" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B174" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C174" s="10" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="10" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B153" s="10" t="s">
+      <c r="B175" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C175" s="10" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" s="10" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B176" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C176" s="10" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" s="10" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B177" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C177" s="10" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" s="10" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="B178" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C178" s="10" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" s="10" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B179" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C179" s="10" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" s="10" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B158" s="10" t="s">
+      <c r="B180" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C180" s="10" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" s="10" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="B181" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C181" s="10" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" s="10" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="B182" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C182" s="10" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" s="10" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="B161" s="10" t="s">
+      <c r="B183" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="C161" s="10" t="s">
+      <c r="C183" s="10" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" s="10" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B184" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C184" s="10" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163" s="10" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B185" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C185" s="10" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" s="10" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B186" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C186" s="10" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165" s="10" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B187" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C187" s="10" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" s="10" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B188" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C188" s="10" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" s="10" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B189" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C189" s="10" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" s="10" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B190" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="C168" s="10" t="s">
+      <c r="C190" s="10" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" s="10" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="B169" s="10" t="s">
+      <c r="B191" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C191" s="10" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" s="10" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B170" s="10" t="s">
+      <c r="B192" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C192" s="10" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171" s="10" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="B171" s="10" t="s">
+      <c r="B193" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C193" s="10" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172" s="10" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B194" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C194" s="10" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" s="10" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B195" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C195" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" s="10" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B196" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="C196" s="10" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="10" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B197" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C197" s="10" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="10" t="s">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B176" s="10" t="s">
+      <c r="B198" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C198" s="10" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="10" t="s">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B199" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C199" s="10" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" s="10" t="s">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="B178" s="10" t="s">
+      <c r="B200" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C200" s="10" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="10" t="s">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B201" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="C179" s="10" t="s">
+      <c r="C201" s="10" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" s="10" t="s">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="B180" s="10" t="s">
+      <c r="B202" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C202" s="10" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="10" t="s">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="B181" s="10" t="s">
+      <c r="B203" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C203" s="10" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="10" t="s">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="B204" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="C182" s="10" t="s">
+      <c r="C204" s="10" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="10" t="s">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B205" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C205" s="10" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" s="10" t="s">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B206" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C206" s="10" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" s="10" t="s">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="B185" s="10" t="s">
+      <c r="B207" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C207" s="10" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" s="10" t="s">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="B186" s="10" t="s">
+      <c r="B208" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C208" s="10" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" s="10" t="s">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="B187" s="10" t="s">
+      <c r="B209" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C209" s="10" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" s="10" t="s">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B210" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C210" s="10" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" s="10" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B211" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C211" s="10" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" s="10" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B212" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C212" s="10" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" s="10" t="s">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B213" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="C213" s="10" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" s="10" t="s">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B214" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C214" s="10" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" s="10" t="s">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B215" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C215" s="10" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" s="10" t="s">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B216" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C216" s="10" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" s="10" t="s">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B217" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C217" s="10" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" s="10" t="s">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B218" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C218" s="10" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" s="10" t="s">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B219" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="C197" s="10" t="s">
+      <c r="C219" s="10" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" s="10" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="B198" s="10" t="s">
+      <c r="B220" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C220" s="10" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" s="10" t="s">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="B221" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C221" s="10" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" s="10" t="s">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B222" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C222" s="10" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" s="10" t="s">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="B201" s="10" t="s">
+      <c r="B223" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C223" s="10" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" s="10" t="s">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B224" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C224" s="10" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" s="10" t="s">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B225" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="C203" s="10" t="s">
+      <c r="C225" s="10" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" s="10" t="s">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="B204" s="10" t="s">
+      <c r="B226" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C204" s="10" t="s">
+      <c r="C226" s="10" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" s="10" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B227" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C205" s="10" t="s">
+      <c r="C227" s="10" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="10" t="s">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="B206" s="10" t="s">
+      <c r="B228" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="C206" s="10" t="s">
+      <c r="C228" s="10" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="10" t="s">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="B207" s="10" t="s">
+      <c r="B229" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="C207" s="10" t="s">
+      <c r="C229" s="10" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="10" t="s">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="B208" s="10" t="s">
+      <c r="B230" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="C230" s="10" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209" s="10" t="s">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="B209" s="10" t="s">
+      <c r="B231" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="C209" s="10" t="s">
+      <c r="C231" s="10" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" s="10" t="s">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B232" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C232" s="10" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211" s="10" t="s">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B233" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C233" s="10" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" s="10" t="s">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="B212" s="10" t="s">
+      <c r="B234" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C234" s="10" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A213" s="10" t="s">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B235" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C235" s="10" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" s="10" t="s">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="B214" s="10" t="s">
+      <c r="B236" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="C214" s="10" t="s">
+      <c r="C236" s="10" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215" s="10" t="s">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B237" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="C237" s="10" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" s="10" t="s">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B238" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="C238" s="10" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217" s="10" t="s">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B239" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="C217" s="10" t="s">
+      <c r="C239" s="10" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" s="10" t="s">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B240" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="C218" s="10" t="s">
+      <c r="C240" s="10" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" s="10" t="s">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B241" s="10" t="s">
         <v>661</v>
       </c>
-      <c r="C219" s="10" t="s">
+      <c r="C241" s="10" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" s="10" t="s">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="B220" s="10" t="s">
+      <c r="B242" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="C220" s="10" t="s">
+      <c r="C242" s="10" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221" s="10" t="s">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="B221" s="10" t="s">
+      <c r="B243" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="C243" s="10" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" s="10" t="s">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="B222" s="10" t="s">
+      <c r="B244" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="C222" s="10" t="s">
+      <c r="C244" s="10" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223" s="10" t="s">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B223" s="10" t="s">
+      <c r="B245" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="C223" s="10" t="s">
+      <c r="C245" s="10" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A224" s="10" t="s">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="B224" s="10" t="s">
+      <c r="B246" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="C224" s="10" t="s">
+      <c r="C246" s="10" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A225" s="10" t="s">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="B225" s="10" t="s">
+      <c r="B247" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="C225" s="10" t="s">
+      <c r="C247" s="10" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A226" s="10" t="s">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="B226" s="10" t="s">
+      <c r="B248" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="C226" s="10" t="s">
+      <c r="C248" s="10" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227" s="10" t="s">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="B227" s="10" t="s">
+      <c r="B249" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="C249" s="10" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228" s="10" t="s">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="B228" s="10" t="s">
+      <c r="B250" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="C228" s="10" t="s">
+      <c r="C250" s="10" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229" s="10" t="s">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="B229" s="10" t="s">
+      <c r="B251" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="C229" s="10" t="s">
+      <c r="C251" s="10" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230" s="10" t="s">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B252" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="C230" s="10" t="s">
+      <c r="C252" s="10" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231" s="10" t="s">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B253" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="C231" s="10" t="s">
+      <c r="C253" s="10" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A232" s="10" t="s">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="B232" s="10" t="s">
+      <c r="B254" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="C232" s="10" t="s">
+      <c r="C254" s="10" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233" s="10" t="s">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B255" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="C233" s="10" t="s">
+      <c r="C255" s="10" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A234" s="10" t="s">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="B234" s="10" t="s">
+      <c r="B256" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="C234" s="10" t="s">
+      <c r="C256" s="10" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235" s="10" t="s">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="B235" s="10" t="s">
+      <c r="B257" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="C235" s="10" t="s">
+      <c r="C257" s="10" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A236" s="10" t="s">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="B236" s="10" t="s">
+      <c r="B258" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="C236" s="10" t="s">
+      <c r="C258" s="10" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237" s="10" t="s">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="B237" s="10" t="s">
+      <c r="B259" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="C237" s="10" t="s">
+      <c r="C259" s="10" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A238" s="10" t="s">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="B238" s="10" t="s">
+      <c r="B260" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C238" s="10" t="s">
+      <c r="C260" s="10" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239" s="10" t="s">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="B239" s="10" t="s">
+      <c r="B261" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A240" s="10" t="s">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="B240" s="10" t="s">
+      <c r="B262" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="C240" s="10" t="s">
+      <c r="C262" s="10" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241" s="10" t="s">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="B241" s="10" t="s">
+      <c r="B263" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="C241" s="10" t="s">
+      <c r="C263" s="10" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A242" s="10" t="s">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="B242" s="10" t="s">
+      <c r="B264" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243" s="10" t="s">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="B243" s="10" t="s">
+      <c r="B265" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="C243" s="10" t="s">
+      <c r="C265" s="10" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A244" s="10" t="s">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="B244" s="10" t="s">
+      <c r="B266" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="C244" s="10" t="s">
+      <c r="C266" s="10" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245" s="10" t="s">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="B245" s="10" t="s">
+      <c r="B267" s="10" t="s">
         <v>739</v>
       </c>
-      <c r="C245" s="10" t="s">
+      <c r="C267" s="10" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A246" s="10" t="s">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B268" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="C246" s="10" t="s">
+      <c r="C268" s="10" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247" s="10" t="s">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B247" s="10" t="s">
+      <c r="B269" s="10" t="s">
         <v>745</v>
       </c>
-      <c r="C247" s="10" t="s">
+      <c r="C269" s="10" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A248" s="10" t="s">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="10" t="s">
         <v>747</v>
       </c>
-      <c r="B248" s="10" t="s">
+      <c r="B270" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="C248" s="10" t="s">
+      <c r="C270" s="10" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249" s="10" t="s">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="B249" s="10" t="s">
+      <c r="B271" s="10" t="s">
         <v>751</v>
       </c>
-      <c r="C249" s="10" t="s">
+      <c r="C271" s="10" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A250" s="10" t="s">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="10" t="s">
         <v>753</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B272" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="C250" s="10" t="s">
+      <c r="C272" s="10" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251" s="10" t="s">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="B251" s="10" t="s">
+      <c r="B273" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C251" s="10" t="s">
+      <c r="C273" s="10" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A252" s="10" t="s">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="10" t="s">
         <v>759</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B274" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="C252" s="10" t="s">
+      <c r="C274" s="10" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253" s="10" t="s">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="B253" s="10" t="s">
+      <c r="B275" s="10" t="s">
         <v>763</v>
       </c>
-      <c r="C253" s="10" t="s">
+      <c r="C275" s="10" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A254" s="10" t="s">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="10" t="s">
         <v>765</v>
       </c>
-      <c r="B254" s="10" t="s">
+      <c r="B276" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="C254" s="10" t="s">
+      <c r="C276" s="10" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255" s="10" t="s">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="B255" s="10" t="s">
+      <c r="B277" s="10" t="s">
         <v>769</v>
       </c>
-      <c r="C255" s="10" t="s">
+      <c r="C277" s="10" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A256" s="10" t="s">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="10" t="s">
         <v>771</v>
       </c>
-      <c r="B256" s="10" t="s">
+      <c r="B278" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C256" s="10" t="s">
+      <c r="C278" s="10" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257" s="10" t="s">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="B257" s="10" t="s">
+      <c r="B279" s="10" t="s">
         <v>775</v>
       </c>
-      <c r="C257" s="10" t="s">
+      <c r="C279" s="10" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A258" s="10" t="s">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="B258" s="10" t="s">
+      <c r="B280" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="C258" s="10" t="s">
+      <c r="C280" s="10" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A259" s="10" t="s">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="B259" s="10" t="s">
+      <c r="B281" s="10" t="s">
         <v>781</v>
       </c>
-      <c r="C259" s="10" t="s">
+      <c r="C281" s="10" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A260" s="10" t="s">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="B260" s="10" t="s">
+      <c r="B282" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="C260" s="10" t="s">
+      <c r="C282" s="10" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A261" s="10" t="s">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="B283" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="C261" s="10" t="s">
+      <c r="C283" s="10" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A262" s="10" t="s">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="B262" s="10" t="s">
+      <c r="B284" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="C262" s="10" t="s">
+      <c r="C284" s="10" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A263" s="10" t="s">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="B263" s="10" t="s">
+      <c r="B285" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="C263" s="10" t="s">
+      <c r="C285" s="10" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A264" s="10" t="s">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="B286" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="C286" s="10" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A265" s="10" t="s">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="B265" s="10" t="s">
+      <c r="B287" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="C265" s="10" t="s">
+      <c r="C287" s="10" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A266" s="10" t="s">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="B266" s="10" t="s">
+      <c r="B288" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="C266" s="10" t="s">
+      <c r="C288" s="10" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A267" s="10" t="s">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="B267" s="10" t="s">
+      <c r="B289" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="C267" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A268" s="10" t="s">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="B268" s="10" t="s">
+      <c r="B290" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="C268" s="10" t="s">
+      <c r="C290" s="10" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A269" s="10" t="s">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="B269" s="10" t="s">
+      <c r="B291" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C269" s="10" t="s">
+      <c r="C291" s="10" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A270" s="10" t="s">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="B270" s="10" t="s">
+      <c r="B292" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="C270" s="10" t="s">
+      <c r="C292" s="10" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A271" s="10" t="s">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="10" t="s">
         <v>816</v>
       </c>
-      <c r="B271" s="10" t="s">
+      <c r="B293" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C271" s="10" t="s">
+      <c r="C293" s="10" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A272" s="10" t="s">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="B272" s="10" t="s">
+      <c r="B294" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="C272" s="10" t="s">
+      <c r="C294" s="10" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A273" s="10" t="s">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="10" t="s">
         <v>822</v>
       </c>
-      <c r="B273" s="10" t="s">
+      <c r="B295" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="C273" s="10" t="s">
+      <c r="C295" s="10" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A274" s="10" t="s">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="10" t="s">
         <v>825</v>
       </c>
-      <c r="B274" s="10" t="s">
+      <c r="B296" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C274" s="10" t="s">
+      <c r="C296" s="10" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A275" s="10" t="s">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="B275" s="10" t="s">
+      <c r="B297" s="10" t="s">
         <v>829</v>
       </c>
-      <c r="C275" s="10" t="s">
+      <c r="C297" s="10" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A276" s="10" t="s">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="10" t="s">
         <v>831</v>
       </c>
-      <c r="B276" s="10" t="s">
+      <c r="B298" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C276" s="10" t="s">
+      <c r="C298" s="10" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A277" s="10" t="s">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="B277" s="10" t="s">
+      <c r="B299" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="C277" s="10" t="s">
+      <c r="C299" s="10" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A278" s="10" t="s">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="10" t="s">
         <v>837</v>
       </c>
-      <c r="B278" s="10" t="s">
+      <c r="B300" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C278" s="10" t="s">
+      <c r="C300" s="10" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A279" s="10" t="s">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="B279" s="10" t="s">
+      <c r="B301" s="10" t="s">
         <v>841</v>
       </c>
-      <c r="C279" s="10" t="s">
+      <c r="C301" s="10" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A280" s="10" t="s">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="10" t="s">
         <v>843</v>
       </c>
-      <c r="B280" s="10" t="s">
+      <c r="B302" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="C280" s="10" t="s">
+      <c r="C302" s="10" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A281" s="10" t="s">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B303" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="C281" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A282" s="10" t="s">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="10" t="s">
         <v>849</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B304" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="C282" s="10" t="s">
+      <c r="C304" s="10" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A283" s="10" t="s">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B305" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="C283" s="10" t="s">
+      <c r="C305" s="10" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A284" s="10" t="s">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="10" t="s">
         <v>855</v>
       </c>
-      <c r="B284" s="10" t="s">
+      <c r="B306" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="C284" s="10" t="s">
+      <c r="C306" s="10" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A285" s="10" t="s">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="B307" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="C307" s="10" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A286" s="10" t="s">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="B286" s="10" t="s">
+      <c r="B308" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="C286" s="10" t="s">
+      <c r="C308" s="10" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A287" s="10" t="s">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="B287" s="10" t="s">
+      <c r="B309" s="10" t="s">
         <v>865</v>
       </c>
-      <c r="C287" s="10" t="s">
+      <c r="C309" s="10" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A288" s="10" t="s">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="10" t="s">
         <v>867</v>
       </c>
-      <c r="B288" s="10" t="s">
+      <c r="B310" s="10" t="s">
         <v>868</v>
       </c>
-      <c r="C288" s="10" t="s">
+      <c r="C310" s="10" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A289" s="10" t="s">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="10" t="s">
         <v>870</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="B311" s="10" t="s">
         <v>871</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="C311" s="10" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A290" s="10" t="s">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="10" t="s">
         <v>873</v>
       </c>
-      <c r="B290" s="10" t="s">
+      <c r="B312" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="C290" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A291" s="10" t="s">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="10" t="s">
         <v>876</v>
       </c>
-      <c r="B291" s="10" t="s">
+      <c r="B313" s="10" t="s">
         <v>877</v>
       </c>
-      <c r="C291" s="10" t="s">
+      <c r="C313" s="10" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A292" s="10" t="s">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="10" t="s">
         <v>879</v>
       </c>
-      <c r="B292" s="10" t="s">
+      <c r="B314" s="10" t="s">
         <v>880</v>
       </c>
-      <c r="C292" s="10" t="s">
+      <c r="C314" s="10" t="s">
         <v>881</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
-    <sortCondition ref="A2:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C42">
+    <sortCondition ref="A2:A42"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C37" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
+    <hyperlink ref="C59" r:id="rId1" xr:uid="{22C4024E-F5EE-4C14-B35D-9A99EB6AF0F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8191,13 +8634,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8205,7 +8648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8213,7 +8656,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8221,7 +8664,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8240,13 +8683,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="198.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8254,7 +8697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8262,7 +8705,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8270,7 +8713,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8286,13 +8729,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="229.6328125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="229.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8300,7 +8743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8308,7 +8751,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8316,7 +8759,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8332,13 +8775,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8346,7 +8789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8354,7 +8797,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8370,13 +8813,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8384,7 +8827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8392,7 +8835,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8408,13 +8851,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8422,7 +8865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8430,7 +8873,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8446,13 +8889,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8460,7 +8903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8468,7 +8911,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8484,12 +8927,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="125.54296875" customWidth="1"/>
+    <col min="2" max="2" width="125.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8497,7 +8940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8505,7 +8948,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -8521,13 +8964,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8535,7 +8978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8543,7 +8986,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8559,13 +9002,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8573,7 +9016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8581,7 +9024,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8597,13 +9040,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="152.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="152.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8611,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8619,7 +9062,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8627,7 +9070,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8643,13 +9086,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8657,7 +9100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8665,7 +9108,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8684,13 +9127,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8698,7 +9141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8706,7 +9149,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8722,13 +9165,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8736,7 +9179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8744,7 +9187,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8760,13 +9203,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8774,7 +9217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8782,7 +9225,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8799,13 +9242,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8813,7 +9256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8821,7 +9264,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8829,7 +9272,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8837,7 +9280,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8851,13 +9294,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8865,7 +9308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8873,7 +9316,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8881,7 +9324,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8889,7 +9332,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8902,13 +9345,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8916,7 +9359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8924,7 +9367,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8932,7 +9375,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8940,7 +9383,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -8953,13 +9396,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8967,7 +9410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -8975,7 +9418,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -8983,7 +9426,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -8991,7 +9434,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9007,13 +9450,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9021,7 +9464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9029,7 +9472,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9037,7 +9480,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9045,7 +9488,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9058,13 +9501,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9072,7 +9515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9080,7 +9523,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9088,7 +9531,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9096,7 +9539,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9109,13 +9552,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="253.90625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="253.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9123,7 +9566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9131,7 +9574,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9139,7 +9582,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9155,13 +9598,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9169,7 +9612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9177,7 +9620,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9185,7 +9628,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9193,7 +9636,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9206,13 +9649,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9220,7 +9663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9228,7 +9671,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9236,7 +9679,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9244,7 +9687,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9257,13 +9700,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9271,7 +9714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9279,7 +9722,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9287,7 +9730,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9295,7 +9738,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9308,13 +9751,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9322,7 +9765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9330,7 +9773,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9338,7 +9781,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9346,7 +9789,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9359,13 +9802,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="199.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9373,7 +9816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9381,7 +9824,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9389,7 +9832,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9397,7 +9840,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9413,13 +9856,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9427,7 +9870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9443,13 +9886,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9457,7 +9900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9473,13 +9916,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9487,7 +9930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9503,13 +9946,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9517,7 +9960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9533,13 +9976,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9547,7 +9990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9563,13 +10006,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="223.90625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="223.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9577,7 +10020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9585,7 +10028,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9593,7 +10036,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9609,13 +10052,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9623,7 +10066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9639,13 +10082,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9653,7 +10096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9669,13 +10112,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9683,7 +10126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9699,13 +10142,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9713,7 +10156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9729,13 +10172,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9743,7 +10186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9759,13 +10202,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9773,7 +10216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9792,12 +10235,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9805,7 +10248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9824,13 +10267,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="159.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="159.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9838,7 +10281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9854,13 +10297,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="181.453125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="181.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9868,7 +10311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9876,7 +10319,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9884,7 +10327,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9900,13 +10343,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="222.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="222.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9914,7 +10357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9922,7 +10365,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9930,7 +10373,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9946,13 +10389,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="137.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="137.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9960,7 +10403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9968,7 +10411,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9976,7 +10419,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9984,13 +10427,13 @@
         <v>899</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10001,13 +10444,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="135.54296875" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="135.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10015,7 +10458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10023,7 +10466,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10031,7 +10474,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10047,13 +10490,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="114.90625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="114.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10061,7 +10504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10069,7 +10512,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10077,7 +10520,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarah.weisberg\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AFCFF6-EC9A-4DDE-BDB7-11F2F00078F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC39F11-6744-43EE-8C70-20B31016904C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-50820" yWindow="-4785" windowWidth="40050" windowHeight="15105" tabRatio="858" firstSheet="30" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -59,7 +59,9 @@
     <sheet name="vms_NwS" sheetId="46" r:id="rId44"/>
     <sheet name="vms_ONA" sheetId="47" r:id="rId45"/>
     <sheet name="mixfish" sheetId="5" r:id="rId46"/>
-    <sheet name="bycatch" sheetId="7" r:id="rId47"/>
+    <sheet name="Sheet1" sheetId="48" r:id="rId47"/>
+    <sheet name="bycatch" sheetId="7" r:id="rId48"/>
+    <sheet name="bycatch_AZ" sheetId="49" r:id="rId49"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -82,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="1001">
   <si>
     <t>section</t>
   </si>
@@ -4717,6 +4719,32 @@
   </si>
   <si>
     <t>https://vocab.ices.dk/?codeguid=023236fc-b701-40b1-90d5-4d09ff60764c</t>
+  </si>
+  <si>
+    <t>total_bycatch</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Azores ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine turtles and multiannual bycatch rates for marine mammals and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 2 marine turtle species (3 métier/species combinations). The highest total bycaught number was estimated for loggerhead turtle in set gillnet followed by loggerhead turtle in drifting longlines and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>bpue</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Azores ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine turtles and multiannual bycatch rates for marine mammals and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 2 marine mammal species (3 métier/species combinations). The highest bycatch rate was estimated for Atlantic spotted dolphin in hand and pole lines, followed by common dolphin in hand and pole lines (mechanized) and hand and pole lines. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 3 marine turtle species (4 métier/species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines, followed by loggerhead turtle in set gillnet and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -5154,16 +5182,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.6640625" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -5174,7 +5202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
@@ -5185,7 +5213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
@@ -5196,7 +5224,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -5207,7 +5235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -5218,7 +5246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>931</v>
       </c>
@@ -5229,7 +5257,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>45</v>
       </c>
@@ -5240,7 +5268,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
@@ -5251,7 +5279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
@@ -5262,7 +5290,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
@@ -5273,7 +5301,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>934</v>
       </c>
@@ -5284,7 +5312,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>937</v>
       </c>
@@ -5295,7 +5323,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>940</v>
       </c>
@@ -5306,7 +5334,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>943</v>
       </c>
@@ -5317,7 +5345,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>946</v>
       </c>
@@ -5328,7 +5356,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>949</v>
       </c>
@@ -5339,7 +5367,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>952</v>
       </c>
@@ -5350,7 +5378,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>49</v>
       </c>
@@ -5361,7 +5389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>18</v>
       </c>
@@ -5372,7 +5400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>955</v>
       </c>
@@ -5383,7 +5411,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>958</v>
       </c>
@@ -5394,7 +5422,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>961</v>
       </c>
@@ -5405,7 +5433,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>964</v>
       </c>
@@ -5416,7 +5444,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>41</v>
       </c>
@@ -5427,7 +5455,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>967</v>
       </c>
@@ -5438,7 +5466,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>23</v>
       </c>
@@ -5449,7 +5477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>35</v>
       </c>
@@ -5460,7 +5488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>31</v>
       </c>
@@ -5471,7 +5499,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>27</v>
       </c>
@@ -5482,7 +5510,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>970</v>
       </c>
@@ -5493,7 +5521,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>973</v>
       </c>
@@ -5504,7 +5532,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>976</v>
       </c>
@@ -5515,7 +5543,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>979</v>
       </c>
@@ -5526,7 +5554,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>982</v>
       </c>
@@ -5537,7 +5565,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>985</v>
       </c>
@@ -5548,7 +5576,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>988</v>
       </c>
@@ -5559,7 +5587,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>991</v>
       </c>
@@ -5570,7 +5598,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>39</v>
       </c>
@@ -5581,7 +5609,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>994</v>
       </c>
@@ -5592,7 +5620,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>33</v>
       </c>
@@ -5603,7 +5631,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>37</v>
       </c>
@@ -5614,7 +5642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>47</v>
       </c>
@@ -5625,7 +5653,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>66</v>
       </c>
@@ -5636,7 +5664,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>69</v>
       </c>
@@ -5647,7 +5675,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>72</v>
       </c>
@@ -5658,7 +5686,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>75</v>
       </c>
@@ -5669,7 +5697,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>78</v>
       </c>
@@ -5680,7 +5708,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>81</v>
       </c>
@@ -5691,7 +5719,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>84</v>
       </c>
@@ -5702,7 +5730,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>87</v>
       </c>
@@ -5713,7 +5741,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>90</v>
       </c>
@@ -5724,7 +5752,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>93</v>
       </c>
@@ -5735,7 +5763,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>96</v>
       </c>
@@ -5746,7 +5774,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>99</v>
       </c>
@@ -5757,7 +5785,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>102</v>
       </c>
@@ -5768,7 +5796,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>105</v>
       </c>
@@ -5779,7 +5807,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>108</v>
       </c>
@@ -5790,7 +5818,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>111</v>
       </c>
@@ -5801,7 +5829,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>114</v>
       </c>
@@ -5812,7 +5840,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>117</v>
       </c>
@@ -5823,7 +5851,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>120</v>
       </c>
@@ -5834,7 +5862,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>123</v>
       </c>
@@ -5845,7 +5873,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>126</v>
       </c>
@@ -5856,7 +5884,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>129</v>
       </c>
@@ -5867,7 +5895,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>132</v>
       </c>
@@ -5878,7 +5906,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>135</v>
       </c>
@@ -5889,7 +5917,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>138</v>
       </c>
@@ -5900,7 +5928,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>141</v>
       </c>
@@ -5911,7 +5939,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>144</v>
       </c>
@@ -5922,7 +5950,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>147</v>
       </c>
@@ -5933,7 +5961,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>150</v>
       </c>
@@ -5944,7 +5972,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>153</v>
       </c>
@@ -5955,7 +5983,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>156</v>
       </c>
@@ -5966,7 +5994,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>159</v>
       </c>
@@ -5977,7 +6005,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>162</v>
       </c>
@@ -5988,7 +6016,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>165</v>
       </c>
@@ -5999,7 +6027,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>168</v>
       </c>
@@ -6010,7 +6038,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>171</v>
       </c>
@@ -6021,7 +6049,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>174</v>
       </c>
@@ -6032,7 +6060,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>177</v>
       </c>
@@ -6043,7 +6071,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>180</v>
       </c>
@@ -6054,7 +6082,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>183</v>
       </c>
@@ -6065,7 +6093,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>186</v>
       </c>
@@ -6076,7 +6104,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>189</v>
       </c>
@@ -6087,7 +6115,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>192</v>
       </c>
@@ -6098,7 +6126,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>195</v>
       </c>
@@ -6109,7 +6137,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>198</v>
       </c>
@@ -6120,7 +6148,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>201</v>
       </c>
@@ -6131,7 +6159,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>204</v>
       </c>
@@ -6142,7 +6170,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>207</v>
       </c>
@@ -6153,7 +6181,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>210</v>
       </c>
@@ -6164,7 +6192,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>213</v>
       </c>
@@ -6175,7 +6203,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>216</v>
       </c>
@@ -6186,7 +6214,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>219</v>
       </c>
@@ -6197,7 +6225,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>222</v>
       </c>
@@ -6208,7 +6236,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>225</v>
       </c>
@@ -6219,7 +6247,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>228</v>
       </c>
@@ -6230,7 +6258,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>231</v>
       </c>
@@ -6241,7 +6269,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>234</v>
       </c>
@@ -6252,7 +6280,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>237</v>
       </c>
@@ -6263,7 +6291,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>240</v>
       </c>
@@ -6274,7 +6302,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>243</v>
       </c>
@@ -6285,7 +6313,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>246</v>
       </c>
@@ -6296,7 +6324,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>249</v>
       </c>
@@ -6307,7 +6335,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>252</v>
       </c>
@@ -6318,7 +6346,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>255</v>
       </c>
@@ -6329,7 +6357,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>258</v>
       </c>
@@ -6340,7 +6368,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>261</v>
       </c>
@@ -6351,7 +6379,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>264</v>
       </c>
@@ -6362,7 +6390,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>267</v>
       </c>
@@ -6373,7 +6401,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>270</v>
       </c>
@@ -6384,7 +6412,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
         <v>273</v>
       </c>
@@ -6395,7 +6423,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>276</v>
       </c>
@@ -6406,7 +6434,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>279</v>
       </c>
@@ -6417,7 +6445,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>282</v>
       </c>
@@ -6428,7 +6456,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>285</v>
       </c>
@@ -6439,7 +6467,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>288</v>
       </c>
@@ -6450,7 +6478,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>291</v>
       </c>
@@ -6461,7 +6489,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>294</v>
       </c>
@@ -6472,7 +6500,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>297</v>
       </c>
@@ -6483,7 +6511,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>300</v>
       </c>
@@ -6494,7 +6522,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>303</v>
       </c>
@@ -6505,7 +6533,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>306</v>
       </c>
@@ -6516,7 +6544,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>309</v>
       </c>
@@ -6527,7 +6555,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
         <v>312</v>
       </c>
@@ -6538,7 +6566,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>315</v>
       </c>
@@ -6549,7 +6577,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>318</v>
       </c>
@@ -6560,7 +6588,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>321</v>
       </c>
@@ -6571,7 +6599,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>324</v>
       </c>
@@ -6582,7 +6610,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>327</v>
       </c>
@@ -6593,7 +6621,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>330</v>
       </c>
@@ -6604,7 +6632,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>333</v>
       </c>
@@ -6615,7 +6643,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>336</v>
       </c>
@@ -6626,7 +6654,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>339</v>
       </c>
@@ -6637,7 +6665,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>342</v>
       </c>
@@ -6648,7 +6676,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>345</v>
       </c>
@@ -6659,7 +6687,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
         <v>348</v>
       </c>
@@ -6670,7 +6698,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>351</v>
       </c>
@@ -6681,7 +6709,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>354</v>
       </c>
@@ -6692,7 +6720,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
         <v>357</v>
       </c>
@@ -6703,7 +6731,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
         <v>360</v>
       </c>
@@ -6714,7 +6742,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>363</v>
       </c>
@@ -6725,7 +6753,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
         <v>366</v>
       </c>
@@ -6736,7 +6764,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
         <v>369</v>
       </c>
@@ -6747,7 +6775,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
         <v>372</v>
       </c>
@@ -6758,7 +6786,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
         <v>375</v>
       </c>
@@ -6769,7 +6797,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
         <v>378</v>
       </c>
@@ -6780,7 +6808,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
         <v>381</v>
       </c>
@@ -6791,7 +6819,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
         <v>384</v>
       </c>
@@ -6802,7 +6830,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
         <v>387</v>
       </c>
@@ -6813,7 +6841,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
         <v>390</v>
       </c>
@@ -6824,7 +6852,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
         <v>393</v>
       </c>
@@ -6835,7 +6863,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
         <v>396</v>
       </c>
@@ -6846,7 +6874,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
         <v>399</v>
       </c>
@@ -6857,7 +6885,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>402</v>
       </c>
@@ -6868,7 +6896,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>405</v>
       </c>
@@ -6879,7 +6907,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>408</v>
       </c>
@@ -6890,7 +6918,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
         <v>411</v>
       </c>
@@ -6901,7 +6929,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>414</v>
       </c>
@@ -6912,7 +6940,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
         <v>417</v>
       </c>
@@ -6923,7 +6951,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
         <v>420</v>
       </c>
@@ -6934,7 +6962,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
         <v>423</v>
       </c>
@@ -6945,7 +6973,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
         <v>426</v>
       </c>
@@ -6956,7 +6984,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
         <v>429</v>
       </c>
@@ -6967,7 +6995,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
         <v>432</v>
       </c>
@@ -6978,7 +7006,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
         <v>435</v>
       </c>
@@ -6989,7 +7017,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
         <v>438</v>
       </c>
@@ -7000,7 +7028,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
         <v>441</v>
       </c>
@@ -7011,7 +7039,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
         <v>444</v>
       </c>
@@ -7022,7 +7050,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
         <v>447</v>
       </c>
@@ -7033,7 +7061,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
         <v>450</v>
       </c>
@@ -7044,7 +7072,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
         <v>453</v>
       </c>
@@ -7055,7 +7083,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
         <v>456</v>
       </c>
@@ -7066,7 +7094,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
         <v>459</v>
       </c>
@@ -7077,7 +7105,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
         <v>462</v>
       </c>
@@ -7088,7 +7116,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
         <v>465</v>
       </c>
@@ -7099,7 +7127,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
         <v>468</v>
       </c>
@@ -7110,7 +7138,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>471</v>
       </c>
@@ -7121,7 +7149,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
         <v>474</v>
       </c>
@@ -7132,7 +7160,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
         <v>477</v>
       </c>
@@ -7143,7 +7171,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
         <v>480</v>
       </c>
@@ -7154,7 +7182,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
         <v>483</v>
       </c>
@@ -7165,7 +7193,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
         <v>486</v>
       </c>
@@ -7176,7 +7204,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
         <v>489</v>
       </c>
@@ -7187,7 +7215,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
         <v>492</v>
       </c>
@@ -7198,7 +7226,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
         <v>495</v>
       </c>
@@ -7209,7 +7237,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
         <v>498</v>
       </c>
@@ -7220,7 +7248,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
         <v>501</v>
       </c>
@@ -7231,7 +7259,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
         <v>504</v>
       </c>
@@ -7242,7 +7270,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
         <v>507</v>
       </c>
@@ -7253,7 +7281,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
         <v>510</v>
       </c>
@@ -7264,7 +7292,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
         <v>513</v>
       </c>
@@ -7275,7 +7303,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
         <v>516</v>
       </c>
@@ -7286,7 +7314,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
         <v>519</v>
       </c>
@@ -7297,7 +7325,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
         <v>522</v>
       </c>
@@ -7308,7 +7336,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
         <v>525</v>
       </c>
@@ -7319,7 +7347,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
         <v>528</v>
       </c>
@@ -7330,7 +7358,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
         <v>531</v>
       </c>
@@ -7341,7 +7369,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
         <v>534</v>
       </c>
@@ -7352,7 +7380,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
         <v>537</v>
       </c>
@@ -7363,7 +7391,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
         <v>540</v>
       </c>
@@ -7374,7 +7402,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
         <v>543</v>
       </c>
@@ -7385,7 +7413,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
         <v>546</v>
       </c>
@@ -7396,7 +7424,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>549</v>
       </c>
@@ -7407,7 +7435,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
         <v>552</v>
       </c>
@@ -7418,7 +7446,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
         <v>555</v>
       </c>
@@ -7429,7 +7457,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
         <v>558</v>
       </c>
@@ -7440,7 +7468,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
         <v>561</v>
       </c>
@@ -7451,7 +7479,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
         <v>564</v>
       </c>
@@ -7462,7 +7490,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
         <v>567</v>
       </c>
@@ -7473,7 +7501,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
         <v>570</v>
       </c>
@@ -7484,7 +7512,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
         <v>573</v>
       </c>
@@ -7495,7 +7523,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
         <v>576</v>
       </c>
@@ -7506,7 +7534,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
         <v>579</v>
       </c>
@@ -7517,7 +7545,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
         <v>582</v>
       </c>
@@ -7528,7 +7556,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
         <v>585</v>
       </c>
@@ -7539,7 +7567,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
         <v>588</v>
       </c>
@@ -7550,7 +7578,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
         <v>591</v>
       </c>
@@ -7561,7 +7589,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
         <v>594</v>
       </c>
@@ -7572,7 +7600,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
         <v>597</v>
       </c>
@@ -7583,7 +7611,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
         <v>600</v>
       </c>
@@ -7594,7 +7622,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
         <v>603</v>
       </c>
@@ -7605,7 +7633,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
         <v>606</v>
       </c>
@@ -7616,7 +7644,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
         <v>609</v>
       </c>
@@ -7627,7 +7655,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
         <v>612</v>
       </c>
@@ -7638,7 +7666,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
         <v>615</v>
       </c>
@@ -7649,7 +7677,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
         <v>618</v>
       </c>
@@ -7660,7 +7688,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
         <v>621</v>
       </c>
@@ -7671,7 +7699,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
         <v>624</v>
       </c>
@@ -7682,7 +7710,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
         <v>627</v>
       </c>
@@ -7693,7 +7721,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
         <v>630</v>
       </c>
@@ -7704,7 +7732,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
         <v>633</v>
       </c>
@@ -7715,7 +7743,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
         <v>636</v>
       </c>
@@ -7726,7 +7754,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
         <v>639</v>
       </c>
@@ -7737,7 +7765,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
         <v>642</v>
       </c>
@@ -7748,7 +7776,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
         <v>645</v>
       </c>
@@ -7759,7 +7787,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
         <v>648</v>
       </c>
@@ -7770,7 +7798,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
         <v>651</v>
       </c>
@@ -7781,7 +7809,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
         <v>654</v>
       </c>
@@ -7792,7 +7820,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
         <v>657</v>
       </c>
@@ -7803,7 +7831,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
         <v>660</v>
       </c>
@@ -7814,7 +7842,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
         <v>663</v>
       </c>
@@ -7825,7 +7853,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
         <v>666</v>
       </c>
@@ -7836,7 +7864,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
         <v>669</v>
       </c>
@@ -7847,7 +7875,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
         <v>672</v>
       </c>
@@ -7858,7 +7886,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
         <v>675</v>
       </c>
@@ -7869,7 +7897,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
         <v>678</v>
       </c>
@@ -7880,7 +7908,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
         <v>681</v>
       </c>
@@ -7891,7 +7919,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
         <v>684</v>
       </c>
@@ -7902,7 +7930,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
         <v>687</v>
       </c>
@@ -7913,7 +7941,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
         <v>690</v>
       </c>
@@ -7924,7 +7952,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
         <v>693</v>
       </c>
@@ -7935,7 +7963,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
         <v>696</v>
       </c>
@@ -7946,7 +7974,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
         <v>699</v>
       </c>
@@ -7957,7 +7985,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
         <v>702</v>
       </c>
@@ -7968,7 +7996,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
         <v>705</v>
       </c>
@@ -7979,7 +8007,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
         <v>708</v>
       </c>
@@ -7990,7 +8018,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
         <v>711</v>
       </c>
@@ -8001,7 +8029,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
         <v>714</v>
       </c>
@@ -8012,7 +8040,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
         <v>717</v>
       </c>
@@ -8023,7 +8051,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
         <v>720</v>
       </c>
@@ -8034,7 +8062,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
         <v>723</v>
       </c>
@@ -8045,7 +8073,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
         <v>726</v>
       </c>
@@ -8056,7 +8084,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
         <v>729</v>
       </c>
@@ -8067,7 +8095,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
         <v>732</v>
       </c>
@@ -8078,7 +8106,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
         <v>735</v>
       </c>
@@ -8089,7 +8117,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
         <v>738</v>
       </c>
@@ -8100,7 +8128,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
         <v>741</v>
       </c>
@@ -8111,7 +8139,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
         <v>744</v>
       </c>
@@ -8122,7 +8150,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
         <v>747</v>
       </c>
@@ -8133,7 +8161,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
         <v>750</v>
       </c>
@@ -8144,7 +8172,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
         <v>753</v>
       </c>
@@ -8155,7 +8183,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
         <v>756</v>
       </c>
@@ -8166,7 +8194,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
         <v>759</v>
       </c>
@@ -8177,7 +8205,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
         <v>762</v>
       </c>
@@ -8188,7 +8216,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
         <v>765</v>
       </c>
@@ -8199,7 +8227,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
         <v>768</v>
       </c>
@@ -8210,7 +8238,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
         <v>771</v>
       </c>
@@ -8221,7 +8249,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
         <v>774</v>
       </c>
@@ -8232,7 +8260,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
         <v>777</v>
       </c>
@@ -8243,7 +8271,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
         <v>780</v>
       </c>
@@ -8254,7 +8282,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
         <v>783</v>
       </c>
@@ -8265,7 +8293,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
         <v>786</v>
       </c>
@@ -8276,7 +8304,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
         <v>789</v>
       </c>
@@ -8287,7 +8315,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
         <v>792</v>
       </c>
@@ -8298,7 +8326,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
         <v>795</v>
       </c>
@@ -8309,7 +8337,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
         <v>798</v>
       </c>
@@ -8320,7 +8348,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
         <v>801</v>
       </c>
@@ -8331,7 +8359,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
         <v>804</v>
       </c>
@@ -8342,7 +8370,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
         <v>807</v>
       </c>
@@ -8353,7 +8381,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
         <v>810</v>
       </c>
@@ -8364,7 +8392,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
         <v>813</v>
       </c>
@@ -8375,7 +8403,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
         <v>816</v>
       </c>
@@ -8386,7 +8414,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
         <v>819</v>
       </c>
@@ -8397,7 +8425,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
         <v>822</v>
       </c>
@@ -8408,7 +8436,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
         <v>825</v>
       </c>
@@ -8419,7 +8447,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
         <v>828</v>
       </c>
@@ -8430,7 +8458,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
         <v>831</v>
       </c>
@@ -8441,7 +8469,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
         <v>834</v>
       </c>
@@ -8452,7 +8480,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
         <v>837</v>
       </c>
@@ -8463,7 +8491,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
         <v>840</v>
       </c>
@@ -8474,7 +8502,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
         <v>843</v>
       </c>
@@ -8485,7 +8513,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
         <v>846</v>
       </c>
@@ -8496,7 +8524,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
         <v>849</v>
       </c>
@@ -8507,7 +8535,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
         <v>852</v>
       </c>
@@ -8518,7 +8546,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
         <v>855</v>
       </c>
@@ -8529,7 +8557,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
         <v>858</v>
       </c>
@@ -8540,7 +8568,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
         <v>861</v>
       </c>
@@ -8551,7 +8579,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
         <v>864</v>
       </c>
@@ -8562,7 +8590,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
         <v>867</v>
       </c>
@@ -8573,7 +8601,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
         <v>870</v>
       </c>
@@ -8584,7 +8612,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
         <v>873</v>
       </c>
@@ -8595,7 +8623,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
         <v>876</v>
       </c>
@@ -8606,7 +8634,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
         <v>879</v>
       </c>
@@ -8634,13 +8662,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8648,7 +8676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8656,7 +8684,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8664,7 +8692,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8683,13 +8711,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="198.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8697,7 +8725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8705,7 +8733,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8713,7 +8741,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8729,13 +8757,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="229.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="229.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8743,7 +8771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -8751,7 +8779,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8759,7 +8787,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8775,13 +8803,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8789,7 +8817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8797,7 +8825,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8813,13 +8841,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8827,7 +8855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8835,7 +8863,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8851,13 +8879,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8865,7 +8893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8873,7 +8901,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8889,13 +8917,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8903,7 +8931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8911,7 +8939,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8927,12 +8955,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+    <col min="2" max="2" width="125.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8940,7 +8968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8948,7 +8976,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="330" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -8964,13 +8992,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8978,7 +9006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8986,7 +9014,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9002,13 +9030,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9016,7 +9044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9024,7 +9052,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9040,13 +9068,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="152.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="152.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9054,7 +9082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9062,7 +9090,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9070,7 +9098,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9086,13 +9114,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9100,7 +9128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9108,7 +9136,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9127,13 +9155,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9141,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9149,7 +9177,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9165,13 +9193,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9179,7 +9207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9187,7 +9215,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9203,13 +9231,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9217,7 +9245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9225,7 +9253,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9242,13 +9270,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9256,7 +9284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9264,7 +9292,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9272,7 +9300,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9280,7 +9308,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9294,13 +9322,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9308,7 +9336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9316,7 +9344,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9324,7 +9352,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9332,7 +9360,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9345,13 +9373,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9359,7 +9387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9367,7 +9395,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9375,7 +9403,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9383,7 +9411,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9396,13 +9424,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9410,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9418,7 +9446,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9426,7 +9454,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9434,7 +9462,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9450,13 +9478,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9464,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9472,7 +9500,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9480,7 +9508,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9488,7 +9516,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9501,13 +9529,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9515,7 +9543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9523,7 +9551,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9531,7 +9559,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9539,7 +9567,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9552,13 +9580,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="253.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="253.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9566,7 +9594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -9574,7 +9602,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9582,7 +9610,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9598,13 +9626,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9612,7 +9640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9620,7 +9648,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9628,7 +9656,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9636,7 +9664,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9649,13 +9677,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9663,7 +9691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9671,7 +9699,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9679,7 +9707,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9687,7 +9715,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9700,13 +9728,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9714,7 +9742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9722,7 +9750,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9730,7 +9758,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9738,7 +9766,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9751,13 +9779,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9765,7 +9793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9773,7 +9801,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9781,7 +9809,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9789,7 +9817,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9802,13 +9830,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9816,7 +9844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>884</v>
       </c>
@@ -9824,7 +9852,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>905</v>
       </c>
@@ -9832,7 +9860,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>906</v>
       </c>
@@ -9840,7 +9868,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>907</v>
       </c>
@@ -9856,13 +9884,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9870,7 +9898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9886,13 +9914,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9900,7 +9928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9916,13 +9944,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9930,7 +9958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9946,13 +9974,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9960,7 +9988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -9976,13 +10004,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9990,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10006,13 +10034,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="223.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="223.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10020,7 +10048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10028,7 +10056,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10036,7 +10064,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10052,13 +10080,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10066,7 +10094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10082,13 +10110,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10096,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10112,13 +10140,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10126,7 +10154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10142,13 +10170,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10156,7 +10184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10172,13 +10200,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10186,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10202,13 +10230,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10216,7 +10244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>920</v>
       </c>
@@ -10235,12 +10263,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10248,7 +10276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -10262,18 +10290,27 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E1B14FC-8227-47AA-A858-20FEF7B4AC2B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="159.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="159.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10281,12 +10318,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE61185-CF8B-43DA-9230-D26A514F1564}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -10297,13 +10375,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="181.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10311,7 +10389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10319,7 +10397,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10327,7 +10405,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10343,13 +10421,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="222.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="222.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10357,7 +10435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10365,7 +10443,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10373,7 +10451,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10389,13 +10467,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="137.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="137.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10403,7 +10481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10411,7 +10489,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10419,7 +10497,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10427,13 +10505,13 @@
         <v>899</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10444,13 +10522,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="135.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="135.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10458,7 +10536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10466,7 +10544,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10474,7 +10552,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10490,13 +10568,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="114.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="114.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10504,7 +10582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
@@ -10512,7 +10590,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10520,7 +10598,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarah.weisberg\fisheriesXplorer\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC39F11-6744-43EE-8C70-20B31016904C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CEF327-C666-45F8-86B5-133815BCE43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50820" yWindow="-4785" windowWidth="40050" windowHeight="15105" tabRatio="858" firstSheet="30" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="28" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -58,10 +58,7 @@
     <sheet name="vms_NrS" sheetId="45" r:id="rId43"/>
     <sheet name="vms_NwS" sheetId="46" r:id="rId44"/>
     <sheet name="vms_ONA" sheetId="47" r:id="rId45"/>
-    <sheet name="mixfish" sheetId="5" r:id="rId46"/>
-    <sheet name="Sheet1" sheetId="48" r:id="rId47"/>
-    <sheet name="bycatch" sheetId="7" r:id="rId48"/>
-    <sheet name="bycatch_AZ" sheetId="49" r:id="rId49"/>
+    <sheet name="bycatch_AZ" sheetId="49" r:id="rId46"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -84,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="998">
   <si>
     <t>section</t>
   </si>
@@ -102,15 +99,6 @@
   </si>
   <si>
     <t>discards</t>
-  </si>
-  <si>
-    <t>sidebar</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Bycatch of protected, endangered, and threatened species&lt;/b&gt;&lt;br&gt;&lt;br&gt; All fisheries have the potential to catch protected, endangered, or threatened species, such as seabirds and marine mammals, as non-targeted bycatch. Data submitted to ICES through annual data calls indicated that between 2017–2021 ten ICES Member Countries had fisheries operating in the Greater North Sea ecoregion (ICES, 2022a). During the same period approximately 13 000 monitoring days were undertaken, primarily by at-sea observers, in a variety of static and mobile gears and on vessels ranging from under 8 m to over 40 m. Most bycatch data collection in the ecoregion is carried out within multipurpose programmes under the DCF and through dedicated bycatch monitoring programmes.&lt;br&gt;&lt;br&gt;&lt;b&gt; Bycatch records in 2021&lt;/b&gt;&lt;br&gt;&lt;br&gt; In 2021, 47 marine mammals from at least four species were recorded as bycatch, mostly in net métiers. Forty-two seabirds from at least five species were recorded as bycatch in bottom trawl, longline, purse-seine and net fisheries (Table 1). Over 13 000 specimens of fish of potential conservation interest were recorded from a wide mix of static and mobile gears. Most of the fish records were tub gurnard (Chelidonichthys lucerna) in bottom trawls. No turtles were reported as bycatch.</t>
   </si>
   <si>
     <t>term</t>
@@ -5182,3467 +5170,3467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.6640625" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>928</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>929</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>931</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>934</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>935</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>937</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>940</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>941</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>943</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>944</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>946</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>947</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>949</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="C18" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>952</v>
+      </c>
+      <c r="B20" t="s">
+        <v>953</v>
+      </c>
+      <c r="C20" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>955</v>
+      </c>
+      <c r="B21" t="s">
+        <v>956</v>
+      </c>
+      <c r="C21" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>958</v>
+      </c>
+      <c r="B22" t="s">
+        <v>959</v>
+      </c>
+      <c r="C22" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>961</v>
+      </c>
+      <c r="B23" t="s">
+        <v>962</v>
+      </c>
+      <c r="C23" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>964</v>
+      </c>
+      <c r="B25" t="s">
+        <v>965</v>
+      </c>
+      <c r="C25" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C28" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>967</v>
+      </c>
+      <c r="B30" t="s">
+        <v>968</v>
+      </c>
+      <c r="C30" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>970</v>
+      </c>
+      <c r="B31" t="s">
+        <v>971</v>
+      </c>
+      <c r="C31" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>973</v>
+      </c>
+      <c r="B32" t="s">
+        <v>974</v>
+      </c>
+      <c r="C32" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>976</v>
+      </c>
+      <c r="B33" t="s">
+        <v>977</v>
+      </c>
+      <c r="C33" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>979</v>
+      </c>
+      <c r="B34" t="s">
+        <v>980</v>
+      </c>
+      <c r="C34" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>982</v>
+      </c>
+      <c r="B35" t="s">
+        <v>983</v>
+      </c>
+      <c r="C35" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>985</v>
+      </c>
+      <c r="B36" t="s">
+        <v>986</v>
+      </c>
+      <c r="C36" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>988</v>
+      </c>
+      <c r="B37" t="s">
+        <v>989</v>
+      </c>
+      <c r="C37" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>991</v>
+      </c>
+      <c r="B39" t="s">
+        <v>992</v>
+      </c>
+      <c r="C39" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="B40" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>932</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B43" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>934</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>935</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>937</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>938</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>940</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>941</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>943</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>944</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>946</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>947</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>949</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>950</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>952</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>953</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>955</v>
-      </c>
-      <c r="B20" t="s">
-        <v>956</v>
-      </c>
-      <c r="C20" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>958</v>
-      </c>
-      <c r="B21" t="s">
-        <v>959</v>
-      </c>
-      <c r="C21" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>961</v>
-      </c>
-      <c r="B22" t="s">
-        <v>962</v>
-      </c>
-      <c r="C22" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>964</v>
-      </c>
-      <c r="B23" t="s">
-        <v>965</v>
-      </c>
-      <c r="C23" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>967</v>
-      </c>
-      <c r="B25" t="s">
-        <v>968</v>
-      </c>
-      <c r="C25" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>970</v>
-      </c>
-      <c r="B30" t="s">
-        <v>971</v>
-      </c>
-      <c r="C30" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>973</v>
-      </c>
-      <c r="B31" t="s">
-        <v>974</v>
-      </c>
-      <c r="C31" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>976</v>
-      </c>
-      <c r="B32" t="s">
-        <v>977</v>
-      </c>
-      <c r="C32" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>979</v>
-      </c>
-      <c r="B33" t="s">
-        <v>980</v>
-      </c>
-      <c r="C33" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>982</v>
-      </c>
-      <c r="B34" t="s">
-        <v>983</v>
-      </c>
-      <c r="C34" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>985</v>
-      </c>
-      <c r="B35" t="s">
-        <v>986</v>
-      </c>
-      <c r="C35" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>988</v>
-      </c>
-      <c r="B36" t="s">
-        <v>989</v>
-      </c>
-      <c r="C36" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>991</v>
-      </c>
-      <c r="B37" t="s">
-        <v>992</v>
-      </c>
-      <c r="C37" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>994</v>
-      </c>
-      <c r="B39" t="s">
-        <v>995</v>
-      </c>
-      <c r="C39" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="C43" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B44" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B45" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C45" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B46" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C46" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C48" s="10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B49" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C49" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B50" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C50" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B51" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B52" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C52" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B53" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C53" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C54" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C55" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B56" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C56" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C57" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B58" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C58" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C59" s="11" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B60" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C60" s="10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B61" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C61" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B62" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C62" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B63" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C63" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B64" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C64" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B65" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C65" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B66" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C66" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B67" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C67" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B68" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C68" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B69" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C69" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B70" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C70" s="10" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B71" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C71" s="10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B72" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C72" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B73" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C73" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B74" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C74" s="10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B75" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C75" s="10" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B76" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C76" s="10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B77" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C77" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B78" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C78" s="10" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B79" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C79" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B80" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C80" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B81" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C81" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B82" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C82" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="10" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B83" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C83" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="10" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B84" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C84" s="10" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B85" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C85" s="10" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="10" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B86" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C86" s="10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="10" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B87" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C87" s="10" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="10" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B88" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C88" s="10" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="10" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B89" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C89" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="10" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B90" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C90" s="10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="10" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B91" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C91" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="10" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B92" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C92" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="10" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B93" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C93" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="10" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B94" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C94" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="10" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B95" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C95" s="10" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="10" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B96" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C96" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="10" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B97" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C97" s="10" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="10" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B98" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C98" s="10" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="10" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B99" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C99" s="10" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="10" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B100" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C100" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="10" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B101" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C101" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="10" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B102" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C102" s="10" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B103" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C103" s="10" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="10" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B104" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C104" s="10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B105" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C105" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="10" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B106" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C106" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="10" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B107" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C107" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="10" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B108" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C108" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="10" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B109" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C109" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="10" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B110" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C110" s="10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B111" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C111" s="10" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="10" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B112" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C112" s="10" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B113" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C113" s="10" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="10" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B114" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C114" s="10" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B115" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C115" s="10" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B116" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="C115" s="10" t="s">
+      <c r="C116" s="10" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="10" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B117" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C117" s="10" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="10" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B118" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C118" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="10" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B119" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C119" s="10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="10" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B120" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C120" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B121" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C121" s="10" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="10" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B122" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C122" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="10" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B123" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C123" s="10" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="10" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B124" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C124" s="10" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="10" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B125" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C125" s="10" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="10" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B126" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C126" s="10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="10" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B127" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C127" s="10" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="10" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B128" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C128" s="10" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="10" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B129" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C129" s="10" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="10" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B130" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C130" s="10" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="10" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B131" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C131" s="10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="10" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B131" s="10" t="s">
+      <c r="B132" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="C131" s="10" t="s">
+      <c r="C132" s="10" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="10" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B133" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C133" s="10" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="10" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B134" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C134" s="10" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="10" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B135" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C135" s="10" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="10" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B136" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="C136" s="10" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="10" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B137" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C137" s="10" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="10" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B138" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="10" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B139" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C139" s="10" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="10" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B140" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C140" s="10" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="10" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B141" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C141" s="10" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="10" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B142" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C141" s="10" t="s">
+      <c r="C142" s="10" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="10" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B143" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C143" s="10" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="10" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B144" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C144" s="10" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="10" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B145" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C145" s="10" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="10" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B146" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C146" s="10" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="10" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B147" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C147" s="10" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="10" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B148" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C148" s="10" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="10" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B149" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C149" s="10" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="10" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B150" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C150" s="10" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B151" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C151" s="10" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="10" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B152" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C152" s="10" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="10" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B153" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C153" s="10" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="10" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B153" s="10" t="s">
+      <c r="B154" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C154" s="10" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="10" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B155" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C155" s="10" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="10" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B156" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C156" s="10" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="10" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="B157" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C157" s="10" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="10" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B158" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C158" s="10" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="10" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B158" s="10" t="s">
+      <c r="B159" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C159" s="10" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="10" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="B160" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C160" s="10" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="10" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="B161" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C161" s="10" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="10" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B161" s="10" t="s">
+      <c r="B162" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="C161" s="10" t="s">
+      <c r="C162" s="10" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="10" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B163" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C163" s="10" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="10" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B164" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C164" s="10" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="10" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B165" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C165" s="10" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="10" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B166" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C166" s="10" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="10" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B167" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C167" s="10" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="10" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B168" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C168" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="10" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B168" s="10" t="s">
+      <c r="B169" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="C168" s="10" t="s">
+      <c r="C169" s="10" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="10" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B169" s="10" t="s">
+      <c r="B170" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C170" s="10" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="10" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="B170" s="10" t="s">
+      <c r="B171" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C171" s="10" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="10" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="B171" s="10" t="s">
+      <c r="B172" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C172" s="10" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="10" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B173" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C173" s="10" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="10" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B174" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C174" s="10" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="10" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B175" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="C175" s="10" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="10" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B176" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C176" s="10" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="10" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="B176" s="10" t="s">
+      <c r="B177" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C177" s="10" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="10" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B178" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C178" s="10" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="10" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B178" s="10" t="s">
+      <c r="B179" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C179" s="10" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="10" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B180" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C179" s="10" t="s">
+      <c r="C180" s="10" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="10" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B180" s="10" t="s">
+      <c r="B181" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C181" s="10" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="10" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="B181" s="10" t="s">
+      <c r="B182" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C182" s="10" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="10" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="B183" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="C182" s="10" t="s">
+      <c r="C183" s="10" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="10" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B184" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C184" s="10" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="10" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B185" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C185" s="10" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="10" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="B185" s="10" t="s">
+      <c r="B186" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C186" s="10" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="10" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="B186" s="10" t="s">
+      <c r="B187" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C187" s="10" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="10" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="B187" s="10" t="s">
+      <c r="B188" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C188" s="10" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="10" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="10" t="s">
         <v>501</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B189" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C189" s="10" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="10" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B190" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C190" s="10" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="10" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B191" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C191" s="10" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="10" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B192" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="C192" s="10" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="10" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B193" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C193" s="10" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="10" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B194" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C194" s="10" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="10" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B195" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C195" s="10" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="10" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B196" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C196" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B197" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C197" s="10" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="10" t="s">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B198" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="C197" s="10" t="s">
+      <c r="C198" s="10" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="10" t="s">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B198" s="10" t="s">
+      <c r="B199" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C199" s="10" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="10" t="s">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="B200" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C200" s="10" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="10" t="s">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B201" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C201" s="10" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="10" t="s">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="B201" s="10" t="s">
+      <c r="B202" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C202" s="10" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="10" t="s">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B203" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C203" s="10" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="10" t="s">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B204" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="C203" s="10" t="s">
+      <c r="C204" s="10" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="10" t="s">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="B204" s="10" t="s">
+      <c r="B205" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="C204" s="10" t="s">
+      <c r="C205" s="10" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="10" t="s">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B206" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="C205" s="10" t="s">
+      <c r="C206" s="10" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="10" t="s">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="B206" s="10" t="s">
+      <c r="B207" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="C206" s="10" t="s">
+      <c r="C207" s="10" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="10" t="s">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="B207" s="10" t="s">
+      <c r="B208" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="C207" s="10" t="s">
+      <c r="C208" s="10" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="10" t="s">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="B208" s="10" t="s">
+      <c r="B209" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="C209" s="10" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="10" t="s">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="B209" s="10" t="s">
+      <c r="B210" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="C209" s="10" t="s">
+      <c r="C210" s="10" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="10" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B211" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C211" s="10" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="10" t="s">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B212" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C212" s="10" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="10" t="s">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="B212" s="10" t="s">
+      <c r="B213" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C213" s="10" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="10" t="s">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B214" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C214" s="10" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="10" t="s">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="B214" s="10" t="s">
+      <c r="B215" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="C214" s="10" t="s">
+      <c r="C215" s="10" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="10" t="s">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B216" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="C216" s="10" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="10" t="s">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B217" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="C216" s="10" t="s">
+      <c r="C217" s="10" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="10" t="s">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B218" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="C217" s="10" t="s">
+      <c r="C218" s="10" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="10" t="s">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B219" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="C218" s="10" t="s">
+      <c r="C219" s="10" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="10" t="s">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B220" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="C219" s="10" t="s">
+      <c r="C220" s="10" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="10" t="s">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="B220" s="10" t="s">
+      <c r="B221" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="C220" s="10" t="s">
+      <c r="C221" s="10" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="10" t="s">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B221" s="10" t="s">
+      <c r="B222" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="C222" s="10" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="10" t="s">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="B222" s="10" t="s">
+      <c r="B223" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="C222" s="10" t="s">
+      <c r="C223" s="10" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="10" t="s">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="B223" s="10" t="s">
+      <c r="B224" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="C223" s="10" t="s">
+      <c r="C224" s="10" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="10" t="s">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="B224" s="10" t="s">
+      <c r="B225" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="C224" s="10" t="s">
+      <c r="C225" s="10" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="10" t="s">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="B225" s="10" t="s">
+      <c r="B226" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="C225" s="10" t="s">
+      <c r="C226" s="10" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="10" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="B226" s="10" t="s">
+      <c r="B227" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C226" s="10" t="s">
+      <c r="C227" s="10" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="10" t="s">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="B227" s="10" t="s">
+      <c r="B228" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="C228" s="10" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="10" t="s">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="B228" s="10" t="s">
+      <c r="B229" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="C228" s="10" t="s">
+      <c r="C229" s="10" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="10" t="s">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="B229" s="10" t="s">
+      <c r="B230" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="C229" s="10" t="s">
+      <c r="C230" s="10" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="10" t="s">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B231" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="C230" s="10" t="s">
+      <c r="C231" s="10" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="10" t="s">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B232" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="C231" s="10" t="s">
+      <c r="C232" s="10" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="10" t="s">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="B232" s="10" t="s">
+      <c r="B233" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="C232" s="10" t="s">
+      <c r="C233" s="10" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="10" t="s">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B234" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="C233" s="10" t="s">
+      <c r="C234" s="10" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="10" t="s">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="B234" s="10" t="s">
+      <c r="B235" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="C234" s="10" t="s">
+      <c r="C235" s="10" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="10" t="s">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="B235" s="10" t="s">
+      <c r="B236" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="C235" s="10" t="s">
+      <c r="C236" s="10" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="10" t="s">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="B236" s="10" t="s">
+      <c r="B237" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="C236" s="10" t="s">
+      <c r="C237" s="10" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="10" t="s">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="B237" s="10" t="s">
+      <c r="B238" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="C237" s="10" t="s">
+      <c r="C238" s="10" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="10" t="s">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="B238" s="10" t="s">
+      <c r="B239" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="C238" s="10" t="s">
+      <c r="C239" s="10" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="10" t="s">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="B239" s="10" t="s">
+      <c r="B240" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="C240" s="10" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="10" t="s">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B240" s="10" t="s">
+      <c r="B241" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="C240" s="10" t="s">
+      <c r="C241" s="10" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="10" t="s">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="B241" s="10" t="s">
+      <c r="B242" s="10" t="s">
         <v>661</v>
       </c>
-      <c r="C241" s="10" t="s">
+      <c r="C242" s="10" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="10" t="s">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="B242" s="10" t="s">
+      <c r="B243" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C243" s="10" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="10" t="s">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="B243" s="10" t="s">
+      <c r="B244" s="10" t="s">
         <v>667</v>
       </c>
-      <c r="C243" s="10" t="s">
+      <c r="C244" s="10" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="10" t="s">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="B244" s="10" t="s">
+      <c r="B245" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="C244" s="10" t="s">
+      <c r="C245" s="10" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="10" t="s">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B245" s="10" t="s">
+      <c r="B246" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="C245" s="10" t="s">
+      <c r="C246" s="10" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="10" t="s">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B247" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="C246" s="10" t="s">
+      <c r="C247" s="10" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="10" t="s">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="B247" s="10" t="s">
+      <c r="B248" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="C247" s="10" t="s">
+      <c r="C248" s="10" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="10" t="s">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="B248" s="10" t="s">
+      <c r="B249" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="C248" s="10" t="s">
+      <c r="C249" s="10" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="10" t="s">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="B249" s="10" t="s">
+      <c r="B250" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="C249" s="10" t="s">
+      <c r="C250" s="10" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="10" t="s">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B251" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="C250" s="10" t="s">
+      <c r="C251" s="10" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="10" t="s">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="B251" s="10" t="s">
+      <c r="B252" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="C251" s="10" t="s">
+      <c r="C252" s="10" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="10" t="s">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B253" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="C252" s="10" t="s">
+      <c r="C253" s="10" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="10" t="s">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="B253" s="10" t="s">
+      <c r="B254" s="10" t="s">
         <v>697</v>
       </c>
-      <c r="C253" s="10" t="s">
+      <c r="C254" s="10" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="10" t="s">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="B254" s="10" t="s">
+      <c r="B255" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="C254" s="10" t="s">
+      <c r="C255" s="10" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="10" t="s">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="B255" s="10" t="s">
+      <c r="B256" s="10" t="s">
         <v>703</v>
       </c>
-      <c r="C255" s="10" t="s">
+      <c r="C256" s="10" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="10" t="s">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="B256" s="10" t="s">
+      <c r="B257" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="C256" s="10" t="s">
+      <c r="C257" s="10" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="10" t="s">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="B257" s="10" t="s">
+      <c r="B258" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="C257" s="10" t="s">
+      <c r="C258" s="10" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="10" t="s">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="10" t="s">
         <v>711</v>
       </c>
-      <c r="B258" s="10" t="s">
+      <c r="B259" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="C258" s="10" t="s">
+      <c r="C259" s="10" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="10" t="s">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="B259" s="10" t="s">
+      <c r="B260" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="C259" s="10" t="s">
+      <c r="C260" s="10" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="10" t="s">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="B260" s="10" t="s">
+      <c r="B261" s="10" t="s">
         <v>718</v>
       </c>
-      <c r="C260" s="10" t="s">
+      <c r="C261" s="10" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="10" t="s">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="B261" s="10" t="s">
+      <c r="B262" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="C261" s="10" t="s">
+      <c r="C262" s="10" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="10" t="s">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="B262" s="10" t="s">
+      <c r="B263" s="10" t="s">
         <v>724</v>
       </c>
-      <c r="C262" s="10" t="s">
+      <c r="C263" s="10" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="10" t="s">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="B263" s="10" t="s">
+      <c r="B264" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="C263" s="10" t="s">
+      <c r="C264" s="10" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="10" t="s">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="B264" s="10" t="s">
+      <c r="B265" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="C264" s="10" t="s">
+      <c r="C265" s="10" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="10" t="s">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="B265" s="10" t="s">
+      <c r="B266" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="C265" s="10" t="s">
+      <c r="C266" s="10" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="10" t="s">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="B266" s="10" t="s">
+      <c r="B267" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="C266" s="10" t="s">
+      <c r="C267" s="10" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="10" t="s">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="B267" s="10" t="s">
+      <c r="B268" s="10" t="s">
         <v>739</v>
       </c>
-      <c r="C267" s="10" t="s">
+      <c r="C268" s="10" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="10" t="s">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="B268" s="10" t="s">
+      <c r="B269" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="C268" s="10" t="s">
+      <c r="C269" s="10" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="10" t="s">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B269" s="10" t="s">
+      <c r="B270" s="10" t="s">
         <v>745</v>
       </c>
-      <c r="C269" s="10" t="s">
+      <c r="C270" s="10" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="10" t="s">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="10" t="s">
         <v>747</v>
       </c>
-      <c r="B270" s="10" t="s">
+      <c r="B271" s="10" t="s">
         <v>748</v>
       </c>
-      <c r="C270" s="10" t="s">
+      <c r="C271" s="10" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="10" t="s">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="B271" s="10" t="s">
+      <c r="B272" s="10" t="s">
         <v>751</v>
       </c>
-      <c r="C271" s="10" t="s">
+      <c r="C272" s="10" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="10" t="s">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="10" t="s">
         <v>753</v>
       </c>
-      <c r="B272" s="10" t="s">
+      <c r="B273" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="C272" s="10" t="s">
+      <c r="C273" s="10" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="10" t="s">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="B273" s="10" t="s">
+      <c r="B274" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C273" s="10" t="s">
+      <c r="C274" s="10" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="10" t="s">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="10" t="s">
         <v>759</v>
       </c>
-      <c r="B274" s="10" t="s">
+      <c r="B275" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="C274" s="10" t="s">
+      <c r="C275" s="10" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="10" t="s">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="B275" s="10" t="s">
+      <c r="B276" s="10" t="s">
         <v>763</v>
       </c>
-      <c r="C275" s="10" t="s">
+      <c r="C276" s="10" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="10" t="s">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="10" t="s">
         <v>765</v>
       </c>
-      <c r="B276" s="10" t="s">
+      <c r="B277" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="C276" s="10" t="s">
+      <c r="C277" s="10" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="10" t="s">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="10" t="s">
         <v>768</v>
       </c>
-      <c r="B277" s="10" t="s">
+      <c r="B278" s="10" t="s">
         <v>769</v>
       </c>
-      <c r="C277" s="10" t="s">
+      <c r="C278" s="10" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="10" t="s">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="10" t="s">
         <v>771</v>
       </c>
-      <c r="B278" s="10" t="s">
+      <c r="B279" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C278" s="10" t="s">
+      <c r="C279" s="10" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="10" t="s">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="B279" s="10" t="s">
+      <c r="B280" s="10" t="s">
         <v>775</v>
       </c>
-      <c r="C279" s="10" t="s">
+      <c r="C280" s="10" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="10" t="s">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="B280" s="10" t="s">
+      <c r="B281" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="C280" s="10" t="s">
+      <c r="C281" s="10" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="10" t="s">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B282" s="10" t="s">
         <v>781</v>
       </c>
-      <c r="C281" s="10" t="s">
+      <c r="C282" s="10" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="10" t="s">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B283" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="C282" s="10" t="s">
+      <c r="C283" s="10" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="10" t="s">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B284" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="C283" s="10" t="s">
+      <c r="C284" s="10" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="10" t="s">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="B284" s="10" t="s">
+      <c r="B285" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="C284" s="10" t="s">
+      <c r="C285" s="10" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="10" t="s">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="B286" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="C286" s="10" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="10" t="s">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="B286" s="10" t="s">
+      <c r="B287" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="C286" s="10" t="s">
+      <c r="C287" s="10" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="10" t="s">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="B287" s="10" t="s">
+      <c r="B288" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="C287" s="10" t="s">
+      <c r="C288" s="10" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="10" t="s">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="B288" s="10" t="s">
+      <c r="B289" s="10" t="s">
         <v>802</v>
       </c>
-      <c r="C288" s="10" t="s">
+      <c r="C289" s="10" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="10" t="s">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="B290" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="C290" s="10" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="10" t="s">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="B290" s="10" t="s">
+      <c r="B291" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="C290" s="10" t="s">
+      <c r="C291" s="10" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="10" t="s">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="10" t="s">
         <v>810</v>
       </c>
-      <c r="B291" s="10" t="s">
+      <c r="B292" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C291" s="10" t="s">
+      <c r="C292" s="10" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="10" t="s">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="B292" s="10" t="s">
+      <c r="B293" s="10" t="s">
         <v>814</v>
       </c>
-      <c r="C292" s="10" t="s">
+      <c r="C293" s="10" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="10" t="s">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="10" t="s">
         <v>816</v>
       </c>
-      <c r="B293" s="10" t="s">
+      <c r="B294" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C293" s="10" t="s">
+      <c r="C294" s="10" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="10" t="s">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="B294" s="10" t="s">
+      <c r="B295" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="C294" s="10" t="s">
+      <c r="C295" s="10" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="10" t="s">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="10" t="s">
         <v>822</v>
       </c>
-      <c r="B295" s="10" t="s">
+      <c r="B296" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="C295" s="10" t="s">
+      <c r="C296" s="10" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="10" t="s">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="10" t="s">
         <v>825</v>
       </c>
-      <c r="B296" s="10" t="s">
+      <c r="B297" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C296" s="10" t="s">
+      <c r="C297" s="10" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="10" t="s">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="B297" s="10" t="s">
+      <c r="B298" s="10" t="s">
         <v>829</v>
       </c>
-      <c r="C297" s="10" t="s">
+      <c r="C298" s="10" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="10" t="s">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="10" t="s">
         <v>831</v>
       </c>
-      <c r="B298" s="10" t="s">
+      <c r="B299" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C298" s="10" t="s">
+      <c r="C299" s="10" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="10" t="s">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="B299" s="10" t="s">
+      <c r="B300" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="C299" s="10" t="s">
+      <c r="C300" s="10" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="10" t="s">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="10" t="s">
         <v>837</v>
       </c>
-      <c r="B300" s="10" t="s">
+      <c r="B301" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C300" s="10" t="s">
+      <c r="C301" s="10" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="10" t="s">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="B301" s="10" t="s">
+      <c r="B302" s="10" t="s">
         <v>841</v>
       </c>
-      <c r="C301" s="10" t="s">
+      <c r="C302" s="10" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="10" t="s">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="10" t="s">
         <v>843</v>
       </c>
-      <c r="B302" s="10" t="s">
+      <c r="B303" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="C302" s="10" t="s">
+      <c r="C303" s="10" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="10" t="s">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="B304" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="C303" s="10" t="s">
+      <c r="C304" s="10" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="10" t="s">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="10" t="s">
         <v>849</v>
       </c>
-      <c r="B304" s="10" t="s">
+      <c r="B305" s="10" t="s">
         <v>850</v>
       </c>
-      <c r="C304" s="10" t="s">
+      <c r="C305" s="10" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="10" t="s">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="B305" s="10" t="s">
+      <c r="B306" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="C305" s="10" t="s">
+      <c r="C306" s="10" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="10" t="s">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="10" t="s">
         <v>855</v>
       </c>
-      <c r="B306" s="10" t="s">
+      <c r="B307" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="C306" s="10" t="s">
+      <c r="C307" s="10" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="B307" s="10" t="s">
+      <c r="B308" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="C307" s="10" t="s">
+      <c r="C308" s="10" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="10" t="s">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="B308" s="10" t="s">
+      <c r="B309" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="C308" s="10" t="s">
+      <c r="C309" s="10" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="10" t="s">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="B309" s="10" t="s">
+      <c r="B310" s="10" t="s">
         <v>865</v>
       </c>
-      <c r="C309" s="10" t="s">
+      <c r="C310" s="10" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="10" t="s">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="10" t="s">
         <v>867</v>
       </c>
-      <c r="B310" s="10" t="s">
+      <c r="B311" s="10" t="s">
         <v>868</v>
       </c>
-      <c r="C310" s="10" t="s">
+      <c r="C311" s="10" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="10" t="s">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="10" t="s">
         <v>870</v>
       </c>
-      <c r="B311" s="10" t="s">
+      <c r="B312" s="10" t="s">
         <v>871</v>
       </c>
-      <c r="C311" s="10" t="s">
+      <c r="C312" s="10" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="10" t="s">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="10" t="s">
         <v>873</v>
       </c>
-      <c r="B312" s="10" t="s">
+      <c r="B313" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="C312" s="10" t="s">
+      <c r="C313" s="10" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="10" t="s">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="10" t="s">
         <v>876</v>
       </c>
-      <c r="B313" s="10" t="s">
+      <c r="B314" s="10" t="s">
         <v>877</v>
       </c>
-      <c r="C313" s="10" t="s">
+      <c r="C314" s="10" t="s">
         <v>878</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="10" t="s">
-        <v>879</v>
-      </c>
-      <c r="B314" s="10" t="s">
-        <v>880</v>
-      </c>
-      <c r="C314" s="10" t="s">
-        <v>881</v>
       </c>
     </row>
   </sheetData>
@@ -8662,13 +8650,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8676,28 +8664,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -8711,13 +8699,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="198.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8725,28 +8713,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -8757,13 +8745,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="229.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="229.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8771,28 +8759,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -8803,13 +8791,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8817,20 +8805,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -8841,13 +8829,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8855,20 +8843,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -8879,13 +8867,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8893,20 +8881,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -8917,13 +8905,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8931,20 +8919,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -8955,12 +8943,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="125.5703125" customWidth="1"/>
+    <col min="2" max="2" width="125.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8968,20 +8956,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -8992,13 +8980,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9006,20 +8994,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9030,13 +9018,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9044,20 +9032,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9068,13 +9056,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="152.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="152.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9082,28 +9070,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
   </sheetData>
@@ -9114,13 +9102,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9128,20 +9116,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9155,13 +9143,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9169,20 +9157,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9193,13 +9181,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9207,20 +9195,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9231,13 +9219,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9245,20 +9233,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9270,13 +9258,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9284,33 +9272,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9322,13 +9310,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9336,33 +9324,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9373,13 +9361,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9387,33 +9375,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9424,13 +9412,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9438,33 +9426,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9478,13 +9466,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9492,33 +9480,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9529,13 +9517,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9543,33 +9531,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9580,13 +9568,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="253.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="253.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9594,28 +9582,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -9626,13 +9614,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9640,33 +9628,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9677,13 +9665,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9691,33 +9679,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9728,13 +9716,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9742,33 +9730,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9779,13 +9767,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9793,33 +9781,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9830,13 +9818,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="199.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9844,33 +9832,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>906</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -9884,13 +9872,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9898,12 +9886,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -9914,13 +9902,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9928,12 +9916,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -9944,13 +9932,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9958,12 +9946,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -9974,13 +9962,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9988,12 +9976,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10004,13 +9992,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10018,12 +10006,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10034,13 +10022,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="223.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="223.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10048,28 +10036,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -10080,13 +10068,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10094,12 +10082,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10110,13 +10098,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10124,12 +10112,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10140,13 +10128,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10154,12 +10142,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10170,13 +10158,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10184,12 +10172,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10200,13 +10188,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10214,12 +10202,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10230,13 +10218,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10244,12 +10232,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -10258,92 +10246,18 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E1B14FC-8227-47AA-A858-20FEF7B4AC2B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="159.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE61185-CF8B-43DA-9230-D26A514F1564}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10351,20 +10265,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>996</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>997</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>999</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -10375,13 +10289,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="181.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="181.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10389,28 +10303,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -10421,13 +10335,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="222.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="222.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10435,28 +10349,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -10467,13 +10381,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="137.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="137.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10481,37 +10395,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="393.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10522,13 +10436,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="135.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="135.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10536,28 +10450,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
     </row>
   </sheetData>
@@ -10568,13 +10482,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="114.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="114.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10582,28 +10496,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarah.weisberg\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CEF327-C666-45F8-86B5-133815BCE43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFD5F8A-D9AA-47A8-A631-653F2A1435F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="28" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-48225" yWindow="-2955" windowWidth="39150" windowHeight="18105" tabRatio="858" firstSheet="34" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -59,6 +59,16 @@
     <sheet name="vms_NwS" sheetId="46" r:id="rId44"/>
     <sheet name="vms_ONA" sheetId="47" r:id="rId45"/>
     <sheet name="bycatch_AZ" sheetId="49" r:id="rId46"/>
+    <sheet name="bycatch_BI" sheetId="50" r:id="rId47"/>
+    <sheet name="bycatch_BrS" sheetId="51" r:id="rId48"/>
+    <sheet name="bycatch_BtS" sheetId="52" r:id="rId49"/>
+    <sheet name="bycatch_CS" sheetId="53" r:id="rId50"/>
+    <sheet name="bycatch_FO" sheetId="54" r:id="rId51"/>
+    <sheet name="bycatch_IS" sheetId="55" r:id="rId52"/>
+    <sheet name="bycatch_GS" sheetId="56" r:id="rId53"/>
+    <sheet name="bycatch_NrS" sheetId="57" r:id="rId54"/>
+    <sheet name="bycatch_NwS" sheetId="58" r:id="rId55"/>
+    <sheet name="bycatch_ONA" sheetId="59" r:id="rId56"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -81,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1010">
   <si>
     <t>section</t>
   </si>
@@ -4712,27 +4722,157 @@
     <t>total_bycatch</t>
   </si>
   <si>
+    <t>bpue</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Azores ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine turtles and multiannual bycatch rates for marine mammals and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 2 marine mammal species (3 métier–species combinations). The highest bycatch rate was estimated for Atlantic spotted dolphin in hand and pole lines, followed by common dolphin in hand and pole lines (mechanized) and hand and pole lines. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 3 marine turtle species (4 métier–species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines, followed by loggerhead turtle in set gillnet and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Bay of Biscay and Iberian Coast ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine mammals, seabirds and turtles and bycatch rates for marine mammals, seabirds and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 17 marine seabird species (40 métier–species combinations). The highest bycatch rate was estimated for manx shearwater in drifting longlines, followed by lesser black-backed gull in midwater otter trawl and northern gannet in midwater otter trawl. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 2 marine turtle species (5 métier–species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines, followed by leatherback turtle in drifting longlines and loggerhead turtle in set gillnets.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Baltic Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;  
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+ Multiannual bycatch rates were estimated for 4 marine mammal species (9 métier–species combinations). The highest bycatch rate was estimated for gray seals in pots and traps, followed by harbor porpoise in trammel nets and harbor seal in trammel nets. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 17 seabird species (28 métier–species combinations). The highest bycatch rate was estimated for great cormorant in trammel nets, followed by common guillemot in drifting longlines and common eider in trammel nets.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Baltic Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 3 marine mammal species (3 métier–species combinations). The highest total bycaught number was estimated for harbor seal in trammel nets, followed by harbor porpoise in trammel nets and ringed seal in pots and traps.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Bay of Biscay and Iberian Coast ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine mammals, seabirds and turtles and bycatch rates for marine mammals, seabirds and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 5 marine mammal species (12 métier–species combination). The highest total bycaught number was estimated for common dolphin in bottom pair trawl, followed by common dolphin in pelagic pair trawl and common dolphin in purse seine.&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
 &lt;p&gt;
 All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Azores ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine turtles and multiannual bycatch rates for marine mammals and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
 &lt;/p&gt; 
 &lt;h4&gt;Bycatch estimates&lt;/h4&gt;
 &lt;p&gt;
-Total bycatch numbers were estimated for 2 marine turtle species (3 métier/species combinations). The highest total bycaught number was estimated for loggerhead turtle in set gillnet followed by loggerhead turtle in drifting longlines and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>bpue</t>
+Total bycatch numbers were estimated for 2 marine turtle species (3 métier–species combinations). The highest total bycaught number was estimated for loggerhead turtle in set gillnet followed by loggerhead turtle in drifting longlines and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
   </si>
   <si>
     <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
 &lt;p&gt;
-All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Azores ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine turtles and multiannual bycatch rates for marine mammals and marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Baltic Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;  
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 6 marine mammal species (17 métier–species combinations). The highest bycatch rate was estimated for gray seals in trammel nets, followed by harbor porpoise in trammel nets and gray seal in set gillnets. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 7 seabird species (13 métier–species combinations). The highest bycatch rate was estimated for northern fulmar in set longlines, followed by herring gull in purse seines and northern gannet in bottom pair trawls.&lt;/p&gt; 
+&lt;p&gt;
+Multiannual bycatch rates were estimated for leatherback turtle in drifting longlines. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Celtic Seas ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;. For 2024, ICES provides annual bycatch estimates for marine mammals and seabird and multiannual bycatch rates for marine mammals, seabirds, and marine turtles. Due to data limitation, ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
 &lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 2 marine mammal species (6 métier–species combinations). The highest total bycaught number was estimated for harbor porpoise in trammel nets, followed by common dolphin in trammel nets and common dolphin in multi-rig otter trawl. &lt;/p&gt;
+&lt;p&gt;
+ Total bycatch numbers were estimated for 4 seabird species (5 métier–species combinations). The highest total bycaught number was estimated for common guillemot in set gillnets, followed by northern gannet in set longlines and herring gull in purse seines. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Icelandic Waters ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 4 marine mammal species (4 métier–species combinations). The highest total bycaught number was estimated for harbor porpoise in set gillnet, followed by white-beaked dolphin in set gillnet and humpback whale in set gillnets.
+&lt;/p&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 8 seabird species (10 métier–species combinations). The highest total bycaught number was estimated for common eider in set gillnet, followed by northern fulmar in set longlines and northern gannet in set longlines. 
+&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Icelandic Waters ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;   
 &lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
 &lt;p&gt;
-Multiannual bycatch rates were estimated for 2 marine mammal species (3 métier/species combinations). The highest bycatch rate was estimated for Atlantic spotted dolphin in hand and pole lines, followed by common dolphin in hand and pole lines (mechanized) and hand and pole lines. &lt;/p&gt;
-&lt;p&gt;
-Multiannual bycatch rates were estimated for 3 marine turtle species (4 métier/species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines, followed by loggerhead turtle in set gillnet and leatherback turtle in drifting longlines.&lt;/p&gt;</t>
+Multiannual bycatch rates were estimated for 7 marine mammal species (8 métier–species combinations). The highest bycatch rate was estimated for harbor porpoise in set gillnet, followed by harbor seal in set gillnet and harp seal in set gillnets. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 15 seabird species (18 métier–species combinations). The highest bycatch rate was estimated for common guillemot in set gillnet, followed by common eider in set gillnet and black guillemot in set gillnet. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Greater North Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 5 marine mammal species (5 métier–species combinations). The highest total bycaught number was estimated for harbor seal in set gillnet, followed by harbor porpoise in trammel nets and common dolphin in purse seines. 
+&lt;/p&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 7 seabird species (12 métier–species combinations). The highest total bycaught number was estimated for northern gannet in beam trawl, followed by northern gannet in set longlines and herring gull in purse seines. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Greater North Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;   
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 5 marine mammal species (21 métier–species combinations). The highest bycatch rate was estimated for harbor seal in fyke nets, followed by common dolphin in purse seine and harbor porpoise in trammel nets. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 19 seabird species (37 métier–species combinations). The highest bycatch rate was estimated for black scoter in trammel nets, followed by herring gull in purse seine and northern gannet in set longlines.  &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Oceanic Northeast Atlantic ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine turtles and bycatch rates for marine turtles. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt; 
+&lt;h4&gt;Bycatch estimates&lt;/h4&gt;
+&lt;p&gt;
+Total bycatch numbers were estimated for 2 marine turtle species (2 métier–species combinations). The highest total bycaught number was estimated for loggerhead turtle in drifting longlines followed by leatherback turtle in drifting longlines. 
+&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Icelandic Waters ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;   
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 2 marine turtle species (2 métier–species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines followed by leatherback turtle in drifting longlines. &lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -4835,7 +4975,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4864,6 +5004,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5170,16 +5313,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.6640625" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5190,7 +5333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>26</v>
       </c>
@@ -5201,7 +5344,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>40</v>
       </c>
@@ -5212,7 +5355,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -5223,7 +5366,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -5234,7 +5377,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>928</v>
       </c>
@@ -5245,7 +5388,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -5256,7 +5399,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -5267,7 +5410,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -5278,7 +5421,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -5289,7 +5432,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>931</v>
       </c>
@@ -5300,7 +5443,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>934</v>
       </c>
@@ -5311,7 +5454,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>937</v>
       </c>
@@ -5322,7 +5465,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>940</v>
       </c>
@@ -5333,7 +5476,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>943</v>
       </c>
@@ -5344,7 +5487,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>946</v>
       </c>
@@ -5355,7 +5498,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>949</v>
       </c>
@@ -5366,7 +5509,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>46</v>
       </c>
@@ -5377,7 +5520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
@@ -5388,7 +5531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>952</v>
       </c>
@@ -5399,7 +5542,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>955</v>
       </c>
@@ -5410,7 +5553,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>958</v>
       </c>
@@ -5421,7 +5564,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>961</v>
       </c>
@@ -5432,7 +5575,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
@@ -5443,7 +5586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>964</v>
       </c>
@@ -5454,7 +5597,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>20</v>
       </c>
@@ -5465,7 +5608,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
@@ -5476,7 +5619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>28</v>
       </c>
@@ -5487,7 +5630,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>24</v>
       </c>
@@ -5498,7 +5641,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>967</v>
       </c>
@@ -5509,7 +5652,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>970</v>
       </c>
@@ -5520,7 +5663,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>973</v>
       </c>
@@ -5531,7 +5674,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>976</v>
       </c>
@@ -5542,7 +5685,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>979</v>
       </c>
@@ -5553,7 +5696,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>982</v>
       </c>
@@ -5564,7 +5707,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>985</v>
       </c>
@@ -5575,7 +5718,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>988</v>
       </c>
@@ -5586,7 +5729,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>36</v>
       </c>
@@ -5597,7 +5740,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>991</v>
       </c>
@@ -5608,7 +5751,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>30</v>
       </c>
@@ -5619,7 +5762,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>34</v>
       </c>
@@ -5630,7 +5773,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>44</v>
       </c>
@@ -5641,7 +5784,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>63</v>
       </c>
@@ -5652,7 +5795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
@@ -5663,7 +5806,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>69</v>
       </c>
@@ -5674,7 +5817,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>72</v>
       </c>
@@ -5685,7 +5828,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
@@ -5696,7 +5839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>78</v>
       </c>
@@ -5707,7 +5850,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>81</v>
       </c>
@@ -5718,7 +5861,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
@@ -5729,7 +5872,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>87</v>
       </c>
@@ -5740,7 +5883,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>90</v>
       </c>
@@ -5751,7 +5894,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -5762,7 +5905,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>96</v>
       </c>
@@ -5773,7 +5916,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
@@ -5784,7 +5927,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>102</v>
       </c>
@@ -5795,7 +5938,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
@@ -5806,7 +5949,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>108</v>
       </c>
@@ -5817,7 +5960,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>111</v>
       </c>
@@ -5828,7 +5971,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
@@ -5839,7 +5982,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>117</v>
       </c>
@@ -5850,7 +5993,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -5861,7 +6004,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>123</v>
       </c>
@@ -5872,7 +6015,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>126</v>
       </c>
@@ -5883,7 +6026,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>129</v>
       </c>
@@ -5894,7 +6037,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
@@ -5905,7 +6048,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>135</v>
       </c>
@@ -5916,7 +6059,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -5927,7 +6070,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>141</v>
       </c>
@@ -5938,7 +6081,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>144</v>
       </c>
@@ -5949,7 +6092,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
@@ -5960,7 +6103,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>150</v>
       </c>
@@ -5971,7 +6114,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
@@ -5982,7 +6125,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>156</v>
       </c>
@@ -5993,7 +6136,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>159</v>
       </c>
@@ -6004,7 +6147,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>162</v>
       </c>
@@ -6015,7 +6158,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>165</v>
       </c>
@@ -6026,7 +6169,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>168</v>
       </c>
@@ -6037,7 +6180,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>171</v>
       </c>
@@ -6048,7 +6191,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>174</v>
       </c>
@@ -6059,7 +6202,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>177</v>
       </c>
@@ -6070,7 +6213,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>180</v>
       </c>
@@ -6081,7 +6224,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>183</v>
       </c>
@@ -6092,7 +6235,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>186</v>
       </c>
@@ -6103,7 +6246,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>189</v>
       </c>
@@ -6114,7 +6257,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>192</v>
       </c>
@@ -6125,7 +6268,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>195</v>
       </c>
@@ -6136,7 +6279,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>198</v>
       </c>
@@ -6147,7 +6290,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>201</v>
       </c>
@@ -6158,7 +6301,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>204</v>
       </c>
@@ -6169,7 +6312,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>207</v>
       </c>
@@ -6180,7 +6323,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>210</v>
       </c>
@@ -6191,7 +6334,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>213</v>
       </c>
@@ -6202,7 +6345,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>216</v>
       </c>
@@ -6213,7 +6356,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>219</v>
       </c>
@@ -6224,7 +6367,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>222</v>
       </c>
@@ -6235,7 +6378,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>225</v>
       </c>
@@ -6246,7 +6389,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
@@ -6257,7 +6400,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>231</v>
       </c>
@@ -6268,7 +6411,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>234</v>
       </c>
@@ -6279,7 +6422,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>237</v>
       </c>
@@ -6290,7 +6433,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>240</v>
       </c>
@@ -6301,7 +6444,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>243</v>
       </c>
@@ -6312,7 +6455,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>246</v>
       </c>
@@ -6323,7 +6466,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>249</v>
       </c>
@@ -6334,7 +6477,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>252</v>
       </c>
@@ -6345,7 +6488,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>255</v>
       </c>
@@ -6356,7 +6499,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>258</v>
       </c>
@@ -6367,7 +6510,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -6378,7 +6521,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>264</v>
       </c>
@@ -6389,7 +6532,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>267</v>
       </c>
@@ -6400,7 +6543,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
         <v>270</v>
       </c>
@@ -6411,7 +6554,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>273</v>
       </c>
@@ -6422,7 +6565,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>276</v>
       </c>
@@ -6433,7 +6576,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>279</v>
       </c>
@@ -6444,7 +6587,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>282</v>
       </c>
@@ -6455,7 +6598,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>285</v>
       </c>
@@ -6466,7 +6609,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>288</v>
       </c>
@@ -6477,7 +6620,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>291</v>
       </c>
@@ -6488,7 +6631,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>294</v>
       </c>
@@ -6499,7 +6642,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>297</v>
       </c>
@@ -6510,7 +6653,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>300</v>
       </c>
@@ -6521,7 +6664,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>303</v>
       </c>
@@ -6532,7 +6675,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>306</v>
       </c>
@@ -6543,7 +6686,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
         <v>309</v>
       </c>
@@ -6554,7 +6697,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>312</v>
       </c>
@@ -6565,7 +6708,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>315</v>
       </c>
@@ -6576,7 +6719,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>318</v>
       </c>
@@ -6587,7 +6730,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>321</v>
       </c>
@@ -6598,7 +6741,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>324</v>
       </c>
@@ -6609,7 +6752,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>327</v>
       </c>
@@ -6620,7 +6763,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>330</v>
       </c>
@@ -6631,7 +6774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>333</v>
       </c>
@@ -6642,7 +6785,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>336</v>
       </c>
@@ -6653,7 +6796,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>339</v>
       </c>
@@ -6664,7 +6807,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>342</v>
       </c>
@@ -6675,7 +6818,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
         <v>345</v>
       </c>
@@ -6686,7 +6829,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>348</v>
       </c>
@@ -6697,7 +6840,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>351</v>
       </c>
@@ -6708,7 +6851,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
         <v>354</v>
       </c>
@@ -6719,7 +6862,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
         <v>357</v>
       </c>
@@ -6730,7 +6873,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>360</v>
       </c>
@@ -6741,7 +6884,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
         <v>363</v>
       </c>
@@ -6752,7 +6895,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
         <v>366</v>
       </c>
@@ -6763,7 +6906,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
         <v>369</v>
       </c>
@@ -6774,7 +6917,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
         <v>372</v>
       </c>
@@ -6785,7 +6928,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
         <v>375</v>
       </c>
@@ -6796,7 +6939,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
         <v>378</v>
       </c>
@@ -6807,7 +6950,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
         <v>381</v>
       </c>
@@ -6818,7 +6961,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
         <v>384</v>
       </c>
@@ -6829,7 +6972,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
         <v>387</v>
       </c>
@@ -6840,7 +6983,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
         <v>390</v>
       </c>
@@ -6851,7 +6994,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
         <v>393</v>
       </c>
@@ -6862,7 +7005,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
         <v>396</v>
       </c>
@@ -6873,7 +7016,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
@@ -6884,7 +7027,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>402</v>
       </c>
@@ -6895,7 +7038,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>405</v>
       </c>
@@ -6906,7 +7049,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
@@ -6917,7 +7060,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>411</v>
       </c>
@@ -6928,7 +7071,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
         <v>414</v>
       </c>
@@ -6939,7 +7082,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
         <v>417</v>
       </c>
@@ -6950,7 +7093,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
         <v>420</v>
       </c>
@@ -6961,7 +7104,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="10" t="s">
         <v>423</v>
       </c>
@@ -6972,7 +7115,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
         <v>426</v>
       </c>
@@ -6983,7 +7126,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="10" t="s">
         <v>429</v>
       </c>
@@ -6994,7 +7137,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
         <v>432</v>
       </c>
@@ -7005,7 +7148,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="10" t="s">
         <v>435</v>
       </c>
@@ -7016,7 +7159,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
@@ -7027,7 +7170,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="10" t="s">
         <v>441</v>
       </c>
@@ -7038,7 +7181,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
         <v>444</v>
       </c>
@@ -7049,7 +7192,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="10" t="s">
         <v>447</v>
       </c>
@@ -7060,7 +7203,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
         <v>450</v>
       </c>
@@ -7071,7 +7214,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="10" t="s">
         <v>453</v>
       </c>
@@ -7082,7 +7225,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
         <v>456</v>
       </c>
@@ -7093,7 +7236,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
         <v>459</v>
       </c>
@@ -7104,7 +7247,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
         <v>462</v>
       </c>
@@ -7115,7 +7258,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="10" t="s">
         <v>465</v>
       </c>
@@ -7126,7 +7269,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>468</v>
       </c>
@@ -7137,7 +7280,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="10" t="s">
         <v>471</v>
       </c>
@@ -7148,7 +7291,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
         <v>474</v>
       </c>
@@ -7159,7 +7302,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="10" t="s">
         <v>477</v>
       </c>
@@ -7170,7 +7313,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
         <v>480</v>
       </c>
@@ -7181,7 +7324,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="10" t="s">
         <v>483</v>
       </c>
@@ -7192,7 +7335,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
         <v>486</v>
       </c>
@@ -7203,7 +7346,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="10" t="s">
         <v>489</v>
       </c>
@@ -7214,7 +7357,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
         <v>492</v>
       </c>
@@ -7225,7 +7368,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
         <v>495</v>
       </c>
@@ -7236,7 +7379,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
         <v>498</v>
       </c>
@@ -7247,7 +7390,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
         <v>501</v>
       </c>
@@ -7258,7 +7401,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
         <v>504</v>
       </c>
@@ -7269,7 +7412,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
         <v>507</v>
       </c>
@@ -7280,7 +7423,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
         <v>510</v>
       </c>
@@ -7291,7 +7434,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
         <v>513</v>
       </c>
@@ -7302,7 +7445,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
         <v>516</v>
       </c>
@@ -7313,7 +7456,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
         <v>519</v>
       </c>
@@ -7324,7 +7467,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
         <v>522</v>
       </c>
@@ -7335,7 +7478,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
         <v>525</v>
       </c>
@@ -7346,7 +7489,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
         <v>528</v>
       </c>
@@ -7357,7 +7500,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
         <v>531</v>
       </c>
@@ -7368,7 +7511,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
         <v>534</v>
       </c>
@@ -7379,7 +7522,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="10" t="s">
         <v>537</v>
       </c>
@@ -7390,7 +7533,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
         <v>540</v>
       </c>
@@ -7401,7 +7544,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="10" t="s">
         <v>543</v>
       </c>
@@ -7412,7 +7555,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>546</v>
       </c>
@@ -7423,7 +7566,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
         <v>549</v>
       </c>
@@ -7434,7 +7577,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
         <v>552</v>
       </c>
@@ -7445,7 +7588,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
         <v>555</v>
       </c>
@@ -7456,7 +7599,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
         <v>558</v>
       </c>
@@ -7467,7 +7610,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
         <v>561</v>
       </c>
@@ -7478,7 +7621,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
         <v>564</v>
       </c>
@@ -7489,7 +7632,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="10" t="s">
         <v>567</v>
       </c>
@@ -7500,7 +7643,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
         <v>570</v>
       </c>
@@ -7511,7 +7654,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="10" t="s">
         <v>573</v>
       </c>
@@ -7522,7 +7665,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
         <v>576</v>
       </c>
@@ -7533,7 +7676,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="10" t="s">
         <v>579</v>
       </c>
@@ -7544,7 +7687,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
         <v>582</v>
       </c>
@@ -7555,7 +7698,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="10" t="s">
         <v>585</v>
       </c>
@@ -7566,7 +7709,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
         <v>588</v>
       </c>
@@ -7577,7 +7720,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="10" t="s">
         <v>591</v>
       </c>
@@ -7588,7 +7731,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
         <v>594</v>
       </c>
@@ -7599,7 +7742,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="10" t="s">
         <v>597</v>
       </c>
@@ -7610,7 +7753,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
         <v>600</v>
       </c>
@@ -7621,7 +7764,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="10" t="s">
         <v>603</v>
       </c>
@@ -7632,7 +7775,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
         <v>606</v>
       </c>
@@ -7643,7 +7786,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
         <v>609</v>
       </c>
@@ -7654,7 +7797,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
         <v>612</v>
       </c>
@@ -7665,7 +7808,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
         <v>615</v>
       </c>
@@ -7676,7 +7819,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
         <v>618</v>
       </c>
@@ -7687,7 +7830,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="10" t="s">
         <v>621</v>
       </c>
@@ -7698,7 +7841,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
         <v>624</v>
       </c>
@@ -7709,7 +7852,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="10" t="s">
         <v>627</v>
       </c>
@@ -7720,7 +7863,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
         <v>630</v>
       </c>
@@ -7731,7 +7874,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
         <v>633</v>
       </c>
@@ -7742,7 +7885,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
         <v>636</v>
       </c>
@@ -7753,7 +7896,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="10" t="s">
         <v>639</v>
       </c>
@@ -7764,7 +7907,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
         <v>642</v>
       </c>
@@ -7775,7 +7918,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
         <v>645</v>
       </c>
@@ -7786,7 +7929,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
         <v>648</v>
       </c>
@@ -7797,7 +7940,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="10" t="s">
         <v>651</v>
       </c>
@@ -7808,7 +7951,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
         <v>654</v>
       </c>
@@ -7819,7 +7962,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="10" t="s">
         <v>657</v>
       </c>
@@ -7830,7 +7973,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
         <v>660</v>
       </c>
@@ -7841,7 +7984,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
         <v>663</v>
       </c>
@@ -7852,7 +7995,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
         <v>666</v>
       </c>
@@ -7863,7 +8006,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="10" t="s">
         <v>669</v>
       </c>
@@ -7874,7 +8017,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
         <v>672</v>
       </c>
@@ -7885,7 +8028,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
         <v>675</v>
       </c>
@@ -7896,7 +8039,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
         <v>678</v>
       </c>
@@ -7907,7 +8050,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="10" t="s">
         <v>681</v>
       </c>
@@ -7918,7 +8061,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
         <v>684</v>
       </c>
@@ -7929,7 +8072,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="10" t="s">
         <v>687</v>
       </c>
@@ -7940,7 +8083,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
         <v>690</v>
       </c>
@@ -7951,7 +8094,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="10" t="s">
         <v>693</v>
       </c>
@@ -7962,7 +8105,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
         <v>696</v>
       </c>
@@ -7973,7 +8116,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="10" t="s">
         <v>699</v>
       </c>
@@ -7984,7 +8127,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
         <v>702</v>
       </c>
@@ -7995,7 +8138,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="10" t="s">
         <v>705</v>
       </c>
@@ -8006,7 +8149,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
         <v>708</v>
       </c>
@@ -8017,7 +8160,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="10" t="s">
         <v>711</v>
       </c>
@@ -8028,7 +8171,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
         <v>714</v>
       </c>
@@ -8039,7 +8182,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="10" t="s">
         <v>717</v>
       </c>
@@ -8050,7 +8193,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
         <v>720</v>
       </c>
@@ -8061,7 +8204,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="10" t="s">
         <v>723</v>
       </c>
@@ -8072,7 +8215,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
         <v>726</v>
       </c>
@@ -8083,7 +8226,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="10" t="s">
         <v>729</v>
       </c>
@@ -8094,7 +8237,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
         <v>732</v>
       </c>
@@ -8105,7 +8248,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="10" t="s">
         <v>735</v>
       </c>
@@ -8116,7 +8259,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
         <v>738</v>
       </c>
@@ -8127,7 +8270,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="10" t="s">
         <v>741</v>
       </c>
@@ -8138,7 +8281,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
         <v>744</v>
       </c>
@@ -8149,7 +8292,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="10" t="s">
         <v>747</v>
       </c>
@@ -8160,7 +8303,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
         <v>750</v>
       </c>
@@ -8171,7 +8314,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="10" t="s">
         <v>753</v>
       </c>
@@ -8182,7 +8325,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
         <v>756</v>
       </c>
@@ -8193,7 +8336,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="10" t="s">
         <v>759</v>
       </c>
@@ -8204,7 +8347,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
         <v>762</v>
       </c>
@@ -8215,7 +8358,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
         <v>765</v>
       </c>
@@ -8226,7 +8369,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
         <v>768</v>
       </c>
@@ -8237,7 +8380,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="10" t="s">
         <v>771</v>
       </c>
@@ -8248,7 +8391,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
         <v>774</v>
       </c>
@@ -8259,7 +8402,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="10" t="s">
         <v>777</v>
       </c>
@@ -8270,7 +8413,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
         <v>780</v>
       </c>
@@ -8281,7 +8424,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
         <v>783</v>
       </c>
@@ -8292,7 +8435,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
         <v>786</v>
       </c>
@@ -8303,7 +8446,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
         <v>789</v>
       </c>
@@ -8314,7 +8457,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
         <v>792</v>
       </c>
@@ -8325,7 +8468,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
         <v>795</v>
       </c>
@@ -8336,7 +8479,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
         <v>798</v>
       </c>
@@ -8347,7 +8490,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="10" t="s">
         <v>801</v>
       </c>
@@ -8358,7 +8501,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
         <v>804</v>
       </c>
@@ -8369,7 +8512,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="10" t="s">
         <v>807</v>
       </c>
@@ -8380,7 +8523,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
         <v>810</v>
       </c>
@@ -8391,7 +8534,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
         <v>813</v>
       </c>
@@ -8402,7 +8545,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
         <v>816</v>
       </c>
@@ -8413,7 +8556,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="10" t="s">
         <v>819</v>
       </c>
@@ -8424,7 +8567,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
         <v>822</v>
       </c>
@@ -8435,7 +8578,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="10" t="s">
         <v>825</v>
       </c>
@@ -8446,7 +8589,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
         <v>828</v>
       </c>
@@ -8457,7 +8600,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="10" t="s">
         <v>831</v>
       </c>
@@ -8468,7 +8611,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
         <v>834</v>
       </c>
@@ -8479,7 +8622,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
         <v>837</v>
       </c>
@@ -8490,7 +8633,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
         <v>840</v>
       </c>
@@ -8501,7 +8644,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
         <v>843</v>
       </c>
@@ -8512,7 +8655,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
         <v>846</v>
       </c>
@@ -8523,7 +8666,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
         <v>849</v>
       </c>
@@ -8534,7 +8677,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
         <v>852</v>
       </c>
@@ -8545,7 +8688,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
         <v>855</v>
       </c>
@@ -8556,7 +8699,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
         <v>858</v>
       </c>
@@ -8567,7 +8710,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
         <v>861</v>
       </c>
@@ -8578,7 +8721,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
         <v>864</v>
       </c>
@@ -8589,7 +8732,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
         <v>867</v>
       </c>
@@ -8600,7 +8743,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
         <v>870</v>
       </c>
@@ -8611,7 +8754,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
         <v>873</v>
       </c>
@@ -8622,7 +8765,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
         <v>876</v>
       </c>
@@ -8650,13 +8793,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8664,7 +8807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8672,7 +8815,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8680,7 +8823,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8699,13 +8842,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="198.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="198.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8713,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8721,7 +8864,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8729,7 +8872,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8745,13 +8888,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="229.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="229.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8759,7 +8902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8767,7 +8910,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8775,7 +8918,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8791,13 +8934,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8805,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8813,7 +8956,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8829,13 +8972,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8843,7 +8986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8851,7 +8994,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8867,13 +9010,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8881,7 +9024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8889,7 +9032,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8905,13 +9048,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8919,7 +9062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8927,7 +9070,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8943,12 +9086,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+    <col min="2" max="2" width="125.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8956,7 +9099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -8964,7 +9107,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="330" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -8980,13 +9123,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8994,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9002,7 +9145,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9018,13 +9161,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9032,7 +9175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9040,7 +9183,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9056,13 +9199,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="152.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="152.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9070,7 +9213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -9078,7 +9221,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9086,7 +9229,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9102,13 +9245,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9116,7 +9259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9124,7 +9267,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9143,13 +9286,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9157,7 +9300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9165,7 +9308,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9181,13 +9324,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9195,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9203,7 +9346,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9219,13 +9362,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9233,7 +9376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9241,7 +9384,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9258,13 +9401,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9272,7 +9415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9280,7 +9423,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9288,7 +9431,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9296,7 +9439,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9310,13 +9453,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9324,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9332,7 +9475,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9340,7 +9483,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9348,7 +9491,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9361,13 +9504,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9375,7 +9518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9383,7 +9526,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9391,7 +9534,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9399,7 +9542,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9412,13 +9555,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9426,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9434,7 +9577,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9442,7 +9585,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9450,7 +9593,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9466,13 +9609,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9480,7 +9623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9488,7 +9631,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9496,7 +9639,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9504,7 +9647,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9517,13 +9660,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9531,7 +9674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9539,7 +9682,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9547,7 +9690,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9555,7 +9698,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9568,13 +9711,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="253.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="253.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9582,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -9590,7 +9733,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9598,7 +9741,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9614,13 +9757,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9628,7 +9771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9636,7 +9779,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9644,7 +9787,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9652,7 +9795,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9665,13 +9808,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9679,7 +9822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9687,7 +9830,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9695,7 +9838,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9703,7 +9846,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9716,13 +9859,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9730,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9738,7 +9881,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9746,7 +9889,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9754,7 +9897,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9767,13 +9910,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9781,7 +9924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9789,7 +9932,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9797,7 +9940,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9805,7 +9948,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9818,13 +9961,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="199.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="199.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9832,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9840,7 +9983,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9848,7 +9991,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9856,7 +9999,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9872,13 +10015,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9886,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -9902,13 +10045,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9916,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -9932,13 +10075,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9946,7 +10089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -9962,13 +10105,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9976,7 +10119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -9992,13 +10135,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10006,7 +10149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10022,13 +10165,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="223.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="223.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10036,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10044,7 +10187,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10052,7 +10195,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10068,13 +10211,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10082,7 +10225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10098,13 +10241,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10112,7 +10255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10128,13 +10271,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10142,7 +10285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10158,13 +10301,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10172,7 +10315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10188,13 +10331,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10202,7 +10345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10218,13 +10361,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10232,7 +10375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10251,13 +10394,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10265,20 +10408,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>994</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7DC1EE-86C5-4108-AF46-1519F3819416}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="345" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="405" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC14161-2EAA-48CD-8103-6BBBB2474891}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432DB22F-F7FA-4CA9-A149-B4C592E95431}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="375" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -10289,13 +10517,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="181.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10303,7 +10531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10311,7 +10539,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10319,7 +10547,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10329,19 +10557,199 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C770D3C-EBB7-4325-A0BF-2D0A464BBA81}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94F2EB0-C540-42F2-9029-153D236879E0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174F19C-D9CC-4AA4-AC39-2264F751CA4E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="405" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="360" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1F98BC-569D-4E63-A11C-5D8C488EFFA3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872AC014-EDC6-46B6-9F04-A4A110CE1015}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="300" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DCF04D-F322-424A-ABB9-6A9DCAD730DC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82D4A72-6C09-4E6C-AC1C-1FD3518043C3}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="222.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="222.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10349,7 +10757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10357,7 +10765,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10365,7 +10773,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10381,13 +10789,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="137.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="137.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10395,7 +10803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10403,7 +10811,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10411,7 +10819,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10419,13 +10827,13 @@
         <v>896</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10436,13 +10844,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="135.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="135.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10450,7 +10858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10458,7 +10866,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10466,7 +10874,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10482,13 +10890,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="114.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="114.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10496,7 +10904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10504,7 +10912,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10512,7 +10920,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarah.weisberg\fisheriesXplorer\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFD5F8A-D9AA-47A8-A631-653F2A1435F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7F0096-B5B7-4580-8B77-0320AEEE864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48225" yWindow="-2955" windowWidth="39150" windowHeight="18105" tabRatio="858" firstSheet="34" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="41" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="1011">
   <si>
     <t>section</t>
   </si>
@@ -4873,6 +4873,9 @@
 &lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
 &lt;p&gt;
 Multiannual bycatch rates were estimated for 2 marine turtle species (2 métier–species combinations). The highest bycatch rate was estimated for loggerhead turtle in drifting longlines followed by leatherback turtle in drifting longlines. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>No bycatch advice available for this ecoregion.</t>
   </si>
 </sst>
 </file>
@@ -4975,7 +4978,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5004,9 +5007,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5313,16 +5313,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.7265625" customWidth="1"/>
+    <col min="17" max="17" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>26</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>40</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>928</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>931</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>934</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>937</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>940</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>943</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>946</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>949</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>46</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>952</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>955</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>958</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>961</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>964</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>20</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>28</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>24</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>967</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>970</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>973</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>976</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>979</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>982</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>985</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>988</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>36</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>991</v>
       </c>
@@ -5751,7 +5751,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>30</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>34</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>44</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>63</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>69</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>72</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>78</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
         <v>81</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
         <v>87</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>90</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>96</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>102</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>108</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>111</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="10" t="s">
         <v>117</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
         <v>123</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>126</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>129</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>135</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
         <v>141</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>144</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>150</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>156</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>159</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>162</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
         <v>165</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>168</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>171</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>174</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>177</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>180</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>183</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>186</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>189</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>192</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>195</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>198</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
         <v>201</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>204</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
         <v>207</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>210</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>213</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>216</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>219</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>222</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>225</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>231</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>234</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>237</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>240</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="10" t="s">
         <v>243</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>246</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="10" t="s">
         <v>249</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>252</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
         <v>255</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>258</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>264</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
         <v>267</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>270</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>273</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>276</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
         <v>279</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>282</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
         <v>285</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>288</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>291</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>294</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>297</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
         <v>300</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>303</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>306</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="10" t="s">
         <v>309</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>312</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>315</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>318</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>321</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>324</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>327</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>330</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>333</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>336</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>339</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>342</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="10" t="s">
         <v>345</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>348</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>351</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>354</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="10" t="s">
         <v>357</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>360</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="10" t="s">
         <v>363</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
         <v>366</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="10" t="s">
         <v>369</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>372</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>375</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>378</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="10" t="s">
         <v>381</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>384</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
         <v>387</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>390</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
         <v>393</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
         <v>396</v>
       </c>
@@ -7016,7 +7016,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
         <v>402</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="10" t="s">
         <v>405</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="10" t="s">
         <v>411</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
         <v>414</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="10" t="s">
         <v>417</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
         <v>420</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="10" t="s">
         <v>423</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
         <v>426</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="10" t="s">
         <v>429</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
         <v>432</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="10" t="s">
         <v>435</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="10" t="s">
         <v>441</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
         <v>444</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="10" t="s">
         <v>447</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>450</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="10" t="s">
         <v>453</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>456</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="10" t="s">
         <v>459</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>462</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="10" t="s">
         <v>465</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
         <v>468</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="10" t="s">
         <v>471</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
         <v>474</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="10" t="s">
         <v>477</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>480</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="10" t="s">
         <v>483</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>486</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="10" t="s">
         <v>489</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>492</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="10" t="s">
         <v>495</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>498</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="10" t="s">
         <v>501</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>504</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="10" t="s">
         <v>507</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>510</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="10" t="s">
         <v>513</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
         <v>516</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="10" t="s">
         <v>519</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
         <v>522</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="10" t="s">
         <v>525</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
         <v>528</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="10" t="s">
         <v>531</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>534</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="10" t="s">
         <v>537</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>540</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="10" t="s">
         <v>543</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>546</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="10" t="s">
         <v>549</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
         <v>552</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="10" t="s">
         <v>555</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>558</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="10" t="s">
         <v>561</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
         <v>564</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="10" t="s">
         <v>567</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>570</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="10" t="s">
         <v>573</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>576</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="10" t="s">
         <v>579</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>582</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="10" t="s">
         <v>585</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>588</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="10" t="s">
         <v>591</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>594</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="10" t="s">
         <v>597</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>600</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="10" t="s">
         <v>603</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>606</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>609</v>
       </c>
@@ -7797,7 +7797,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>612</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>615</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>618</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>621</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>624</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>627</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>630</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
         <v>633</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>636</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>639</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>642</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>645</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>648</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
         <v>651</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
         <v>654</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="10" t="s">
         <v>657</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="10" t="s">
         <v>660</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="10" t="s">
         <v>663</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="10" t="s">
         <v>666</v>
       </c>
@@ -8006,7 +8006,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="10" t="s">
         <v>669</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="10" t="s">
         <v>672</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="10" t="s">
         <v>675</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="10" t="s">
         <v>678</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="10" t="s">
         <v>681</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="10" t="s">
         <v>684</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="10" t="s">
         <v>687</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="10" t="s">
         <v>690</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="10" t="s">
         <v>693</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="10" t="s">
         <v>696</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="10" t="s">
         <v>699</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="10" t="s">
         <v>702</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="10" t="s">
         <v>705</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="10" t="s">
         <v>708</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="10" t="s">
         <v>711</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="10" t="s">
         <v>714</v>
       </c>
@@ -8182,7 +8182,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" s="10" t="s">
         <v>717</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="10" t="s">
         <v>720</v>
       </c>
@@ -8204,7 +8204,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="10" t="s">
         <v>723</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="10" t="s">
         <v>726</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="10" t="s">
         <v>729</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="10" t="s">
         <v>732</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="10" t="s">
         <v>735</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="10" t="s">
         <v>738</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="10" t="s">
         <v>741</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="10" t="s">
         <v>744</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="10" t="s">
         <v>747</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="10" t="s">
         <v>750</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="10" t="s">
         <v>753</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="10" t="s">
         <v>756</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="10" t="s">
         <v>759</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="10" t="s">
         <v>762</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="10" t="s">
         <v>765</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="10" t="s">
         <v>768</v>
       </c>
@@ -8380,7 +8380,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="10" t="s">
         <v>771</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="10" t="s">
         <v>774</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="10" t="s">
         <v>777</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="10" t="s">
         <v>780</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="10" t="s">
         <v>783</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="10" t="s">
         <v>786</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="10" t="s">
         <v>789</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="10" t="s">
         <v>792</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="10" t="s">
         <v>795</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="10" t="s">
         <v>798</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="10" t="s">
         <v>801</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="10" t="s">
         <v>804</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="10" t="s">
         <v>807</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="10" t="s">
         <v>810</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" s="10" t="s">
         <v>813</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" s="10" t="s">
         <v>816</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" s="10" t="s">
         <v>819</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" s="10" t="s">
         <v>822</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" s="10" t="s">
         <v>825</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" s="10" t="s">
         <v>828</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" s="10" t="s">
         <v>831</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" s="10" t="s">
         <v>834</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" s="10" t="s">
         <v>837</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" s="10" t="s">
         <v>840</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" s="10" t="s">
         <v>843</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" s="10" t="s">
         <v>846</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" s="10" t="s">
         <v>849</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" s="10" t="s">
         <v>852</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" s="10" t="s">
         <v>855</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" s="10" t="s">
         <v>858</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" s="10" t="s">
         <v>861</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" s="10" t="s">
         <v>864</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" s="10" t="s">
         <v>867</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" s="10" t="s">
         <v>870</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" s="10" t="s">
         <v>873</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" s="10" t="s">
         <v>876</v>
       </c>
@@ -8793,13 +8793,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8842,13 +8842,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="198.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="198.26953125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8888,13 +8888,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="229.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="229.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -8934,13 +8934,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -8972,13 +8972,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9010,13 +9010,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9048,13 +9048,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9086,12 +9086,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="125.5703125" customWidth="1"/>
+    <col min="2" max="2" width="125.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -9123,13 +9123,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9161,13 +9161,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9199,13 +9199,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="152.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="152.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9245,13 +9245,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9286,13 +9286,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9324,13 +9324,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9362,13 +9362,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9376,7 +9376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -9401,13 +9401,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9453,13 +9453,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9504,13 +9504,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9555,13 +9555,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9609,13 +9609,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9631,7 +9631,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9660,13 +9660,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9711,13 +9711,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="253.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="253.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -9741,7 +9741,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -9757,13 +9757,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9779,7 +9779,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9808,13 +9808,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9859,13 +9859,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9910,13 +9910,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -9961,13 +9961,13 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="199.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="199.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9975,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>881</v>
       </c>
@@ -9983,7 +9983,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>902</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>903</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>904</v>
       </c>
@@ -10015,13 +10015,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10045,13 +10045,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10075,13 +10075,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10105,13 +10105,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10135,13 +10135,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10165,13 +10165,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="223.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="223.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10211,13 +10211,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10241,13 +10241,13 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10255,7 +10255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10271,13 +10271,13 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10301,13 +10301,13 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10331,13 +10331,13 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10361,13 +10361,13 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>917</v>
       </c>
@@ -10394,13 +10394,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10432,13 +10432,13 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7DC1EE-86C5-4108-AF46-1519F3819416}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="345" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="405" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10469,9 +10469,38 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC14161-2EAA-48CD-8103-6BBBB2474891}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10479,13 +10508,13 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432DB22F-F7FA-4CA9-A149-B4C592E95431}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10493,7 +10522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -10501,7 +10530,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="375" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10517,13 +10546,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="181.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="181.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10531,7 +10560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10539,7 +10568,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10547,7 +10576,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10563,13 +10592,13 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C770D3C-EBB7-4325-A0BF-2D0A464BBA81}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10577,7 +10606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="377" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -10585,7 +10614,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="406" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10600,9 +10629,38 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94F2EB0-C540-42F2-9029-153D236879E0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10610,13 +10668,13 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174F19C-D9CC-4AA4-AC39-2264F751CA4E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10624,7 +10682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="405" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
@@ -10632,7 +10690,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="360" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="348" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10647,9 +10705,37 @@
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1F98BC-569D-4E63-A11C-5D8C488EFFA3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="35.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10657,13 +10743,13 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872AC014-EDC6-46B6-9F04-A4A110CE1015}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10671,15 +10757,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="330" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="319" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="300" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="290" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10694,9 +10780,38 @@
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DCF04D-F322-424A-ABB9-6A9DCAD730DC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10704,13 +10819,13 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82D4A72-6C09-4E6C-AC1C-1FD3518043C3}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10718,15 +10833,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="290" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>994</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
@@ -10743,13 +10858,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="222.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="222.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10757,7 +10872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10765,7 +10880,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10773,7 +10888,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10789,13 +10904,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="137.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="137.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10803,7 +10918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="393.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10811,7 +10926,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10819,7 +10934,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10827,13 +10942,13 @@
         <v>896</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
     </row>
   </sheetData>
@@ -10844,13 +10959,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="135.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="135.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10858,7 +10973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10866,7 +10981,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10874,7 +10989,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -10890,13 +11005,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="114.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="114.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10904,7 +11019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
@@ -10912,7 +11027,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -10920,7 +11035,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7F0096-B5B7-4580-8B77-0320AEEE864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E590FAB-0618-4FA5-B28E-C9CB7538FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" firstSheet="41" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="41" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="glossary" sheetId="17" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="1013">
   <si>
     <t>section</t>
   </si>
@@ -4876,6 +4876,26 @@
   </si>
   <si>
     <t>No bycatch advice available for this ecoregion.</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Barents Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch rate estimates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;   
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 3 marine mammal species in one métier. The highest bycatch rate was estimated for harbor seal in set gillnets, followed by harbor porpoise in set gillnets and grey seal in set gillnets. &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;Bycatch of endangered, threatened and protected species&lt;/h4&gt;
+&lt;p&gt;
+All fisheries have the potential to catch endangered, protected and threatened (ETP) species as non-targeted bycatch. The list of ETP marine mammal, seabird, fish and marine turtle species of bycatch relevance for the Norwegian Sea ecoregion can be found in &lt;a href = "https://doi.org/10.17895/ices.pub.31245037" target = "_blank"&gt;  ICES Roadmap &lt;/a&gt;.  For 2024 ICES provides bycatch estimates on marine mammals and seabirds and bycatch rates for marine mammals and seabirds. Due to data limitation ICES estimates bycatch only for certain species and métier combinations.  See&lt;a href = "https://doi.org/10.17895/ices.advice.30734714" target = "_blank"&gt;  ICES (2025) &lt;/a&gt; for more details
+&lt;/p&gt;   
+&lt;h4&gt;Bycatch rate estimates&lt;/h4&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 3 marine mammal species in one métier. The highest bycatch rate was estimated for harbor porpoise in set gillnets, followed by harbor seal in set gillnets and grey seal in set gillnets. &lt;/p&gt;
+&lt;p&gt;
+Multiannual bycatch rates were estimated for 5 seabird species in one métier. The highest bycatch rate was estimated for northern fulmar in set gillnets, followed by common guillemot in set gillnets and razorbill in set gillnets.  &lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -10435,7 +10455,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -10492,12 +10512,12 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -10803,12 +10823,12 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="232" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>995</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/texts.xlsx
+++ b/data-raw/texts.xlsx
@@ -1,74 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2023\fisheriesXplorer\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E590FAB-0618-4FA5-B28E-C9CB7538FE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E67168F-AD47-4301-8020-C33B61F3F315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="858" firstSheet="41" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30720" yWindow="360" windowWidth="61332" windowHeight="15300" tabRatio="858" firstSheet="21" activeTab="55" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="glossary" sheetId="17" r:id="rId1"/>
-    <sheet name="overview_AZ" sheetId="8" r:id="rId2"/>
-    <sheet name="overview_BI" sheetId="9" r:id="rId3"/>
-    <sheet name="overview_BrS" sheetId="10" r:id="rId4"/>
-    <sheet name="overview_BtS" sheetId="11" r:id="rId5"/>
-    <sheet name="overview_CS" sheetId="12" r:id="rId6"/>
-    <sheet name="overview_FO" sheetId="13" r:id="rId7"/>
-    <sheet name="overview_IS" sheetId="15" r:id="rId8"/>
-    <sheet name="overview_GS" sheetId="14" r:id="rId9"/>
-    <sheet name="overview_NrS" sheetId="1" r:id="rId10"/>
-    <sheet name="overview_NwS" sheetId="2" r:id="rId11"/>
-    <sheet name="overview_ONA" sheetId="16" r:id="rId12"/>
-    <sheet name="landings_discards_AZ" sheetId="20" r:id="rId13"/>
-    <sheet name="landings_discards_BI" sheetId="21" r:id="rId14"/>
-    <sheet name="landings_discards_BrS" sheetId="22" r:id="rId15"/>
-    <sheet name="landings_discards_BtS" sheetId="23" r:id="rId16"/>
-    <sheet name="landings_discards_CS" sheetId="18" r:id="rId17"/>
-    <sheet name="landings_discards_FO" sheetId="24" r:id="rId18"/>
-    <sheet name="landings_discards_IS" sheetId="25" r:id="rId19"/>
-    <sheet name="landings_discards_GS" sheetId="26" r:id="rId20"/>
-    <sheet name="landings_discards_NrS" sheetId="3" r:id="rId21"/>
-    <sheet name="landings_discards_NwS" sheetId="19" r:id="rId22"/>
-    <sheet name="landings_discards_ONA" sheetId="27" r:id="rId23"/>
-    <sheet name="status_AZ" sheetId="28" r:id="rId24"/>
-    <sheet name="status_BI" sheetId="29" r:id="rId25"/>
-    <sheet name="status_BrS" sheetId="30" r:id="rId26"/>
-    <sheet name="status_BtS" sheetId="31" r:id="rId27"/>
-    <sheet name="status_CS" sheetId="4" r:id="rId28"/>
-    <sheet name="status_FO" sheetId="32" r:id="rId29"/>
-    <sheet name="status_IS" sheetId="33" r:id="rId30"/>
-    <sheet name="status_GS" sheetId="34" r:id="rId31"/>
-    <sheet name="status_NrS" sheetId="35" r:id="rId32"/>
-    <sheet name="status_NwS" sheetId="36" r:id="rId33"/>
-    <sheet name="status_ONA" sheetId="37" r:id="rId34"/>
-    <sheet name="vms_AZ" sheetId="6" r:id="rId35"/>
-    <sheet name="vms_BI" sheetId="38" r:id="rId36"/>
-    <sheet name="vms_BrS" sheetId="39" r:id="rId37"/>
-    <sheet name="vms_BtS" sheetId="40" r:id="rId38"/>
-    <sheet name="vms_CS" sheetId="41" r:id="rId39"/>
-    <sheet name="vms_FO" sheetId="42" r:id="rId40"/>
-    <sheet name="vms_IS" sheetId="43" r:id="rId41"/>
-    <sheet name="vms_GS" sheetId="44" r:id="rId42"/>
-    <sheet name="vms_NrS" sheetId="45" r:id="rId43"/>
-    <sheet name="vms_NwS" sheetId="46" r:id="rId44"/>
-    <sheet name="vms_ONA" sheetId="47" r:id="rId45"/>
-    <sheet name="bycatch_AZ" sheetId="49" r:id="rId46"/>
-    <sheet name="bycatch_BI" sheetId="50" r:id="rId47"/>
-    <sheet name="bycatch_BrS" sheetId="51" r:id="rId48"/>
-    <sheet name="bycatch_BtS" sheetId="52" r:id="rId49"/>
-    <sheet name="bycatch_CS" sheetId="53" r:id="rId50"/>
-    <sheet name="bycatch_FO" sheetId="54" r:id="rId51"/>
-    <sheet name="bycatch_IS" sheetId="55" r:id="rId52"/>
-    <sheet name="bycatch_GS" sheetId="56" r:id="rId53"/>
-    <sheet name="bycatch_NrS" sheetId="57" r:id="rId54"/>
-    <sheet name="bycatch_NwS" sheetId="58" r:id="rId55"/>
-    <sheet name="bycatch_ONA" sheetId="59" r:id="rId56"/>
+    <sheet name="overview_AZ" sheetId="8" r:id="rId1"/>
+    <sheet name="overview_BI" sheetId="9" r:id="rId2"/>
+    <sheet name="overview_BrS" sheetId="10" r:id="rId3"/>
+    <sheet name="overview_BtS" sheetId="11" r:id="rId4"/>
+    <sheet name="overview_CS" sheetId="12" r:id="rId5"/>
+    <sheet name="overview_FO" sheetId="13" r:id="rId6"/>
+    <sheet name="overview_IS" sheetId="15" r:id="rId7"/>
+    <sheet name="overview_GS" sheetId="14" r:id="rId8"/>
+    <sheet name="overview_NrS" sheetId="1" r:id="rId9"/>
+    <sheet name="overview_NwS" sheetId="2" r:id="rId10"/>
+    <sheet name="overview_ONA" sheetId="16" r:id="rId11"/>
+    <sheet name="landings_discards_AZ" sheetId="20" r:id="rId12"/>
+    <sheet name="landings_discards_BI" sheetId="21" r:id="rId13"/>
+    <sheet name="landings_discards_BrS" sheetId="22" r:id="rId14"/>
+    <sheet name="landings_discards_BtS" sheetId="23" r:id="rId15"/>
+    <sheet name="landings_discards_CS" sheetId="18" r:id="rId16"/>
+    <sheet name="landings_discards_FO" sheetId="24" r:id="rId17"/>
+    <sheet name="landings_discards_IS" sheetId="25" r:id="rId18"/>
+    <sheet name="landings_discards_GS" sheetId="26" r:id="rId19"/>
+    <sheet name="landings_discards_NrS" sheetId="3" r:id="rId20"/>
+    <sheet name="landings_discards_NwS" sheetId="19" r:id="rId21"/>
+    <sheet name="landings_discards_ONA" sheetId="27" r:id="rId22"/>
+    <sheet name="status_AZ" sheetId="28" r:id="rId23"/>
+    <sheet name="status_BI" sheetId="29" r:id="rId24"/>
+    <sheet name="status_BrS" sheetId="30" r:id="rId25"/>
+    <sheet name="status_BtS" sheetId="31" r:id="rId26"/>
+    <sheet name="status_CS" sheetId="4" r:id="rId27"/>
+    <sheet name="status_FO" sheetId="32" r:id="rId28"/>
+    <sheet name="status_IS" sheetId="33" r:id="rId29"/>
+    <sheet name="status_GS" sheetId="34" r:id="rId30"/>
+    <sheet name="status_NrS" sheetId="35" r:id="rId31"/>
+    <sheet name="status_NwS" sheetId="36" r:id="rId32"/>
+    <sheet name="status_ONA" sheetId="37" r:id="rId33"/>
+    <sheet name="vms_AZ" sheetId="6" r:id="rId34"/>
+    <sheet name="vms_BI" sheetId="38" r:id="rId35"/>
+    <sheet name="vms_BrS" sheetId="39" r:id="rId36"/>
+    <sheet name="vms_BtS" sheetId="40" r:id="rId37"/>
+    <sheet name="vms_CS" sheetId="41" r:id="rId38"/>
+    <sheet name="vms_FO" sheetId="42" r:id="rId39"/>
+    <sheet name="vms_IS" sheetId="43" r:id="rId40"/>
+    <sheet name="vms_GS" sheetId="44" r:id="rId41"/>
+    <sheet name="vms_NrS" sheetId="45" r:id="rId42"/>
+    <sheet name="vms_NwS" sheetId="46" r:id="rId43"/>
+    <sheet name="vms_ONA" sheetId="47" r:id="rId44"/>
+    <sheet name="bycatch_AZ" sheetId="49" r:id="rId45"/>
+    <sheet name="bycatch_BI" sheetId="50" r:id="rId46"/>
+    <sheet name="bycatch_BrS" sheetId="51" r:id="rId47"/>
+    <sheet name="bycatch_BtS" sheetId="52" r:id="rId48"/>
+    <sheet name="bycatch_CS" sheetId="53" r:id="rId49"/>
+    <sheet name="bycatch_FO" sheetId="54" r:id="rId50"/>
+    <sheet name="bycatch_IS" sheetId="55" r:id="rId51"/>
+    <sheet name="bycatch_GS" sheetId="56" r:id="rId52"/>
+    <sheet name="bycatch_NrS" sheetId="57" r:id="rId53"/>
+    <sheet name="bycatch_NwS" sheetId="58" r:id="rId54"/>
+    <sheet name="bycatch_ONA" sheetId="59" r:id="rId55"/>
+    <sheet name="glossary" sheetId="17" r:id="rId56"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -5331,18 +5331,2083 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="152.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>882</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="198.21875" style="4" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>892</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="229.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>899</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="125.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>913</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="253.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="223.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="199.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>903</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="181.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>895</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE61185-CF8B-43DA-9230-D26A514F1564}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="271.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7DC1EE-86C5-4108-AF46-1519F3819416}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC14161-2EAA-48CD-8103-6BBBB2474891}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432DB22F-F7FA-4CA9-A149-B4C592E95431}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="360" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C770D3C-EBB7-4325-A0BF-2D0A464BBA81}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="222.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94F2EB0-C540-42F2-9029-153D236879E0}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174F19C-D9CC-4AA4-AC39-2264F751CA4E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1F98BC-569D-4E63-A11C-5D8C488EFFA3}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872AC014-EDC6-46B6-9F04-A4A110CE1015}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="288" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DCF04D-F322-424A-ABB9-6A9DCAD730DC}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82D4A72-6C09-4E6C-AC1C-1FD3518043C3}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>995</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4FE-E411-4E36-B8C3-47DB4028DB0F}">
   <dimension ref="A1:C314"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="168.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.7265625" customWidth="1"/>
-    <col min="17" max="17" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="168.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.77734375" customWidth="1"/>
+    <col min="17" max="17" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5353,7 +7418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>26</v>
       </c>
@@ -5364,7 +7429,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>40</v>
       </c>
@@ -5375,7 +7440,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -5386,7 +7451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -5397,7 +7462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>928</v>
       </c>
@@ -5408,7 +7473,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -5419,7 +7484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -5430,7 +7495,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -5441,7 +7506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -5452,7 +7517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>931</v>
       </c>
@@ -5463,7 +7528,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>934</v>
       </c>
@@ -5474,7 +7539,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>937</v>
       </c>
@@ -5485,7 +7550,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>940</v>
       </c>
@@ -5496,7 +7561,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>943</v>
       </c>
@@ -5507,7 +7572,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>946</v>
       </c>
@@ -5518,7 +7583,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>949</v>
       </c>
@@ -5529,7 +7594,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>46</v>
       </c>
@@ -5540,7 +7605,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>15</v>
       </c>
@@ -5551,7 +7616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>952</v>
       </c>
@@ -5562,7 +7627,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>955</v>
       </c>
@@ -5573,7 +7638,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>958</v>
       </c>
@@ -5584,7 +7649,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>961</v>
       </c>
@@ -5595,7 +7660,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
@@ -5606,7 +7671,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>964</v>
       </c>
@@ -5617,7 +7682,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>20</v>
       </c>
@@ -5628,7 +7693,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
@@ -5639,7 +7704,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>28</v>
       </c>
@@ -5650,7 +7715,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>24</v>
       </c>
@@ -5661,7 +7726,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>967</v>
       </c>
@@ -5672,7 +7737,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>970</v>
       </c>
@@ -5683,7 +7748,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>973</v>
       </c>
@@ -5694,7 +7759,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>976</v>
       </c>
@@ -5705,7 +7770,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>979</v>
       </c>
@@ -5716,7 +7781,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>982</v>
       </c>
@@ -5727,7 +7792,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>985</v>
       </c>
@@ -5738,7 +7803,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>988</v>
       </c>
@@ -5749,7 +7814,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>36</v>
       </c>
@@ -5760,7 +7825,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>991</v>
       </c>
@@ -5771,7 +7836,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>30</v>
       </c>
@@ -5782,7 +7847,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>34</v>
       </c>
@@ -5793,7 +7858,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>44</v>
       </c>
@@ -5804,7 +7869,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>63</v>
       </c>
@@ -5815,7 +7880,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
@@ -5826,7 +7891,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>69</v>
       </c>
@@ -5837,7 +7902,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>72</v>
       </c>
@@ -5848,7 +7913,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
@@ -5859,7 +7924,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>78</v>
       </c>
@@ -5870,7 +7935,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>81</v>
       </c>
@@ -5881,7 +7946,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>84</v>
       </c>
@@ -5892,7 +7957,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>87</v>
       </c>
@@ -5903,7 +7968,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>90</v>
       </c>
@@ -5914,7 +7979,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -5925,7 +7990,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>96</v>
       </c>
@@ -5936,7 +8001,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>99</v>
       </c>
@@ -5947,7 +8012,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>102</v>
       </c>
@@ -5958,7 +8023,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>105</v>
       </c>
@@ -5969,7 +8034,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>108</v>
       </c>
@@ -5980,7 +8045,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>111</v>
       </c>
@@ -5991,7 +8056,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
@@ -6002,7 +8067,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>117</v>
       </c>
@@ -6013,7 +8078,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
@@ -6024,7 +8089,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>123</v>
       </c>
@@ -6035,7 +8100,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>126</v>
       </c>
@@ -6046,7 +8111,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>129</v>
       </c>
@@ -6057,7 +8122,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
@@ -6068,7 +8133,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>135</v>
       </c>
@@ -6079,7 +8144,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -6090,7 +8155,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>141</v>
       </c>
@@ -6101,7 +8166,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>144</v>
       </c>
@@ -6112,7 +8177,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
@@ -6123,7 +8188,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>150</v>
       </c>
@@ -6134,7 +8199,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>153</v>
       </c>
@@ -6145,7 +8210,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>156</v>
       </c>
@@ -6156,7 +8221,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>159</v>
       </c>
@@ -6167,7 +8232,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>162</v>
       </c>
@@ -6178,7 +8243,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>165</v>
       </c>
@@ -6189,7 +8254,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>168</v>
       </c>
@@ -6200,7 +8265,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>171</v>
       </c>
@@ -6211,7 +8276,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>174</v>
       </c>
@@ -6222,7 +8287,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>177</v>
       </c>
@@ -6233,7 +8298,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>180</v>
       </c>
@@ -6244,7 +8309,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>183</v>
       </c>
@@ -6255,7 +8320,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>186</v>
       </c>
@@ -6266,7 +8331,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>189</v>
       </c>
@@ -6277,7 +8342,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>192</v>
       </c>
@@ -6288,7 +8353,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>195</v>
       </c>
@@ -6299,7 +8364,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>198</v>
       </c>
@@ -6310,7 +8375,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
         <v>201</v>
       </c>
@@ -6321,7 +8386,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>204</v>
       </c>
@@ -6332,7 +8397,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>207</v>
       </c>
@@ -6343,7 +8408,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>210</v>
       </c>
@@ -6354,7 +8419,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>213</v>
       </c>
@@ -6365,7 +8430,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>216</v>
       </c>
@@ -6376,7 +8441,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>219</v>
       </c>
@@ -6387,7 +8452,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>222</v>
       </c>
@@ -6398,7 +8463,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
         <v>225</v>
       </c>
@@ -6409,7 +8474,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>228</v>
       </c>
@@ -6420,7 +8485,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>231</v>
       </c>
@@ -6431,7 +8496,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>234</v>
       </c>
@@ -6442,7 +8507,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>237</v>
       </c>
@@ -6453,7 +8518,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>240</v>
       </c>
@@ -6464,7 +8529,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>243</v>
       </c>
@@ -6475,7 +8540,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>246</v>
       </c>
@@ -6486,7 +8551,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>249</v>
       </c>
@@ -6497,7 +8562,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>252</v>
       </c>
@@ -6508,7 +8573,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>255</v>
       </c>
@@ -6519,7 +8584,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>258</v>
       </c>
@@ -6530,7 +8595,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>261</v>
       </c>
@@ -6541,7 +8606,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>264</v>
       </c>
@@ -6552,7 +8617,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>267</v>
       </c>
@@ -6563,7 +8628,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>270</v>
       </c>
@@ -6574,7 +8639,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>273</v>
       </c>
@@ -6585,7 +8650,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>276</v>
       </c>
@@ -6596,7 +8661,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>279</v>
       </c>
@@ -6607,7 +8672,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>282</v>
       </c>
@@ -6618,7 +8683,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>285</v>
       </c>
@@ -6629,7 +8694,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
         <v>288</v>
       </c>
@@ -6640,7 +8705,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
         <v>291</v>
       </c>
@@ -6651,7 +8716,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>294</v>
       </c>
@@ -6662,7 +8727,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
         <v>297</v>
       </c>
@@ -6673,7 +8738,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>300</v>
       </c>
@@ -6684,7 +8749,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>303</v>
       </c>
@@ -6695,7 +8760,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>306</v>
       </c>
@@ -6706,7 +8771,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
         <v>309</v>
       </c>
@@ -6717,7 +8782,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
         <v>312</v>
       </c>
@@ -6728,7 +8793,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
         <v>315</v>
       </c>
@@ -6739,7 +8804,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
         <v>318</v>
       </c>
@@ -6750,7 +8815,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
         <v>321</v>
       </c>
@@ -6761,7 +8826,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
         <v>324</v>
       </c>
@@ -6772,7 +8837,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>327</v>
       </c>
@@ -6783,7 +8848,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
         <v>330</v>
       </c>
@@ -6794,7 +8859,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
         <v>333</v>
       </c>
@@ -6805,7 +8870,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
         <v>336</v>
       </c>
@@ -6816,7 +8881,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
         <v>339</v>
       </c>
@@ -6827,7 +8892,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
         <v>342</v>
       </c>
@@ -6838,7 +8903,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
         <v>345</v>
       </c>
@@ -6849,7 +8914,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
         <v>348</v>
       </c>
@@ -6860,7 +8925,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
         <v>351</v>
       </c>
@@ -6871,7 +8936,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="10" t="s">
         <v>354</v>
       </c>
@@ -6882,7 +8947,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="10" t="s">
         <v>357</v>
       </c>
@@ -6893,7 +8958,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="10" t="s">
         <v>360</v>
       </c>
@@ -6904,7 +8969,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="10" t="s">
         <v>363</v>
       </c>
@@ -6915,7 +8980,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="10" t="s">
         <v>366</v>
       </c>
@@ -6926,7 +8991,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="10" t="s">
         <v>369</v>
       </c>
@@ -6937,7 +9002,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="10" t="s">
         <v>372</v>
       </c>
@@ -6948,7 +9013,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
         <v>375</v>
       </c>
@@ -6959,7 +9024,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
         <v>378</v>
       </c>
@@ -6970,7 +9035,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="10" t="s">
         <v>381</v>
       </c>
@@ -6981,7 +9046,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
         <v>384</v>
       </c>
@@ -6992,7 +9057,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
         <v>387</v>
       </c>
@@ -7003,7 +9068,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="10" t="s">
         <v>390</v>
       </c>
@@ -7014,7 +9079,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="10" t="s">
         <v>393</v>
       </c>
@@ -7025,7 +9090,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="10" t="s">
         <v>396</v>
       </c>
@@ -7036,7 +9101,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
         <v>399</v>
       </c>
@@ -7047,7 +9112,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
         <v>402</v>
       </c>
@@ -7058,7 +9123,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="10" t="s">
         <v>405</v>
       </c>
@@ -7069,7 +9134,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
@@ -7080,7 +9145,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="10" t="s">
         <v>411</v>
       </c>
@@ -7091,7 +9156,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="10" t="s">
         <v>414</v>
       </c>
@@ -7102,7 +9167,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
         <v>417</v>
       </c>
@@ -7113,7 +9178,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="10" t="s">
         <v>420</v>
       </c>
@@ -7124,7 +9189,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
         <v>423</v>
       </c>
@@ -7135,7 +9200,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
         <v>426</v>
       </c>
@@ -7146,7 +9211,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
         <v>429</v>
       </c>
@@ -7157,7 +9222,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="10" t="s">
         <v>432</v>
       </c>
@@ -7168,7 +9233,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>435</v>
       </c>
@@ -7179,7 +9244,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
@@ -7190,7 +9255,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
         <v>441</v>
       </c>
@@ -7201,7 +9266,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="10" t="s">
         <v>444</v>
       </c>
@@ -7212,7 +9277,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="10" t="s">
         <v>447</v>
       </c>
@@ -7223,7 +9288,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="10" t="s">
         <v>450</v>
       </c>
@@ -7234,7 +9299,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
         <v>453</v>
       </c>
@@ -7245,7 +9310,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="10" t="s">
         <v>456</v>
       </c>
@@ -7256,7 +9321,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="10" t="s">
         <v>459</v>
       </c>
@@ -7267,7 +9332,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="10" t="s">
         <v>462</v>
       </c>
@@ -7278,7 +9343,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="10" t="s">
         <v>465</v>
       </c>
@@ -7289,7 +9354,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="10" t="s">
         <v>468</v>
       </c>
@@ -7300,7 +9365,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
         <v>471</v>
       </c>
@@ -7311,7 +9376,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="10" t="s">
         <v>474</v>
       </c>
@@ -7322,7 +9387,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
         <v>477</v>
       </c>
@@ -7333,7 +9398,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
         <v>480</v>
       </c>
@@ -7344,7 +9409,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="10" t="s">
         <v>483</v>
       </c>
@@ -7355,7 +9420,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
         <v>486</v>
       </c>
@@ -7366,7 +9431,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="10" t="s">
         <v>489</v>
       </c>
@@ -7377,7 +9442,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="10" t="s">
         <v>492</v>
       </c>
@@ -7388,7 +9453,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="10" t="s">
         <v>495</v>
       </c>
@@ -7399,7 +9464,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
         <v>498</v>
       </c>
@@ -7410,7 +9475,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
         <v>501</v>
       </c>
@@ -7421,7 +9486,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="10" t="s">
         <v>504</v>
       </c>
@@ -7432,7 +9497,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="10" t="s">
         <v>507</v>
       </c>
@@ -7443,7 +9508,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="10" t="s">
         <v>510</v>
       </c>
@@ -7454,7 +9519,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="10" t="s">
         <v>513</v>
       </c>
@@ -7465,7 +9530,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="10" t="s">
         <v>516</v>
       </c>
@@ -7476,7 +9541,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="10" t="s">
         <v>519</v>
       </c>
@@ -7487,7 +9552,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="10" t="s">
         <v>522</v>
       </c>
@@ -7498,7 +9563,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="10" t="s">
         <v>525</v>
       </c>
@@ -7509,7 +9574,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
         <v>528</v>
       </c>
@@ -7520,7 +9585,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="10" t="s">
         <v>531</v>
       </c>
@@ -7531,7 +9596,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="10" t="s">
         <v>534</v>
       </c>
@@ -7542,7 +9607,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
         <v>537</v>
       </c>
@@ -7553,7 +9618,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="10" t="s">
         <v>540</v>
       </c>
@@ -7564,7 +9629,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="10" t="s">
         <v>543</v>
       </c>
@@ -7575,7 +9640,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
         <v>546</v>
       </c>
@@ -7586,7 +9651,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
         <v>549</v>
       </c>
@@ -7597,7 +9662,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
         <v>552</v>
       </c>
@@ -7608,7 +9673,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="10" t="s">
         <v>555</v>
       </c>
@@ -7619,7 +9684,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="10" t="s">
         <v>558</v>
       </c>
@@ -7630,7 +9695,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="10" t="s">
         <v>561</v>
       </c>
@@ -7641,7 +9706,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
         <v>564</v>
       </c>
@@ -7652,7 +9717,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="10" t="s">
         <v>567</v>
       </c>
@@ -7663,7 +9728,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="10" t="s">
         <v>570</v>
       </c>
@@ -7674,7 +9739,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="10" t="s">
         <v>573</v>
       </c>
@@ -7685,7 +9750,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="10" t="s">
         <v>576</v>
       </c>
@@ -7696,7 +9761,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="10" t="s">
         <v>579</v>
       </c>
@@ -7707,7 +9772,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="10" t="s">
         <v>582</v>
       </c>
@@ -7718,7 +9783,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="10" t="s">
         <v>585</v>
       </c>
@@ -7729,7 +9794,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="10" t="s">
         <v>588</v>
       </c>
@@ -7740,7 +9805,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="10" t="s">
         <v>591</v>
       </c>
@@ -7751,7 +9816,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="10" t="s">
         <v>594</v>
       </c>
@@ -7762,7 +9827,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="10" t="s">
         <v>597</v>
       </c>
@@ -7773,7 +9838,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="10" t="s">
         <v>600</v>
       </c>
@@ -7784,7 +9849,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="10" t="s">
         <v>603</v>
       </c>
@@ -7795,7 +9860,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="10" t="s">
         <v>606</v>
       </c>
@@ -7806,7 +9871,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="10" t="s">
         <v>609</v>
       </c>
@@ -7817,7 +9882,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="10" t="s">
         <v>612</v>
       </c>
@@ -7828,7 +9893,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="10" t="s">
         <v>615</v>
       </c>
@@ -7839,7 +9904,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="10" t="s">
         <v>618</v>
       </c>
@@ -7850,7 +9915,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="10" t="s">
         <v>621</v>
       </c>
@@ -7861,7 +9926,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
         <v>624</v>
       </c>
@@ -7872,7 +9937,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="10" t="s">
         <v>627</v>
       </c>
@@ -7883,7 +9948,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
         <v>630</v>
       </c>
@@ -7894,7 +9959,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="10" t="s">
         <v>633</v>
       </c>
@@ -7905,7 +9970,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="10" t="s">
         <v>636</v>
       </c>
@@ -7916,7 +9981,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="10" t="s">
         <v>639</v>
       </c>
@@ -7927,7 +9992,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="10" t="s">
         <v>642</v>
       </c>
@@ -7938,7 +10003,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="10" t="s">
         <v>645</v>
       </c>
@@ -7949,7 +10014,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="10" t="s">
         <v>648</v>
       </c>
@@ -7960,7 +10025,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="10" t="s">
         <v>651</v>
       </c>
@@ -7971,7 +10036,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="10" t="s">
         <v>654</v>
       </c>
@@ -7982,7 +10047,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="10" t="s">
         <v>657</v>
       </c>
@@ -7993,7 +10058,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="10" t="s">
         <v>660</v>
       </c>
@@ -8004,7 +10069,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
         <v>663</v>
       </c>
@@ -8015,7 +10080,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="10" t="s">
         <v>666</v>
       </c>
@@ -8026,7 +10091,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="10" t="s">
         <v>669</v>
       </c>
@@ -8037,7 +10102,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
         <v>672</v>
       </c>
@@ -8048,7 +10113,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="10" t="s">
         <v>675</v>
       </c>
@@ -8059,7 +10124,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="10" t="s">
         <v>678</v>
       </c>
@@ -8070,7 +10135,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="10" t="s">
         <v>681</v>
       </c>
@@ -8081,7 +10146,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="10" t="s">
         <v>684</v>
       </c>
@@ -8092,7 +10157,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="10" t="s">
         <v>687</v>
       </c>
@@ -8103,7 +10168,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="10" t="s">
         <v>690</v>
       </c>
@@ -8114,7 +10179,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="10" t="s">
         <v>693</v>
       </c>
@@ -8125,7 +10190,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="10" t="s">
         <v>696</v>
       </c>
@@ -8136,7 +10201,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="10" t="s">
         <v>699</v>
       </c>
@@ -8147,7 +10212,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
         <v>702</v>
       </c>
@@ -8158,7 +10223,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="10" t="s">
         <v>705</v>
       </c>
@@ -8169,7 +10234,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="10" t="s">
         <v>708</v>
       </c>
@@ -8180,7 +10245,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="10" t="s">
         <v>711</v>
       </c>
@@ -8191,7 +10256,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="10" t="s">
         <v>714</v>
       </c>
@@ -8202,7 +10267,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="10" t="s">
         <v>717</v>
       </c>
@@ -8213,7 +10278,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="10" t="s">
         <v>720</v>
       </c>
@@ -8224,7 +10289,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="10" t="s">
         <v>723</v>
       </c>
@@ -8235,7 +10300,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
         <v>726</v>
       </c>
@@ -8246,7 +10311,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="10" t="s">
         <v>729</v>
       </c>
@@ -8257,7 +10322,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="10" t="s">
         <v>732</v>
       </c>
@@ -8268,7 +10333,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
         <v>735</v>
       </c>
@@ -8279,7 +10344,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="10" t="s">
         <v>738</v>
       </c>
@@ -8290,7 +10355,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
         <v>741</v>
       </c>
@@ -8301,7 +10366,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="10" t="s">
         <v>744</v>
       </c>
@@ -8312,7 +10377,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="10" t="s">
         <v>747</v>
       </c>
@@ -8323,7 +10388,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="10" t="s">
         <v>750</v>
       </c>
@@ -8334,7 +10399,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="10" t="s">
         <v>753</v>
       </c>
@@ -8345,7 +10410,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="10" t="s">
         <v>756</v>
       </c>
@@ -8356,7 +10421,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="10" t="s">
         <v>759</v>
       </c>
@@ -8367,7 +10432,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
         <v>762</v>
       </c>
@@ -8378,7 +10443,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
         <v>765</v>
       </c>
@@ -8389,7 +10454,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
         <v>768</v>
       </c>
@@ -8400,7 +10465,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
         <v>771</v>
       </c>
@@ -8411,7 +10476,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
         <v>774</v>
       </c>
@@ -8422,7 +10487,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="10" t="s">
         <v>777</v>
       </c>
@@ -8433,7 +10498,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
         <v>780</v>
       </c>
@@ -8444,7 +10509,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="10" t="s">
         <v>783</v>
       </c>
@@ -8455,7 +10520,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="10" t="s">
         <v>786</v>
       </c>
@@ -8466,7 +10531,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="10" t="s">
         <v>789</v>
       </c>
@@ -8477,7 +10542,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="10" t="s">
         <v>792</v>
       </c>
@@ -8488,7 +10553,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="10" t="s">
         <v>795</v>
       </c>
@@ -8499,7 +10564,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="10" t="s">
         <v>798</v>
       </c>
@@ -8510,7 +10575,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" s="10" t="s">
         <v>801</v>
       </c>
@@ -8521,7 +10586,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" s="10" t="s">
         <v>804</v>
       </c>
@@ -8532,7 +10597,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="10" t="s">
         <v>807</v>
       </c>
@@ -8543,7 +10608,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="10" t="s">
         <v>810</v>
       </c>
@@ -8554,7 +10619,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="10" t="s">
         <v>813</v>
       </c>
@@ -8565,7 +10630,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" s="10" t="s">
         <v>816</v>
       </c>
@@ -8576,7 +10641,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
         <v>819</v>
       </c>
@@ -8587,7 +10652,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
         <v>822</v>
       </c>
@@ -8598,7 +10663,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="10" t="s">
         <v>825</v>
       </c>
@@ -8609,7 +10674,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="10" t="s">
         <v>828</v>
       </c>
@@ -8620,7 +10685,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="10" t="s">
         <v>831</v>
       </c>
@@ -8631,7 +10696,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="10" t="s">
         <v>834</v>
       </c>
@@ -8642,7 +10707,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="10" t="s">
         <v>837</v>
       </c>
@@ -8653,7 +10718,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
         <v>840</v>
       </c>
@@ -8664,7 +10729,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="10" t="s">
         <v>843</v>
       </c>
@@ -8675,7 +10740,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="10" t="s">
         <v>846</v>
       </c>
@@ -8686,7 +10751,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="10" t="s">
         <v>849</v>
       </c>
@@ -8697,7 +10762,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="10" t="s">
         <v>852</v>
       </c>
@@ -8708,7 +10773,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="10" t="s">
         <v>855</v>
       </c>
@@ -8719,7 +10784,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>858</v>
       </c>
@@ -8730,7 +10795,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>861</v>
       </c>
@@ -8741,7 +10806,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>864</v>
       </c>
@@ -8752,7 +10817,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>867</v>
       </c>
@@ -8763,7 +10828,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>870</v>
       </c>
@@ -8774,7 +10839,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" s="10" t="s">
         <v>873</v>
       </c>
@@ -8785,7 +10850,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>876</v>
       </c>
@@ -8807,2114 +10872,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="137.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="390" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="7" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>901</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="198.26953125" style="4" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>892</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744F2D0C-79DF-4FE3-924E-E680015F9291}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="229.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>899</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2C24DB-5CFD-48C4-BB67-81838BA61C50}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="328.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BBE4C-C868-422D-A432-89141BF78270}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="286.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537C8D36-44B6-40AB-B2F5-C278C8F38BBE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="288" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1208CFA8-0BD4-4A00-92D8-FF2B69E34213}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="294" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D76C43-B7D3-42D3-B057-81CA4865142E}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="125.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="319" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>913</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C668CA08-39B4-442C-BE86-54D5793A9F15}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="260.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82938685-CEEB-4659-B68E-B225C7C9053C}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="308.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C69BDA-CBD4-4A20-96F1-D4184C7A4A9F}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="152.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="258.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>882</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B002E-5D4B-4A97-8E05-ADA2BC7262BC}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="348" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35913B4E-3457-4352-AB64-7123F047E008}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="243.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FEA048-930A-43AC-A2F7-E864F3A29AEA}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.54296875" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDA5AB7-BD7F-4972-B610-8565F27586E1}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3A9AAE-7632-44EA-B097-966294B825CF}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6950BB04-C139-4D8C-A7DF-A5C6DE881B95}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0EDBDB-CFB0-452E-9EB1-4612E534D157}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFB3DE4-9A8D-444C-8A7F-95843C784F87}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB4192-B3A0-40C4-9076-17E7860549D0}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="253.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="279" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>893</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C70DEC-BE18-4032-87AC-08A2E40C3A39}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C59D7F3-BDC1-449F-9172-26F24432D1B6}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF4D87F-C244-46B9-BEBE-7BAD5D19F1F9}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EFC30CA-8C29-4D4C-B219-684CAC50F683}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051B8018-23E1-4D0A-B47D-B5B875F199B2}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="199.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>902</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>903</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD5BEFF-ABF3-4924-AB24-FF61AF228C0E}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924E1A3D-452D-420C-B25E-B5B00D9E4E1C}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815AD19-E228-474C-9937-3BF8367B118E}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D15E140-89C9-45F3-80F4-6B8F3C0CB47C}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D16401-415E-4611-9BEF-C11909718B5A}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="223.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>894</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE1070B-144A-405D-8FC5-7DE029CC4010}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29691E-1FE6-43C9-8319-10047CCCEDC2}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44602A52-179B-4771-A428-8A5F60E9F4E5}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A8B149-F3B9-47FC-B67F-BAF2CCCF6F3A}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407DE1E1-ED4A-4EC4-9635-4F064BD979D5}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD0BC59-9F8E-4902-8633-6FC5285FFBA9}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE61185-CF8B-43DA-9230-D26A514F1564}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="120.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="271.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7DC1EE-86C5-4108-AF46-1519F3819416}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC14161-2EAA-48CD-8103-6BBBB2474891}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432DB22F-F7FA-4CA9-A149-B4C592E95431}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59C6F2-69D0-4598-BA12-1B489ABE98B2}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="181.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>895</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C770D3C-EBB7-4325-A0BF-2D0A464BBA81}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="377" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="406" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94F2EB0-C540-42F2-9029-153D236879E0}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2174F19C-D9CC-4AA4-AC39-2264F751CA4E}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="391.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="348" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1F98BC-569D-4E63-A11C-5D8C488EFFA3}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872AC014-EDC6-46B6-9F04-A4A110CE1015}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="319" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="290" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DCF04D-F322-424A-ABB9-6A9DCAD730DC}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="232" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82D4A72-6C09-4E6C-AC1C-1FD3518043C3}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="290" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>994</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1D8E1-BE83-467E-ABE2-EB20A46DABB5}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="222.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>916</v>
-      </c>
+      <c r="B4" s="7" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10922,15 +10928,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{385D6F23-1F00-43DA-8201-777B854F56F6}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="137.26953125" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="135.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10938,38 +10944,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="400" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="6"/>
+      <c r="B4" s="1" t="s">
+        <v>898</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10977,15 +10974,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A026B00C-E4B3-4E36-BEA1-AD93DF3D486F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="135.54296875" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="114.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10993,28 +10990,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>
@@ -11023,44 +11020,47 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27175C00-9C85-488E-AAAE-6AE4E23126BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
-    <col min="2" max="2" width="114.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="303" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>897</v>
+      <c r="B4" s="3" t="s">
+        <v>901</v>
       </c>
     </row>
   </sheetData>
